--- a/data/output/corpus_run/queries.xlsx
+++ b/data/output/corpus_run/queries.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K201"/>
+  <dimension ref="A1:J201"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -409,9 +409,8 @@
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="60.83203125" customWidth="1"/>
-    <col min="10" max="10" width="60.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="80.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,9 +442,6 @@
         <v>query_text</v>
       </c>
       <c r="J1" t="str">
-        <v>query_text_zh</v>
-      </c>
-      <c r="K1" t="str">
         <v>error</v>
       </c>
     </row>
@@ -454,33 +450,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>q_scene_002_001</v>
+        <v>q_scene_006_001</v>
       </c>
       <c r="C2" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D2" t="str">
-        <v>个人生活类</v>
+        <v>Adding &amp; Creating 新建与创建</v>
       </c>
       <c r="E2" t="str">
-        <v>Travel Memory Scrapbook</v>
+        <v>Task creation card with priority selector and due date picker</v>
       </c>
       <c r="F2" t="str">
         <v>medium</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="H2">
-        <v>11837</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Build a Travel Memory Scrapbook screen for a mobile app where users can create trip entries with a cover photo, trip title, date range, and a collage-style photo grid underneath. Each entry should be tappable to open a detail view with a vertical scroll layout showing photos mixed with short text notes — kind of like a digital scrapbook page. Keep the UI warm and nostalgic, maybe slightly aged paper texture as background, and make sure the photo grid on the entry card supports at least 3–5 images in a masonry or asymmetric layout rather than a plain uniform grid.</v>
+        <v>[DRY-RUN] Task creation card with priority selector and due date picker — medium</v>
       </c>
       <c r="J2" t="str">
-        <v>帮我做一个移动端的旅行记忆相册页面，用户可以新建旅程卡片，每张卡片上有封面照片、旅程标题、起止日期，以及下方一个拼贴风格的照片网格。点击卡片后进入详情页，详情页是竖向滚动的布局，照片和短文字笔记交错穿插排列，整体感觉就像翻一本数字剪贴簿。视觉风格要温暖、有点复古怀旧，背景最好带做旧纸张的质感，卡片上的照片网格要能放3到5张图，用瀑布流或者不对称的方式来排，不要那种方方正正的均匀网格。</v>
-      </c>
-      <c r="K2" t="str">
         <v/>
       </c>
     </row>
@@ -489,33 +482,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>q_scene_002_002</v>
+        <v>q_scene_006_002</v>
       </c>
       <c r="C3" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D3" t="str">
-        <v>个人生活类</v>
+        <v>Adding &amp; Creating 新建与创建</v>
       </c>
       <c r="E3" t="str">
-        <v>Annual Family Photo Album</v>
+        <v>Event planning form with location, attendee invite and RSVP</v>
       </c>
       <c r="F3" t="str">
         <v>medium</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>10119</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Build a mobile screen for an Annual Family Photo Album app — the main view should show a vertical scrollable timeline where each year is a collapsible section header with a cover photo thumbnail and a count of photos inside. Tapping a year expands it into a grid of photos (3 columns), and long-pressing any photo should show a quick preview overlay with the date and a short caption field. Keep the color palette warm and minimal, no heavy chrome.</v>
+        <v>[DRY-RUN] Event planning form with location, attendee invite and RSVP — medium</v>
       </c>
       <c r="J3" t="str">
-        <v>做一个家庭年度相册应用的移动端页面——主视图是一个可垂直滚动的时间轴，每一年作为一个可折叠的分区标题，显示该年的封面缩略图和照片数量。点击某一年可展开，以3列网格的形式展示该年所有照片；长按任意一张照片则弹出快速预览浮层，显示拍摄日期并提供一个简短的备注输入框。整体配色温暖克制，不要复杂的界面装饰。</v>
-      </c>
-      <c r="K3" t="str">
         <v/>
       </c>
     </row>
@@ -524,33 +514,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>q_scene_002_003</v>
+        <v>q_scene_006_003</v>
       </c>
       <c r="C4" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D4" t="str">
-        <v>个人生活类</v>
+        <v>Adding &amp; Creating 新建与创建</v>
       </c>
       <c r="E4" t="str">
-        <v>Baby Growth Milestone Tracker</v>
+        <v>Contact creation via QR scan or business card OCR</v>
       </c>
       <c r="F4" t="str">
         <v>medium</v>
       </c>
       <c r="G4">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>9197</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>Build a mobile screen for a Baby Growth Milestone Tracker where parents can log and view their baby's developmental milestones organized by age range (0-3 months, 3-6 months, etc.). Each milestone card should show a checkmark toggle, a short description, and an optional photo slot. Include a progress ring at the top showing overall completion percentage for the current age stage, and make sure the milestone list is scrollable with smooth section headers separating each age group.</v>
+        <v>[DRY-RUN] Contact creation via QR scan or business card OCR — medium</v>
       </c>
       <c r="J4" t="str">
-        <v>做一个手机端的宝宝成长里程碑记录页面，让父母可以按年龄段（0-3个月、3-6个月等）记录和查看宝宝的发育进展。每个里程碑卡片要有一个勾选开关、简短描述，以及一个可选的照片插槽。页面顶部放一个圆形进度环，显示当前年龄阶段的整体完成百分比。里程碑列表要支持滚动，各年龄组之间用悬浮吸顶的分组标题隔开，滚动效果要流畅。</v>
-      </c>
-      <c r="K4" t="str">
         <v/>
       </c>
     </row>
@@ -559,33 +546,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>q_scene_002_004</v>
+        <v>q_scene_006_004</v>
       </c>
       <c r="C5" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D5" t="str">
-        <v>个人生活类</v>
+        <v>Adding &amp; Creating 新建与创建</v>
       </c>
       <c r="E5" t="str">
-        <v>Painting &amp; Artwork Exhibition</v>
+        <v>Wishlist item add with price-drop alert and shop link</v>
       </c>
       <c r="F5" t="str">
         <v>medium</v>
       </c>
       <c r="G5">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>9590</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Build a painting &amp; artwork exhibition screen for a personal mobile app where users can browse their collected artworks in a gallery grid view, tap to open a full-screen detail modal that shows the artwork image, title, artist name, medium, and a short note the user wrote about why they saved it. The grid should support two layout modes (2-column tight and single wide-card scroll) with a toggle button at the top, and each card should have a subtle tag label like "Oil" or "Watercolor" overlaid on the bottom-left corner.</v>
+        <v>[DRY-RUN] Wishlist item add with price-drop alert and shop link — medium</v>
       </c>
       <c r="J5" t="str">
-        <v>做一个个人移动端 App 里的绘画与艺术品展示页，用户可以在画廊网格中浏览自己收藏的作品，点击某件作品后弹出全屏详情弹窗，展示作品图片、标题、艺术家姓名、所用媒介材质，以及用户自己写的一段收藏理由备注。网格需要支持两种布局模式切换——双列紧凑网格和单列宽卡片滚动，顶部放一个切换按钮；每张卡片左下角要叠加一个小标签，比如「油画」或「水彩」。</v>
-      </c>
-      <c r="K5" t="str">
         <v/>
       </c>
     </row>
@@ -594,33 +578,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>q_scene_002_005</v>
+        <v>q_scene_007_001</v>
       </c>
       <c r="C6" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D6" t="str">
-        <v>个人生活类</v>
+        <v>Editing &amp; Updating 编辑与更新</v>
       </c>
       <c r="E6" t="str">
-        <v>Pet Life Chronicle</v>
+        <v>Workout log correction with edit history and reason note</v>
       </c>
       <c r="F6" t="str">
         <v>medium</v>
       </c>
       <c r="G6">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>11868</v>
+        <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Build a mobile app screen for a "Pet Life Chronicle" feature where users can log daily moments for their pets — each entry should have a photo, mood tag (happy, sleepy, playful, etc.), and a short note. The timeline view should display entries in a vertical scroll with a card-based layout, showing the pet's avatar and name at the top, and each card should have a soft rounded style with pastel background colors that vary by mood tag. Also include a floating "+" button to add new entries.</v>
+        <v>[DRY-RUN] Workout log correction with edit history and reason note — medium</v>
       </c>
       <c r="J6" t="str">
-        <v>做一个"宠物生活日记"功能的移动端页面，让用户可以记录宠物的日常瞬间——每条记录包含一张照片、一个心情标签（开心、困困、活泼等）以及一段简短的文字备注。时间轴视图以垂直滚动的卡片式布局展示所有记录，顶部显示宠物的头像和名字，每张卡片采用圆角柔和的风格，并根据不同的心情标签搭配对应的莫兰迪色系背景色。另外页面右下角要有一个悬浮的"+"按钮用于添加新记录。</v>
-      </c>
-      <c r="K6" t="str">
         <v/>
       </c>
     </row>
@@ -629,33 +610,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>q_scene_002_006</v>
+        <v>q_scene_007_002</v>
       </c>
       <c r="C7" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D7" t="str">
-        <v>个人生活类</v>
+        <v>Editing &amp; Updating 编辑与更新</v>
       </c>
       <c r="E7" t="str">
-        <v>Pregnancy Journey Diary</v>
+        <v>Budget category rename and icon change with live preview</v>
       </c>
       <c r="F7" t="str">
         <v>medium</v>
       </c>
       <c r="G7">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>9212</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Build a mobile screen for a Pregnancy Journey Diary app where users can log weekly milestones — each week entry should have a card with the baby's size comparison (like "size of a lemon"), a mood tracker with emoji selection, and a photo upload slot. The timeline should scroll vertically with week numbers on the left as sticky anchors, and tapping a card expands it to show a notes field and a symptom checklist. Keep the color palette soft and warm — think blush pinks and cream tones.</v>
+        <v>[DRY-RUN] Budget category rename and icon change with live preview — medium</v>
       </c>
       <c r="J7" t="str">
-        <v>帮我做一个孕期日记App的移动端页面，用户可以记录每周的重要时刻——每一周都有一张卡片，显示宝宝的大小类比（比如"柠檬那么大"）、带表情符号的心情打卡，以及一个上传照片的位置。时间轴整体垂直滚动，左侧固定显示周数作为锚点导航，点击卡片后展开，露出备注输入框和症状核对清单。配色要温柔温暖，以粉玫瑰色和奶油色为主基调。</v>
-      </c>
-      <c r="K7" t="str">
         <v/>
       </c>
     </row>
@@ -664,33 +642,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>q_scene_002_007</v>
+        <v>q_scene_007_003</v>
       </c>
       <c r="C8" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D8" t="str">
-        <v>个人生活类</v>
+        <v>Editing &amp; Updating 编辑与更新</v>
       </c>
       <c r="E8" t="str">
-        <v>Wedding Anniversary Gallery</v>
+        <v>Event reschedule with attendee re-notification dialog</v>
       </c>
       <c r="F8" t="str">
         <v>medium</v>
       </c>
       <c r="G8">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="H8">
-        <v>10196</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>Build a Wedding Anniversary Gallery screen for a mobile app — it should display photos organized by year (e.g., Year 1, Year 2, etc.) in a vertical scroll layout, with each year section showing a horizontal swipeable strip of photos. Add a floating "Add Memory" button that opens a simple upload sheet where the user can pick a photo and optionally add a short caption. Keep the overall vibe warm and minimal, maybe a soft cream background with subtle gold accents for the year labels.</v>
+        <v>[DRY-RUN] Event reschedule with attendee re-notification dialog — medium</v>
       </c>
       <c r="J8" t="str">
-        <v>帮我做一个手机 App 里的结婚纪念相册页面——按年份（比如第1年、第2年这样）把照片分组展示，整体是垂直滚动的布局，每个年份区块里有一排可以左右滑动的照片条。页面上要有一个悬浮的"添加回忆"按钮，点击后弹出一个简单的上传面板，让用户选张照片，还可以选填一段简短的描述。整体风格要温馨、简洁，背景用柔和的米白色，年份标签用淡淡的金色点缀一下就好。</v>
-      </c>
-      <c r="K8" t="str">
         <v/>
       </c>
     </row>
@@ -699,33 +674,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>q_scene_002_008</v>
+        <v>q_scene_007_004</v>
       </c>
       <c r="C9" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D9" t="str">
-        <v>个人生活类</v>
+        <v>Editing &amp; Updating 编辑与更新</v>
       </c>
       <c r="E9" t="str">
-        <v>Childhood Memory Archive</v>
+        <v>Itinerary day reorder via drag-and-drop with conflict check</v>
       </c>
       <c r="F9" t="str">
         <v>medium</v>
       </c>
       <c r="G9">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="H9">
-        <v>11329</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v>Build a Childhood Memory Archive screen for a personal mobile app — it should display memories as a vertical timeline with each entry showing a thumbnail photo, age/year tag, and a short caption. Tapping a card expands it into a full-screen detail view with a larger image, a longer text block, and a location tag if available. Keep the overall color palette warm and slightly aged-looking (think cream, faded amber, dusty rose), and make sure the timeline has a visible connecting line with small dot markers between entries.</v>
+        <v>[DRY-RUN] Itinerary day reorder via drag-and-drop with conflict check — medium</v>
       </c>
       <c r="J9" t="str">
-        <v>做一个个人移动应用里的「童年记忆档案」页面——用竖向时间轴的方式展示每段记忆，每条卡片要有缩略图、年龄／年份标签和一句简短描述。点击卡片后展开成全屏详情视图，显示更大的图片、完整的文字内容，以及位置标签（如果有的话）。整体配色要偏暖、带一点做旧感，像奶油色、褪色琥珀、雾玫瑰这类调子，时间轴要有一条贯穿各条目的连接线，每个节点之间用小圆点标记。</v>
-      </c>
-      <c r="K9" t="str">
         <v/>
       </c>
     </row>
@@ -734,33 +706,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>q_scene_002_009</v>
+        <v>q_scene_008_001</v>
       </c>
       <c r="C10" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D10" t="str">
-        <v>个人生活类</v>
+        <v>Searching &amp; Finding 搜索与查找</v>
       </c>
       <c r="E10" t="str">
-        <v>Garden Growth Journal</v>
+        <v>Multi-criteria filter-then-search with chip display</v>
       </c>
       <c r="F10" t="str">
         <v>medium</v>
       </c>
       <c r="G10">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="H10">
-        <v>9045</v>
+        <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>Build a Garden Growth Journal screen for a mobile app where users can log their plants' progress over time. Each plant entry should have a photo timeline at the top (horizontal scroll of dated photos), below that a notes section with date-stamped entries, and a simple health status tracker using emoji indicators (thriving, okay, struggling). The overall vibe should feel like a personal nature diary — soft greens, earthy tones, rounded cards. Make sure tapping a photo in the timeline expands it into a full-screen modal with the date and any attached note.</v>
+        <v>[DRY-RUN] Multi-criteria filter-then-search with chip display — medium</v>
       </c>
       <c r="J10" t="str">
-        <v>做一个移动端的「花园成长日记」页面，让用户可以记录植物的生长过程。每条植物记录顶部是一个带日期的照片时间轴（横向滚动），往下是带时间戳的文字笔记区，还有一个用 emoji 表示的简单健康状态追踪器（茁壮成长、状态一般、有点萎靡）。整体风格要像私人自然日记那种感觉——柔和的绿色系、大地色调、圆角卡片。记得点击时间轴里的照片后，要全屏弹出一个 modal，显示对应的日期和附带的笔记内容。</v>
-      </c>
-      <c r="K10" t="str">
         <v/>
       </c>
     </row>
@@ -769,33 +738,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>q_scene_003_001</v>
+        <v>q_scene_008_002</v>
       </c>
       <c r="C11" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D11" t="str">
-        <v>个人专业类</v>
+        <v>Searching &amp; Finding 搜索与查找</v>
       </c>
       <c r="E11" t="str">
-        <v>Photography Portfolio Showcase</v>
+        <v>Saved search with new-result push notification</v>
       </c>
       <c r="F11" t="str">
         <v>medium</v>
       </c>
       <c r="G11">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="H11">
-        <v>10582</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Build a mobile photography portfolio screen where photos are displayed in a masonry grid layout — each card should show the image with a subtle overlay on tap that reveals the title, shoot date, and category tag. There needs to be a horizontal filter bar at the top to switch between categories like Portrait, Landscape, and Street, and tapping a photo should open a full-screen viewer with swipe-to-navigate between shots in the same category.</v>
+        <v>[DRY-RUN] Saved search with new-result push notification — medium</v>
       </c>
       <c r="J11" t="str">
-        <v>做一个手机端的摄影作品集页面，照片以瀑布流布局展示——每张卡片点击后出现一层半透明遮罩，显示照片标题、拍摄日期和分类标签。顶部需要一个横向滚动的分类筛选栏，可以在人像、风景、街拍等类别之间切换；点击某张照片后进入全屏预览模式，支持在同一分类的照片之间左右滑动切换。</v>
-      </c>
-      <c r="K11" t="str">
         <v/>
       </c>
     </row>
@@ -804,33 +770,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>q_scene_003_002</v>
+        <v>q_scene_008_003</v>
       </c>
       <c r="C12" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D12" t="str">
-        <v>个人专业类</v>
+        <v>Searching &amp; Finding 搜索与查找</v>
       </c>
       <c r="E12" t="str">
-        <v>UI/UX Designer Case Studies</v>
+        <v>Search scoped within folder, album or collection</v>
       </c>
       <c r="F12" t="str">
         <v>medium</v>
       </c>
       <c r="G12">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H12">
-        <v>10851</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Build a case study detail screen for a UI/UX designer portfolio app — each case should have a hero image at the top, followed by a scrollable section with the problem statement, process breakdown (with inline sketches or wireframe thumbnails), and final outcome. Add a sticky bottom bar showing project tags like "Mobile", "B2B", "Redesign" and a save/bookmark button. Keep the layout clean and editorial, something like a Medium article but more visual-heavy.</v>
+        <v>[DRY-RUN] Search scoped within folder, album or collection — medium</v>
       </c>
       <c r="J12" t="str">
-        <v>帮我做一个UI/UX设计师作品集App里的案例详情页——每个案例顶部要有一张大图，下面是可滚动的内容区，依次展示问题陈述、设计过程拆解（中间穿插草图或线框图缩略图），以及最终成果。底部加一个悬浮固定栏，显示项目标签比如"移动端"、"B2B"、"改版重设计"，还有一个收藏/书签按钮。整体风格要干净、有杂志感，有点像Medium的文章排版，但视觉内容要更重一些。</v>
-      </c>
-      <c r="K12" t="str">
         <v/>
       </c>
     </row>
@@ -839,33 +802,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>q_scene_003_003</v>
+        <v>q_scene_008_004</v>
       </c>
       <c r="C13" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D13" t="str">
-        <v>个人专业类</v>
+        <v>Searching &amp; Finding 搜索与查找</v>
       </c>
       <c r="E13" t="str">
-        <v>Graphic Designer Brand Book</v>
+        <v>Autocomplete with recent history and trending terms</v>
       </c>
       <c r="F13" t="str">
         <v>medium</v>
       </c>
       <c r="G13">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>7861</v>
+        <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>Build a mobile screen for a Graphic Designer's personal Brand Book — it should display their core brand identity elements like logo variations, color palette swatches, and typography specimens in a clean, scrollable layout. Each section needs a collapsible header so users can expand or collapse it. The color swatches should show the hex code and a copy-to-clipboard tap action. Keep the overall visual style minimal and editorial, dark background with high-contrast type, no decorative fluff.</v>
+        <v>[DRY-RUN] Autocomplete with recent history and trending terms — medium</v>
       </c>
       <c r="J13" t="str">
-        <v>做一个平面设计师个人品牌手册的移动端页面——需要展示核心品牌视觉元素，包括 Logo 变体、色彩色板和字体排版示例，整体采用简洁的可滚动布局。每个区块要有可折叠的标题栏，支持展开和收起操作。色板需要显示对应的十六进制色值，并支持点击一键复制到剪贴板。整体视觉风格要简约、编辑感强，深色背景配高对比度文字，不要任何多余的装饰元素。</v>
-      </c>
-      <c r="K13" t="str">
         <v/>
       </c>
     </row>
@@ -874,33 +834,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>q_scene_003_004</v>
+        <v>q_scene_009_001</v>
       </c>
       <c r="C14" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D14" t="str">
-        <v>个人专业类</v>
+        <v>Selecting &amp; Choosing 选择与选取</v>
       </c>
       <c r="E14" t="str">
-        <v>Resume &amp; CV Builder</v>
+        <v>Searchable dropdown selection with grouped options</v>
       </c>
       <c r="F14" t="str">
         <v>medium</v>
       </c>
       <c r="G14">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="H14">
-        <v>8909</v>
+        <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v>Build a resume builder screen for mobile where users can fill in sections like Work Experience, Education, and Skills using expandable cards. Each card should have an "Add Entry" button at the bottom, and completed entries should show a summary preview (job title + company, or degree + school). There should be a floating "Export PDF" button fixed to the bottom of the screen that stays visible while scrolling through the form.</v>
+        <v>[DRY-RUN] Searchable dropdown selection with grouped options — medium</v>
       </c>
       <c r="J14" t="str">
-        <v>做一个手机端的简历制作页面，用户可以通过可展开的卡片填写工作经验、教育背景和技能等模块。每张卡片底部有一个「添加条目」按钮，已填写完成的条目以摘要形式展示（如职位名称＋公司，或学历＋学校名称）。页面底部固定一个悬浮的「导出 PDF」按钮，滚动表单时始终保持可见。</v>
-      </c>
-      <c r="K14" t="str">
         <v/>
       </c>
     </row>
@@ -909,33 +866,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>q_scene_003_005</v>
+        <v>q_scene_009_002</v>
       </c>
       <c r="C15" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D15" t="str">
-        <v>个人专业类</v>
+        <v>Selecting &amp; Choosing 选择与选取</v>
       </c>
       <c r="E15" t="str">
-        <v>Illustrator Artwork Gallery</v>
+        <v>Calendar date-range selector with visual span highlight</v>
       </c>
       <c r="F15" t="str">
         <v>medium</v>
       </c>
       <c r="G15">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>9446</v>
+        <v>0</v>
       </c>
       <c r="I15" t="str">
-        <v>Build an Illustrator Artwork Gallery screen for a personal portfolio app — needs a masonry or fixed-grid layout that displays high-res illustration thumbnails with the artwork title and medium (e.g. "digital ink", "watercolor") shown as a small tag overlay. Tapping a card should open a full-screen detail view with zoom support and a side panel showing process notes or artist commentary. Keep the overall aesthetic dark and minimal so the artwork stays front and center.</v>
+        <v>[DRY-RUN] Calendar date-range selector with visual span highlight — medium</v>
       </c>
       <c r="J15" t="str">
-        <v>为个人作品集应用搭建一个插画作品展示页面——需要用瀑布流或固定网格布局来展示高清插画缩略图，每张卡片上要叠加显示作品标题和创作媒介（比如"数字墨线"、"水彩"）的小标签。点击卡片后进入全屏详情视图，支持缩放操作，并带有侧边面板展示创作过程笔记或作者点评。整体风格保持深色极简，让作品本身成为视觉焦点。</v>
-      </c>
-      <c r="K15" t="str">
         <v/>
       </c>
     </row>
@@ -944,33 +898,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>q_scene_003_006</v>
+        <v>q_scene_009_003</v>
       </c>
       <c r="C16" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D16" t="str">
-        <v>个人专业类</v>
+        <v>Selecting &amp; Choosing 选择与选取</v>
       </c>
       <c r="E16" t="str">
-        <v>Freelance Copywriter Samples</v>
+        <v>Image grid multi-select with counter badge overlay</v>
       </c>
       <c r="F16" t="str">
         <v>medium</v>
       </c>
       <c r="G16">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>11432</v>
+        <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>Build a portfolio samples screen for a freelance copywriter profile — each sample card should show the project title, client industry tag, a 2-line excerpt of the copy, and a "View Full" button that expands to a scrollable modal with the complete text. Keep the list filterable by industry tag at the top, and make sure the card layout feels clean and readable on mobile without too much visual clutter.</v>
+        <v>[DRY-RUN] Image grid multi-select with counter badge overlay — medium</v>
       </c>
       <c r="J16" t="str">
-        <v>帮我做一个自由文案撰稿人个人主页的作品集展示页面，每张作品卡片需要包含项目标题、客户所属行业标签、两行文案摘录，以及一个"查看完整"按钮，点击后弹出可滚动的弹窗展示全文。页面顶部要支持按行业标签筛选作品列表，卡片整体布局在移动端要保持简洁易读，不要有太多视觉干扰。</v>
-      </c>
-      <c r="K16" t="str">
         <v/>
       </c>
     </row>
@@ -979,33 +930,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>q_scene_003_007</v>
+        <v>q_scene_009_004</v>
       </c>
       <c r="C17" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D17" t="str">
-        <v>个人专业类</v>
+        <v>Selecting &amp; Choosing 选择与选取</v>
       </c>
       <c r="E17" t="str">
-        <v>Architect Project Portfolio</v>
+        <v>Color swatch selection with live hex and name preview</v>
       </c>
       <c r="F17" t="str">
         <v>medium</v>
       </c>
       <c r="G17">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="H17">
-        <v>9473</v>
+        <v>0</v>
       </c>
       <c r="I17" t="str">
-        <v>Build a mobile portfolio screen for an architect that showcases their projects in a scrollable card grid — each card should show a hero image, project name, typology tag (residential, commercial, cultural, etc.), and year. Tapping a card opens a detail view with a full-bleed image carousel, project description, key specs (site area, program, status), and a section for concept diagrams or drawings. Keep the visual style minimal and editorial — dark background, clean sans-serif typography, and subtle transitions between views.</v>
+        <v>[DRY-RUN] Color swatch selection with live hex and name preview — medium</v>
       </c>
       <c r="J17" t="str">
-        <v>为一位建筑师设计一个移动端作品集页面，以可滚动的卡片网格展示项目——每张卡片显示主视觉图片、项目名称、类型标签（住宅、商业、文化等）以及年份。点击卡片后进入详情页，包含全出血图片轮播、项目描述、关键参数（用地面积、功能定位、建设状态），以及一个展示概念草图或设计图纸的区块。整体视觉风格保持极简、编辑感——深色背景、简洁无衬线字体，页面切换时带有细腻的过渡动效。</v>
-      </c>
-      <c r="K17" t="str">
         <v/>
       </c>
     </row>
@@ -1014,33 +962,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>q_scene_003_008</v>
+        <v>q_scene_010_001</v>
       </c>
       <c r="C18" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D18" t="str">
-        <v>个人专业类</v>
+        <v>Filtering &amp; Sorting 筛选与排序</v>
       </c>
       <c r="E18" t="str">
-        <v>Fashion Stylist Lookbook</v>
+        <v>Location radius filter on interactive map view</v>
       </c>
       <c r="F18" t="str">
         <v>medium</v>
       </c>
       <c r="G18">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>11701</v>
+        <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>Build a mobile lookbook screen for a fashion stylist portfolio app — the main view should be a vertical scroll of full-bleed editorial photos with a floating overlay showing the look name and styling notes, and tapping a photo expands it into a detail sheet that includes outfit breakdown (pieces, brands, color palette swatches) plus a "Save Look" button. Keep the aesthetic minimal and editorial — dark background, serif typography for titles, thin sans-serif for body text. The photo grid on the home tab should support both single-column and 2-column toggle.</v>
+        <v>[DRY-RUN] Location radius filter on interactive map view — medium</v>
       </c>
       <c r="J18" t="str">
-        <v>帮我为一款时尚造型师作品集 App 搭建一个移动端 Lookbook 页面——主界面是满版大图的纵向滚动列表，每张编辑风格照片上叠加一个浮动信息层，显示造型名称和搭配备注；点击任意照片后展开一个详情面板，内容包括单品拆解（具体单品、品牌、色板色块）以及一个「保存造型」按钮。整体视觉风格要极简、编辑感——深色背景、标题使用衬线字体、正文使用细款无衬线字体。首页标签的照片网格需支持单列与双列的一键切换。</v>
-      </c>
-      <c r="K18" t="str">
         <v/>
       </c>
     </row>
@@ -1049,33 +994,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>q_scene_003_009</v>
+        <v>q_scene_010_002</v>
       </c>
       <c r="C19" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D19" t="str">
-        <v>个人专业类</v>
+        <v>Filtering &amp; Sorting 筛选与排序</v>
       </c>
       <c r="E19" t="str">
-        <v>Interior Designer Moodboard</v>
+        <v>Tag AND/OR logic filter with toggle switch</v>
       </c>
       <c r="F19" t="str">
         <v>medium</v>
       </c>
       <c r="G19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>70804</v>
+        <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>Build a moodboard screen for an interior designer portfolio app — the layout should be a masonry grid where users can pin images tagged by room type (living room, bedroom, kitchen, etc.) and color palette. Each card should show a thumbnail, a small color swatch strip extracted from the image, and a tap-to-expand detail view with notes. Include a floating "+" button to add new items and a filter bar at the top to sort by tag or dominant color.</v>
+        <v>[DRY-RUN] Tag AND/OR logic filter with toggle switch — medium</v>
       </c>
       <c r="J19" t="str">
-        <v>为室内设计师作品集应用开发一个灵感板页面——布局采用瀑布流网格，用户可以将图片按房间类型（客厅、卧室、厨房等）和色彩搭配打标签收藏。每张卡片需展示缩略图、从图片中提取的小色块条，以及点击可展开的详情视图（含备注）。页面底部放一个悬浮的"+"按钮用于添加新内容，顶部设置筛选栏，支持按标签或主色调排序。</v>
-      </c>
-      <c r="K19" t="str">
         <v/>
       </c>
     </row>
@@ -1084,33 +1026,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>q_scene_004_001</v>
+        <v>q_scene_010_003</v>
       </c>
       <c r="C20" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D20" t="str">
-        <v>办公/商务类</v>
+        <v>Filtering &amp; Sorting 筛选与排序</v>
       </c>
       <c r="E20" t="str">
-        <v>SaaS Product Landing Page</v>
+        <v>Sort by relevance, date, rating or distance with dropdown</v>
       </c>
       <c r="F20" t="str">
         <v>medium</v>
       </c>
       <c r="G20">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="H20">
-        <v>14877</v>
+        <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>Build a mobile landing page for a B2B SaaS product — needs a hero section with a bold headline, short value prop, and a CTA button that sticks to the bottom on scroll. Below that, add a 3-feature highlights strip with icons and one-line descriptions, then a pricing tier section with two plans (monthly/annual toggle). Keep the visual style clean and corporate — think dark navy + white with accent blue. No carousels, everything stacked vertically for mobile.</v>
+        <v>[DRY-RUN] Sort by relevance, date, rating or distance with dropdown — medium</v>
       </c>
       <c r="J20" t="str">
-        <v>做一个面向 B2B SaaS 产品的移动端落地页——顶部需要一个 hero 区块，包含醒目的大标题、简短的价值主张，以及一个滚动时固定在底部的 CTA 按钮。往下是一个三栏功能亮点条，每栏带图标和一行说明文字，再往下是定价区块，提供两个套餐方案，支持按月/按年计费切换。整体视觉风格要简洁、商务感强，配色用深海军蓝加白色，点缀蓝色作为强调色。不要轮播组件，所有内容在移动端垂直堆叠排列。</v>
-      </c>
-      <c r="K20" t="str">
         <v/>
       </c>
     </row>
@@ -1119,33 +1058,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>q_scene_004_002</v>
+        <v>q_scene_010_004</v>
       </c>
       <c r="C21" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D21" t="str">
-        <v>办公/商务类</v>
+        <v>Filtering &amp; Sorting 筛选与排序</v>
       </c>
       <c r="E21" t="str">
-        <v>Startup Pitch Deck Viewer</v>
+        <v>Custom sort order drag-to-rank interface</v>
       </c>
       <c r="F21" t="str">
         <v>medium</v>
       </c>
       <c r="G21">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H21">
-        <v>10396</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
-        <v>Build a mobile Startup Pitch Deck Viewer screen where users can swipe through slide cards horizontally — each card shows the slide title, a thumbnail preview area, and a short summary text below it. Add a slide progress indicator at the top (e.g. "Slide 3 / 12") and a bottom toolbar with buttons for bookmarking the current slide and jumping to a specific section like Team, Problem, or Financials via a dropdown. Keep the layout clean and business-focused, dark navy background with white card surfaces.</v>
+        <v>[DRY-RUN] Custom sort order drag-to-rank interface — medium</v>
       </c>
       <c r="J21" t="str">
-        <v>做一个移动端的创业路演 Pitch Deck 查看页面，用户可以左右滑动浏览幻灯片卡片——每张卡片展示幻灯片标题、缩略图预览区域，以及下方的简短摘要文字。顶部加一个幻灯片进度提示，比如"第 3 页 / 共 12 页"，底部工具栏包含两个功能：收藏当前幻灯片的按钮，以及通过下拉菜单快速跳转到指定章节（如团队介绍、问题分析、财务数据等）。整体布局简洁、商务感强，深海军蓝背景搭配白色卡片。</v>
-      </c>
-      <c r="K21" t="str">
         <v/>
       </c>
     </row>
@@ -1154,33 +1090,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>q_scene_004_003</v>
+        <v>q_scene_011_001</v>
       </c>
       <c r="C22" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D22" t="str">
-        <v>办公/商务类</v>
+        <v>Deleting &amp; Removing 删除与移除</v>
       </c>
       <c r="E22" t="str">
-        <v>Annual Report Presentation</v>
+        <v>Delete with dependent item warning and cascade option</v>
       </c>
       <c r="F22" t="str">
         <v>medium</v>
       </c>
       <c r="G22">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="H22">
-        <v>8802</v>
+        <v>0</v>
       </c>
       <c r="I22" t="str">
-        <v>Build a mobile screen for an annual report presentation viewer — it should have a swipeable slide deck layout where each card shows a key metric or chart (revenue, growth, margins, etc.), with a sticky header showing the company name and fiscal year. Add a floating progress indicator so users can see which slide they're on, and make sure charts are tap-to-expand so you can view details in full screen. Keep the overall look clean and corporate, dark navy palette.</v>
+        <v>[DRY-RUN] Delete with dependent item warning and cascade option — medium</v>
       </c>
       <c r="J22" t="str">
-        <v>做一个手机端的年度报告演示查看页面，采用可左右滑动的卡片翻页布局，每张卡片展示一项核心指标或图表（营收、增长率、利润率等），页面顶部有吸顶标题栏，显示公司名称和财年。加一个悬浮进度指示器，让用户随时知道当前浏览的是第几张。图表要支持点击放大、全屏查看详情。整体风格简洁商务，采用深海军蓝配色。</v>
-      </c>
-      <c r="K22" t="str">
         <v/>
       </c>
     </row>
@@ -1189,33 +1122,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>q_scene_004_004</v>
+        <v>q_scene_011_002</v>
       </c>
       <c r="C23" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D23" t="str">
-        <v>办公/商务类</v>
+        <v>Deleting &amp; Removing 删除与移除</v>
       </c>
       <c r="E23" t="str">
-        <v>Client Proposal Showcase</v>
+        <v>Long-press haptic delete with shake animation confirm</v>
       </c>
       <c r="F23" t="str">
         <v>medium</v>
       </c>
       <c r="G23">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H23">
-        <v>9151</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
-        <v>Build a Client Proposal Showcase screen for a business mobile app where users can browse and present proposals to clients. Each proposal card should show the project title, client name, a status badge (draft/sent/approved), and a thumbnail preview. Tapping a card opens a full-screen detail view with a scrollable PDF-style layout. Include a top filter bar to sort by status or date, and a floating action button to create a new proposal.</v>
+        <v>[DRY-RUN] Long-press haptic delete with shake animation confirm — medium</v>
       </c>
       <c r="J23" t="str">
-        <v>做一个商业移动应用的客户提案展示页面，用户可以在这里浏览提案并向客户进行演示。每张提案卡片需要展示项目名称、客户姓名、状态标签（草稿/已发送/已审批）以及缩略图预览。点击卡片后进入全屏详情页，采用可滚动的类PDF排版样式。页面顶部需要有筛选栏，支持按状态或日期排序，同时提供一个悬浮操作按钮用于新建提案。</v>
-      </c>
-      <c r="K23" t="str">
         <v/>
       </c>
     </row>
@@ -1224,33 +1154,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>q_scene_004_005</v>
+        <v>q_scene_011_003</v>
       </c>
       <c r="C24" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D24" t="str">
-        <v>办公/商务类</v>
+        <v>Deleting &amp; Removing 删除与移除</v>
       </c>
       <c r="E24" t="str">
-        <v>Corporate Brand Identity Page</v>
+        <v>Drag item to trash zone removal interaction</v>
       </c>
       <c r="F24" t="str">
         <v>medium</v>
       </c>
       <c r="G24">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>8933</v>
+        <v>0</v>
       </c>
       <c r="I24" t="str">
-        <v>Build a Corporate Brand Identity page for the mobile app — it should display the company logo prominently at the top with a clean hero section, followed by brand color swatches with hex codes, typography samples showing the primary and secondary fonts, and a short brand voice/mission statement block. Keep the layout card-based and scrollable, with a sticky header showing the company name. The overall feel should be polished and professional, suitable for a business research or pitch context.</v>
+        <v>[DRY-RUN] Drag item to trash zone removal interaction — medium</v>
       </c>
       <c r="J24" t="str">
-        <v>做一个移动端的企业品牌识别页面——顶部要突出展示公司Logo，配一个简洁的hero区域，往下依次是带十六进制色值的品牌色板、展示主字体和辅助字体的字体样式示例，以及一段品牌调性／使命宣言的文字模块。整体布局采用卡片式设计，页面可滚动，顶部有吸顶导航栏显示公司名称。整体风格要精致、专业，适合用于商业调研或路演演示场景。</v>
-      </c>
-      <c r="K24" t="str">
         <v/>
       </c>
     </row>
@@ -1259,33 +1186,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>q_scene_004_006</v>
+        <v>q_scene_011_004</v>
       </c>
       <c r="C25" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D25" t="str">
-        <v>办公/商务类</v>
+        <v>Deleting &amp; Removing 删除与移除</v>
       </c>
       <c r="E25" t="str">
-        <v>Product Catalog Showcase</v>
+        <v>Remove from shared list with co-owner notification</v>
       </c>
       <c r="F25" t="str">
         <v>medium</v>
       </c>
       <c r="G25">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>11412</v>
+        <v>0</v>
       </c>
       <c r="I25" t="str">
-        <v>Build a product catalog showcase screen for a business mobile app — needs a grid layout with product cards showing thumbnail, product name, category tag, and a short description. Tapping a card should expand into a detail view with a larger image, full specs, and a "Save to Collection" button. Keep the overall aesthetic clean and professional, something suitable for B2B presentations.</v>
+        <v>[DRY-RUN] Remove from shared list with co-owner notification — medium</v>
       </c>
       <c r="J25" t="str">
-        <v>帮我做一个商业移动应用的产品目录展示页，用网格布局排列产品卡片，每张卡片要包含缩略图、产品名称、分类标签和简短描述。点击卡片后展开进入详情页，显示大图、完整规格参数，以及一个"加入收藏集"的按钮。整体风格要简洁、专业，适合 B2B 场景下的商务演示使用。</v>
-      </c>
-      <c r="K25" t="str">
         <v/>
       </c>
     </row>
@@ -1294,33 +1218,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>q_scene_004_007</v>
+        <v>q_scene_012_001</v>
       </c>
       <c r="C26" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D26" t="str">
-        <v>办公/商务类</v>
+        <v>Editing Profile 编辑个人资料</v>
       </c>
       <c r="E26" t="str">
-        <v>Investment Prospectus Reader</v>
+        <v>Location privacy level toggle (city / country / hidden)</v>
       </c>
       <c r="F26" t="str">
         <v>medium</v>
       </c>
       <c r="G26">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="H26">
-        <v>9437</v>
+        <v>0</v>
       </c>
       <c r="I26" t="str">
-        <v>Build a mobile screen for an Investment Prospectus Reader app — the main view should display a paginated PDF/document reader with a sticky header showing the company name, ticker, and filing date. Add a collapsible table of contents sidebar that lets users jump to sections like "Risk Factors", "Financials", and "Management". Include a bottom action bar with bookmark, highlight, and share buttons. Keep the UI clean and professional, dark mode preferred.</v>
+        <v>[DRY-RUN] Location privacy level toggle (city / country / hidden) — medium</v>
       </c>
       <c r="J26" t="str">
-        <v>做一个投资招股书阅读器应用的移动端页面——主视图展示分页式 PDF/文档阅读区，顶部有固定悬浮栏，显示公司名称、股票代码和申报日期。左侧加一个可折叠的目录侧边栏，方便用户快速跳转到"风险因素"、"财务数据"、"管理层"等章节。底部设置操作栏，包含书签、高亮和分享按钮。整体风格简洁专业，优先使用深色模式。</v>
-      </c>
-      <c r="K26" t="str">
         <v/>
       </c>
     </row>
@@ -1329,33 +1250,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>q_scene_004_008</v>
+        <v>q_scene_012_002</v>
       </c>
       <c r="C27" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D27" t="str">
-        <v>办公/商务类</v>
+        <v>Editing Profile 编辑个人资料</v>
       </c>
       <c r="E27" t="str">
-        <v>NGO Impact Report</v>
+        <v>Notification channel fine-grained preference control</v>
       </c>
       <c r="F27" t="str">
         <v>medium</v>
       </c>
       <c r="G27">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="H27">
-        <v>9506</v>
+        <v>0</v>
       </c>
       <c r="I27" t="str">
-        <v>Build a mobile screen for an NGO Impact Report viewer — it should have a scrollable summary card at the top showing key stats (beneficiaries reached, funds utilized, projects completed) with icon+number layout, followed by a sectioned list of program areas with expandable rows that reveal brief outcome descriptions. Keep the color palette clean and trustworthy (blues/greens), and make sure the stats cards support dynamic data so the numbers can be swapped out per report cycle.</v>
+        <v>[DRY-RUN] Notification channel fine-grained preference control — medium</v>
       </c>
       <c r="J27" t="str">
-        <v>帮我做一个手机端的 NGO 影响力报告查看页面——顶部要有一个可横向滚动的摘要卡片区，展示关键数据（受益人数、资金使用情况、已完成项目数），每项用图标加数字的形式排列；下方是按项目领域分组的列表，每行可以展开，展开后显示简短的成果说明。整体配色要干净、有信任感，用蓝色和绿色系。另外数据卡片里的数字要支持动态绑定，方便每个报告周期直接替换数据。</v>
-      </c>
-      <c r="K27" t="str">
         <v/>
       </c>
     </row>
@@ -1364,33 +1282,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>q_scene_004_009</v>
+        <v>q_scene_012_003</v>
       </c>
       <c r="C28" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D28" t="str">
-        <v>办公/商务类</v>
+        <v>Editing Profile 编辑个人资料</v>
       </c>
       <c r="E28" t="str">
-        <v>Real Estate Property Brochure</v>
+        <v>Account privacy switch (public / followers-only / private)</v>
       </c>
       <c r="F28" t="str">
         <v>medium</v>
       </c>
       <c r="G28">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="H28">
-        <v>10104</v>
+        <v>0</v>
       </c>
       <c r="I28" t="str">
-        <v>Build a mobile screen for a real estate property brochure viewer — it should display a hero image of the property at the top, followed by key stats (price, square footage, bedrooms/bathrooms) in a horizontal card row, then a scrollable section with property description and highlights. Include a sticky bottom bar with a "Schedule Viewing" CTA button and an agent contact card with avatar, name, and phone number. Keep the layout clean and professional, suited for a business/corporate feel.</v>
+        <v>[DRY-RUN] Account privacy switch (public / followers-only / private) — medium</v>
       </c>
       <c r="J28" t="str">
-        <v>做一个移动端的房产楼盘宣传册浏览页——顶部展示房产的全宽 hero 大图，下方用横向卡片行排列核心参数（价格、建筑面积、卧室/卫生间数量），再往下是可滚动的详情区域，包含房产描述和亮点介绍。底部设置一个固定栏，放置"预约看房" CTA 按钮，以及一张经纪人联系卡片，展示头像、姓名和电话号码。整体布局简洁大气，呈现商务/企业级的专业感。</v>
-      </c>
-      <c r="K28" t="str">
         <v/>
       </c>
     </row>
@@ -1399,33 +1314,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>q_scene_005_001</v>
+        <v>q_scene_012_004</v>
       </c>
       <c r="C29" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D29" t="str">
-        <v>文化/知识类</v>
+        <v>Editing Profile 编辑个人资料</v>
       </c>
       <c r="E29" t="str">
-        <v>Historical Figure Biography</v>
+        <v>Two-factor authentication setup with backup code download</v>
       </c>
       <c r="F29" t="str">
         <v>medium</v>
       </c>
       <c r="G29">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>8407</v>
+        <v>0</v>
       </c>
       <c r="I29" t="str">
-        <v>Build a Historical Figure Biography screen for the mobile app — it should have a hero section at the top with the figure's portrait, name, birth/death years, and a short one-liner tagline. Below that, use a tabbed layout with at least three tabs: Timeline, Key Contributions, and Influence &amp; Legacy. The Timeline tab should show a vertical scrollable list of dated events with brief descriptions. Keep the overall feel clean and editorial, dark background with off-white text, and make sure the portrait supports a fallback placeholder if no image is available.</v>
+        <v>[DRY-RUN] Two-factor authentication setup with backup code download — medium</v>
       </c>
       <c r="J29" t="str">
-        <v>为移动端 App 开发一个历史人物传记页面——顶部需要一个 hero 区域，展示人物肖像、姓名、生卒年份以及一句简短的人物简介标语。下方采用分 Tab 布局，至少包含三个标签页：时间轴、主要贡献、影响与遗产。时间轴标签页以垂直滚动列表的形式呈现各历史事件，每条事件带有日期和简要说明。整体风格要简洁、有格调，深色背景配米白色文字，人物肖像在无图片时需支持默认占位图降级处理。</v>
-      </c>
-      <c r="K29" t="str">
         <v/>
       </c>
     </row>
@@ -1434,33 +1346,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>q_scene_005_002</v>
+        <v>q_scene_013_001</v>
       </c>
       <c r="C30" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D30" t="str">
-        <v>文化/知识类</v>
+        <v>Uploading &amp; Downloading 上传与下载</v>
       </c>
       <c r="E30" t="str">
-        <v>Brand Heritage Story</v>
+        <v>Cloud storage import picker (Drive, Dropbox, iCloud)</v>
       </c>
       <c r="F30" t="str">
         <v>medium</v>
       </c>
       <c r="G30">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="H30">
-        <v>18297</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
-        <v>Build a "Brand Heritage Story" screen for a cultural research mobile app — it should have a vertical timeline layout showing key milestones in the brand's history, with each entry having a year label, a short title, and an expandable text block for deeper context. Add a hero image section at the top with the brand's founding era aesthetic, and make sure the timeline entries animate in as the user scrolls down. Keep the color palette muted and editorial-feeling, nothing too flashy.</v>
+        <v>[DRY-RUN] Cloud storage import picker (Drive, Dropbox, iCloud) — medium</v>
       </c>
       <c r="J30" t="str">
-        <v>为一款文化研究类移动应用开发"品牌历史故事"页面——采用纵向时间轴布局，展示品牌发展历程中的关键里程碑，每个节点包含年份标签、简短标题，以及可展开的详细说明文本块。页面顶部加一个英雄图区，视觉风格呼应品牌创立年代的历史质感，时间轴各节点在用户下滑时依次触发入场动画。整体配色保持低饱和度、偏编辑排版风格，不要过于张扬。</v>
-      </c>
-      <c r="K30" t="str">
         <v/>
       </c>
     </row>
@@ -1469,33 +1378,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>q_scene_005_003</v>
+        <v>q_scene_013_002</v>
       </c>
       <c r="C31" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D31" t="str">
-        <v>文化/知识类</v>
+        <v>Uploading &amp; Downloading 上传与下载</v>
       </c>
       <c r="E31" t="str">
-        <v>Scientific Discovery Timeline</v>
+        <v>URL-based remote file import with preview</v>
       </c>
       <c r="F31" t="str">
         <v>medium</v>
       </c>
       <c r="G31">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="H31">
-        <v>12761</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
-        <v>Build a Scientific Discovery Timeline screen for the mobile app — a vertically scrollable timeline where each node represents a major scientific breakthrough, showing the year, discovery name, and a short description. The nodes should alternate left/right like a classic zigzag timeline layout, and tapping a node should expand it inline to reveal more detail (scientist name, field, impact summary) without navigating away. Use a clean academic aesthetic — dark navy background, gold accent lines connecting the nodes, and subtle entrance animations as the user scrolls down.</v>
+        <v>[DRY-RUN] URL-based remote file import with preview — medium</v>
       </c>
       <c r="J31" t="str">
-        <v>做一个移动端的"科学发现时间轴"页面——整体竖向滚动，每个节点代表一项重大科学突破，显示年份、发现名称和简短描述。节点按照经典的左右交错锯齿形布局排列，点击某个节点后直接在原位展开，显示更多详情（科学家姓名、所属领域、影响摘要），不跳转新页面。视觉风格要有学术感——深海军蓝背景，金色线条连接各节点，页面向下滚动时节点带有轻柔的入场动画。</v>
-      </c>
-      <c r="K31" t="str">
         <v/>
       </c>
     </row>
@@ -1504,33 +1410,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>q_scene_005_004</v>
+        <v>q_scene_013_003</v>
       </c>
       <c r="C32" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D32" t="str">
-        <v>文化/知识类</v>
+        <v>Uploading &amp; Downloading 上传与下载</v>
       </c>
       <c r="E32" t="str">
-        <v>Cultural Festival Guide</v>
+        <v>Upload with auto-compress and quality selector preview</v>
       </c>
       <c r="F32" t="str">
         <v>medium</v>
       </c>
       <c r="G32">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>11010</v>
+        <v>0</v>
       </c>
       <c r="I32" t="str">
-        <v>Build a Cultural Festival Guide screen for a mobile app where users can browse upcoming cultural festivals filtered by region and month. Each festival card should show the festival name, country of origin, dates, a short description, and a cultural significance tag (like "religious", "harvest", "heritage"). Tapping a card expands it into a detail view with a timeline of key events during the festival, traditions explained in short paragraphs, and a "Save to Calendar" button. Keep the visual style rich but clean — use warm earth tones and subtle pattern backgrounds inspired by traditional textiles.</v>
+        <v>[DRY-RUN] Upload with auto-compress and quality selector preview — medium</v>
       </c>
       <c r="J32" t="str">
-        <v>做一个移动端的文化节庆指南页面，用户可以按地区和月份筛选浏览即将到来的文化节日。每张节日卡片需要展示节日名称、起源国家、日期、简短介绍，以及一个文化标签（比如"宗教"、"丰收"、"非遗"之类的）。点击卡片后展开进入详情页，里面要有一条节日期间重要活动的时间轴、用简短段落介绍的传统习俗，还有一个"添加到日历"按钮。整体风格要丰富但不杂乱——用暖土色调，搭配从传统织物纹样中提取灵感的微妙图案背景。</v>
-      </c>
-      <c r="K32" t="str">
         <v/>
       </c>
     </row>
@@ -1539,33 +1442,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>q_scene_005_005</v>
+        <v>q_scene_013_004</v>
       </c>
       <c r="C33" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D33" t="str">
-        <v>文化/知识类</v>
+        <v>Uploading &amp; Downloading 上传与下载</v>
       </c>
       <c r="E33" t="str">
-        <v>Literary Author Profile</v>
+        <v>Background upload continuing through device lock</v>
       </c>
       <c r="F33" t="str">
         <v>medium</v>
       </c>
       <c r="G33">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="H33">
-        <v>10678</v>
+        <v>0</v>
       </c>
       <c r="I33" t="str">
-        <v>Build a Literary Author Profile screen for a mobile research/culture app. The profile should include a hero section with the author's portrait, name, birth/death years, and nationality, followed by a scrollable body with sections for biography, major works (displayed as a horizontal card carousel with cover thumbnails), literary style tags, and notable quotes. Keep the visual tone editorial and minimal — think clean typography, muted colors, no flashy animations. The works carousel should support tap-to-expand showing a brief synopsis. Make sure the layout handles long biographies gracefully with a "read more" collapse toggle.</v>
+        <v>[DRY-RUN] Background upload continuing through device lock — medium</v>
       </c>
       <c r="J33" t="str">
-        <v>做一个移动端文化研究类应用的文学作家个人资料页。顶部要有一个主视觉区，展示作者肖像、姓名、生卒年份和国籍，下方是可滚动的正文区域，依次包含以下几个板块：作家生平简介、代表作品（以横向卡片轮播的形式呈现，每张卡片带封面缩略图）、文学风格标签，以及经典语录。整体视觉风格要偏编辑感、简洁克制——字体排版干净、配色低饱和度、不要花哨的动效。作品轮播支持点击展开，显示该作品的简短内容梗概。传记文字较长时要能优雅地处理，加一个"展开更多/收起"的折叠切换交互。</v>
-      </c>
-      <c r="K33" t="str">
         <v/>
       </c>
     </row>
@@ -1574,33 +1474,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>q_scene_005_006</v>
+        <v>q_scene_014_001</v>
       </c>
       <c r="C34" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D34" t="str">
-        <v>文化/知识类</v>
+        <v>Copying &amp; Duplicating 复制与副本</v>
       </c>
       <c r="E34" t="str">
-        <v>Space Exploration Chronicle</v>
+        <v>Share-to-app copy with format conversion selector</v>
       </c>
       <c r="F34" t="str">
         <v>medium</v>
       </c>
       <c r="G34">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="H34">
-        <v>71623</v>
+        <v>0</v>
       </c>
       <c r="I34" t="str">
-        <v>Build a timeline screen for the "Space Exploration Chronicle" app — it should display major space missions in a vertical scrollable timeline with each entry showing the mission name, launch year, agency logo, and a one-line summary. Tapping a card should expand it to reveal more details like mission objectives and outcome. Keep the visual style dark-themed with subtle star particle background, and make sure the timeline line itself has a glowing effect to feel immersive.</v>
+        <v>[DRY-RUN] Share-to-app copy with format conversion selector — medium</v>
       </c>
       <c r="J34" t="str">
-        <v>帮我做一个"太空探索编年史"应用的时间线页面——用垂直可滚动的时间轴展示重大太空任务，每条记录显示任务名称、发射年份、机构 logo 以及一句话简介。点击卡片后展开，显示任务目标和最终结果等详细信息。整体视觉风格要暗色主题，加上细腻的星粒子背景，时间轴连接线要有发光效果，营造出沉浸感。</v>
-      </c>
-      <c r="K34" t="str">
         <v/>
       </c>
     </row>
@@ -1609,33 +1506,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>q_scene_005_007</v>
+        <v>q_scene_014_002</v>
       </c>
       <c r="C35" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D35" t="str">
-        <v>文化/知识类</v>
+        <v>Copying &amp; Duplicating 复制与副本</v>
       </c>
       <c r="E35" t="str">
-        <v>Ancient Civilization Deep Dive</v>
+        <v>Copy rich-text with formatting fully preserved</v>
       </c>
       <c r="F35" t="str">
         <v>medium</v>
       </c>
       <c r="G35">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="H35">
-        <v>75086</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
-        <v>Build a mobile screen for an "Ancient Civilization Deep Dive" feature — it should have a horizontally scrollable civilization selector at the top (Egypt, Mesopotamia, Indus Valley, etc. as pill tabs with small icons), and below that a content area that switches between a Timeline view and an Artifacts Gallery view via a segmented toggle. The timeline should show dated events as vertical cards with a connecting line, and the artifacts gallery should be a 2-column masonry grid with tappable cards that expand into a detail modal. Keep the color palette dark and earthy — think deep ochre, sandstone, and dark charcoal backgrounds.</v>
+        <v>[DRY-RUN] Copy rich-text with formatting fully preserved — medium</v>
       </c>
       <c r="J35" t="str">
-        <v>做一个"古代文明深度探索"功能的移动端页面——顶部要有一个可横向滑动的文明选择器，把埃及、美索不达米亚、印度河流域等选项做成带小图标的胶囊标签；下面的内容区通过分段切换控件在"时间轴视图"和"文物图鉴视图"之间切换。时间轴部分用带连接线的竖向卡片展示各个历史事件和对应年代；文物图鉴部分做成两列瀑布流布局，卡片可点击，点击后展开一个详情弹窗。整体配色要暗沉、厚重，偏土系风格，主要用深赭石色、沙岩色和深炭灰色作为背景色调。</v>
-      </c>
-      <c r="K35" t="str">
         <v/>
       </c>
     </row>
@@ -1644,33 +1538,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>q_scene_005_008</v>
+        <v>q_scene_014_003</v>
       </c>
       <c r="C36" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D36" t="str">
-        <v>文化/知识类</v>
+        <v>Copying &amp; Duplicating 复制与副本</v>
       </c>
       <c r="E36" t="str">
-        <v>Documentary Companion Guide</v>
+        <v>Duplicate layer in design canvas with offset</v>
       </c>
       <c r="F36" t="str">
         <v>medium</v>
       </c>
       <c r="G36">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>73815</v>
+        <v>0</v>
       </c>
       <c r="I36" t="str">
-        <v>Build a Documentary Companion Guide screen for a mobile app — it should display alongside a documentary film and show timestamped context cards that appear as the film progresses. Each card needs a title, a short 2–3 sentence explanation, and optionally a "deep dive" expand button that opens a modal with sources or related reading. The layout should feel like a clean editorial guide, dark background with readable typography, and the cards should be scrollable in a side panel or bottom sheet without blocking the video area.</v>
+        <v>[DRY-RUN] Duplicate layer in design canvas with offset — medium</v>
       </c>
       <c r="J36" t="str">
-        <v>为一款移动端 App 构建一个纪录片随行导览页面——该页面需与纪录片同步显示，随着影片播放进度，依次呈现带有时间戳的上下文卡片。每张卡片包含一个标题、两到三句简短说明，以及一个可选的「深入了解」展开按钮，点击后弹出 modal 展示参考来源或相关延伸阅读。整体布局要有干净的编辑风格，深色背景配以易读的字体排版，卡片区域以侧边栏或底部抽屉的形式可滚动浏览，不得遮挡视频播放区域。</v>
-      </c>
-      <c r="K36" t="str">
         <v/>
       </c>
     </row>
@@ -1679,33 +1570,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>q_scene_005_009</v>
+        <v>q_scene_014_004</v>
       </c>
       <c r="C37" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="D37" t="str">
-        <v>文化/知识类</v>
+        <v>Copying &amp; Duplicating 复制与副本</v>
       </c>
       <c r="E37" t="str">
-        <v>Local Folklore Archive</v>
+        <v>Fork public template to personal workspace</v>
       </c>
       <c r="F37" t="str">
         <v>medium</v>
       </c>
       <c r="G37">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="H37">
-        <v>133262</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
-        <v>Build a Local Folklore Archive screen for a mobile research app — needs a browsable list of folklore entries grouped by region or category, with each card showing a title, a short excerpt, and a region tag. Tapping a card opens a detail view with the full story text, source attribution, and a related entries section at the bottom. The overall feel should be like a digital museum — clean but with some texture, maybe a slightly aged paper background or muted earthy tones. Filter by region should be accessible from the top of the list without taking up too much space.</v>
+        <v>[DRY-RUN] Fork public template to personal workspace — medium</v>
       </c>
       <c r="J37" t="str">
-        <v>为一款移动端研究类应用构建"本地民间传说档案"页面——需要一个可浏览的传说条目列表，按地区或分类分组展示，每张卡片显示标题、简短摘要和地区标签。点击卡片后进入详情页，展示完整故事正文、来源出处，以及底部的相关条目推荐区。整体风格要有数字博物馆的感觉——简洁但带点质感，可以考虑略带做旧感的纸张背景或低饱和度的大地色调。按地区筛选的入口放在列表顶部，但不能占用太多空间。</v>
-      </c>
-      <c r="K37" t="str">
         <v/>
       </c>
     </row>
@@ -1714,33 +1602,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>q_scene_006_001</v>
+        <v>q_scene_015_001</v>
       </c>
       <c r="C38" t="str">
         <v>交互方式</v>
       </c>
       <c r="D38" t="str">
-        <v>Adding &amp; Creating 新建与创建</v>
+        <v>Misc 其他</v>
       </c>
       <c r="E38" t="str">
-        <v>Recipe step-by-step creation wizard with ingredient input</v>
+        <v>Permission request dialog with contextual use-case explanation</v>
       </c>
       <c r="F38" t="str">
         <v>medium</v>
       </c>
       <c r="G38">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="H38">
-        <v>71367</v>
+        <v>0</v>
       </c>
       <c r="I38" t="str">
-        <v>Build a multi-step recipe creation wizard for mobile where users can add ingredients with quantity and unit fields in step one, then define cooking steps in order on step two — each step should support a short description and optional timer value. Include a progress indicator at the top showing which step they're on, and make sure users can go back and edit previous steps without losing data. The final screen should show a summary preview before submitting.</v>
+        <v>[DRY-RUN] Permission request dialog with contextual use-case explanation — medium</v>
       </c>
       <c r="J38" t="str">
-        <v>做一个移动端的多步骤食谱创建向导，第一步让用户添加食材，每种食材可以填写用量和单位；第二步按顺序填写烹饪步骤，每个步骤支持输入简短说明，并可选填一个计时时长。顶部需要有进度指示器显示当前处于哪一步，同时确保用户返回上一步修改时不会丢失已填写的数据。最后一屏在正式提交前展示一个完整的内容预览摘要。</v>
-      </c>
-      <c r="K38" t="str">
         <v/>
       </c>
     </row>
@@ -1749,33 +1634,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>q_scene_006_002</v>
+        <v>q_scene_015_002</v>
       </c>
       <c r="C39" t="str">
         <v>交互方式</v>
       </c>
       <c r="D39" t="str">
-        <v>Adding &amp; Creating 新建与创建</v>
+        <v>Misc 其他</v>
       </c>
       <c r="E39" t="str">
-        <v>Habit setup with frequency picker and smart reminder</v>
+        <v>Offline banner with queued-action list and sync on reconnect</v>
       </c>
       <c r="F39" t="str">
         <v>medium</v>
       </c>
       <c r="G39">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="H39">
-        <v>71258</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
-        <v>Build a habit creation screen where users can name a new habit, then pick frequency using a segmented control (daily / specific days / X times per week) — when "specific days" is selected, show a row of day toggles (Mon–Sun). Below that, add a smart reminder section that suggests a time based on the habit type (e.g., morning for "exercise", evening for "journal") but lets the user override it with a time picker. The confirm button should be disabled until both a name and at least one frequency option are set.</v>
+        <v>[DRY-RUN] Offline banner with queued-action list and sync on reconnect — medium</v>
       </c>
       <c r="J39" t="str">
-        <v>做一个新建习惯的页面，用户可以给习惯起名，然后通过分段控件选择频率（每天 / 指定日期 / 每周 X 次）——选中"指定日期"时，展示一排星期切换按钮（周一到周日）。下方加一个智能提醒模块，根据习惯类型自动推荐合适的时间（比如"运动"推荐早上，"写日记"推荐晚上），但允许用户通过时间选择器手动覆盖。确认按钮在用户填写习惯名称且至少选择一种频率之前保持禁用状态。</v>
-      </c>
-      <c r="K39" t="str">
         <v/>
       </c>
     </row>
@@ -1784,33 +1666,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>q_scene_006_003</v>
+        <v>q_scene_015_003</v>
       </c>
       <c r="C40" t="str">
         <v>交互方式</v>
       </c>
       <c r="D40" t="str">
-        <v>Adding &amp; Creating 新建与创建</v>
+        <v>Misc 其他</v>
       </c>
       <c r="E40" t="str">
-        <v>Journal entry composer with mood tagging and photo attach</v>
+        <v>Progressive content reveal during skeleton load</v>
       </c>
       <c r="F40" t="str">
         <v>medium</v>
       </c>
       <c r="G40">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="H40">
-        <v>8196</v>
+        <v>0</v>
       </c>
       <c r="I40" t="str">
-        <v>Build a journal entry composer screen for mobile where users can write freeform text, pick a mood from a horizontal scrollable row of emoji tags (like 😊 😔 😤 😴 etc.), and attach up to 4 photos from their camera roll shown as small thumbnails at the bottom. The composer should have a minimal, distraction-free look with a floating "Save" button that only activates once the text field has at least a few characters. Mood selection should highlight the chosen emoji with a soft colored background ring, and tapping an already-selected mood deselects it.</v>
+        <v>[DRY-RUN] Progressive content reveal during skeleton load — medium</v>
       </c>
       <c r="J40" t="str">
-        <v>做一个移动端的日记撰写页面，用户可以自由输入文字，在一排横向可左右滑动的 emoji 心情标签（比如 😊 😔 😤 😴 这些）里选择当前心情，还能从相册里选最多 4 张照片，以小缩略图的形式排在底部。整体风格要极简、沉浸感强，不要有多余的干扰元素，页面上有一个悬浮的"保存"按钮，只有当输入框里输入了一定字数之后才变成可点击状态。选中某个心情 emoji 时，该 emoji 周围要出现一圈柔和的彩色背景光晕来高亮显示，再次点击已选中的心情则取消选中。</v>
-      </c>
-      <c r="K40" t="str">
         <v/>
       </c>
     </row>
@@ -1819,33 +1698,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>q_scene_007_001</v>
+        <v>q_scene_015_004</v>
       </c>
       <c r="C41" t="str">
         <v>交互方式</v>
       </c>
       <c r="D41" t="str">
-        <v>Editing &amp; Updating 编辑与更新</v>
+        <v>Misc 其他</v>
       </c>
       <c r="E41" t="str">
-        <v>Inline text field edit with auto-save and change indicator</v>
+        <v>Destructive action confirm dialog with countdown</v>
       </c>
       <c r="F41" t="str">
         <v>medium</v>
       </c>
       <c r="G41">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="H41">
-        <v>8468</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
-        <v>Build an inline text field component for a mobile app where tapping a label switches it to an editable input in place — no separate edit screen. It should auto-save after a short debounce (like 800ms after the user stops typing) and show a subtle visual indicator (a small dot or icon next to the field) while the save is pending, then switch to a checkmark or green state once saved. If the save fails, show an error state on that indicator without disrupting the rest of the UI.</v>
+        <v>[DRY-RUN] Destructive action confirm dialog with countdown — medium</v>
       </c>
       <c r="J41" t="str">
-        <v>做一个移动端的行内文本编辑组件，点击标签文字后直接在原位切换成可编辑输入框，不跳转到单独的编辑页面。用户停止输入约800毫秒后自动触发保存，保存等待期间在字段旁边显示一个小圆点或图标作为提示，保存成功后切换成对勾或变成绿色状态。如果保存失败，就在那个指示图标上展示错误状态，不影响页面其他部分的正常显示。</v>
-      </c>
-      <c r="K41" t="str">
         <v/>
       </c>
     </row>
@@ -1854,33 +1730,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>q_scene_007_002</v>
+        <v>q_scene_016_001</v>
       </c>
       <c r="C42" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D42" t="str">
-        <v>Editing &amp; Updating 编辑与更新</v>
+        <v>计算器/换算器 ★</v>
       </c>
       <c r="E42" t="str">
-        <v>Profile photo crop, filter and retake before confirm</v>
+        <v>Percentage and discount price calculator</v>
       </c>
       <c r="F42" t="str">
         <v>medium</v>
       </c>
       <c r="G42">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="H42">
-        <v>10372</v>
+        <v>0</v>
       </c>
       <c r="I42" t="str">
-        <v>Build a profile photo editing flow where after the user picks or captures a photo, they land on a screen with three tabs — crop, filter, and retake — before hitting confirm. The crop tab should support free and circle crop modes with pinch-to-zoom. The filter tab needs at least a few preset options shown as thumbnail previews. Retake should relaunch the camera without losing the current edits until they choose a new photo. Confirm button stays fixed at the bottom and only activates once a crop or filter action has been applied.</v>
+        <v>[DRY-RUN] Percentage and discount price calculator — medium</v>
       </c>
       <c r="J42" t="str">
-        <v>做一个头像编辑流程：用户选择或拍摄照片后，进入一个带三个标签页的编辑界面——裁剪、滤镜和重拍，确认前需在这里完成操作。裁剪标签页要支持自由裁剪和圆形裁剪两种模式，并支持双指捏合缩放。滤镜标签页至少提供几种预设风格，每种以缩略图形式展示供预览。点击重拍时重新调起相机，但在用户选好新照片之前，当前的编辑内容不要丢失。确认按钮固定在页面底部，只有当用户实际执行过裁剪或滤镜操作后才变为可点击状态。</v>
-      </c>
-      <c r="K42" t="str">
         <v/>
       </c>
     </row>
@@ -1889,33 +1762,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>q_scene_007_003</v>
+        <v>q_scene_016_002</v>
       </c>
       <c r="C43" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D43" t="str">
-        <v>Editing &amp; Updating 编辑与更新</v>
+        <v>计算器/换算器 ★</v>
       </c>
       <c r="E43" t="str">
-        <v>Batch task status update via multi-select and action bar</v>
+        <v>Age calculator from birth date with zodiac</v>
       </c>
       <c r="F43" t="str">
         <v>medium</v>
       </c>
       <c r="G43">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="H43">
-        <v>11337</v>
+        <v>0</v>
       </c>
       <c r="I43" t="str">
-        <v>Build a batch task status update flow for the mobile task list screen — long-pressing a task item should trigger multi-select mode, showing checkboxes on each row and a floating action bar at the bottom. The action bar needs at least three status options (e.g. Mark Complete, Mark In Progress, Archive) that apply to all selected items at once. Make sure the action bar disappears and checkboxes clear when the selection is empty or the user taps cancel.</v>
+        <v>[DRY-RUN] Age calculator from birth date with zodiac — medium</v>
       </c>
       <c r="J43" t="str">
-        <v>在移动端任务列表页面做一个批量更新任务状态的交互流程——长按任务条目时触发多选模式，每行显示复选框，底部出现一个浮动操作栏。操作栏里至少要有三个状态选项（比如标记为已完成、标记为进行中、归档），可以一次性应用到所有选中的条目上。另外要确保当没有选中任何条目或用户点击取消时，操作栏自动收起，复选框也随之清除。</v>
-      </c>
-      <c r="K43" t="str">
         <v/>
       </c>
     </row>
@@ -1924,33 +1794,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>q_scene_008_001</v>
+        <v>q_scene_016_003</v>
       </c>
       <c r="C44" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D44" t="str">
-        <v>Searching &amp; Finding 搜索与查找</v>
+        <v>计算器/换算器 ★</v>
       </c>
       <c r="E44" t="str">
-        <v>Global keyword search with real-time animated suggestions</v>
+        <v>Time zone difference calculator with world clock</v>
       </c>
       <c r="F44" t="str">
         <v>medium</v>
       </c>
       <c r="G44">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="H44">
-        <v>11613</v>
+        <v>0</v>
       </c>
       <c r="I44" t="str">
-        <v>Build a global keyword search bar for the app that shows real-time animated suggestions as the user types — the suggestions should slide in from below with a subtle fade, and each item should stagger in with a small delay so it doesn't feel like a sudden dump of results. The search should scan across multiple sections (products, users, articles) and group results by category with a small label. Debounce the input so it's not firing on every keystroke, and highlight the matched keyword portion in each suggestion row.</v>
+        <v>[DRY-RUN] Time zone difference calculator with world clock — medium</v>
       </c>
       <c r="J44" t="str">
-        <v>帮我给这个应用做一个全局关键词搜索框，用户输入的时候要实时显示动态建议列表——每条建议从下方滑入并带有淡入效果，而且各条目要错开一点时间依次出现，不要一下子全堆出来显得很突兀。搜索范围要覆盖多个模块（商品、用户、文章），结果按类别分组并带小标签区分。输入要做防抖处理，不要每敲一个字就触发请求，另外每条建议里匹配到的关键词部分需要高亮显示。</v>
-      </c>
-      <c r="K44" t="str">
         <v/>
       </c>
     </row>
@@ -1959,33 +1826,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>q_scene_008_002</v>
+        <v>q_scene_016_004</v>
       </c>
       <c r="C45" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D45" t="str">
-        <v>Searching &amp; Finding 搜索与查找</v>
+        <v>计算器/换算器 ★</v>
       </c>
       <c r="E45" t="str">
-        <v>Voice search with live speech-to-text transcript display</v>
+        <v>Calorie burn estimator by activity and body weight</v>
       </c>
       <c r="F45" t="str">
         <v>medium</v>
       </c>
       <c r="G45">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="H45">
-        <v>8639</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
-        <v>Build a voice search screen for a mobile app where tapping the mic button starts recording and shows a live speech-to-text transcript in real time as the user speaks — the transcript text should animate in word by word and be editable before the user submits the search. Include a pulsing waveform animation while recording is active, and a clear visual state difference between idle, listening, and processing states.</v>
+        <v>[DRY-RUN] Calorie burn estimator by activity and body weight — medium</v>
       </c>
       <c r="J45" t="str">
-        <v>做一个移动端的语音搜索页面，点击麦克风按钮后开始录音，并实时显示语音转文字的内容——文字要逐词动态出现，用户说话时同步渲染，提交搜索前还可以手动编辑转录结果。录音过程中需要有脉冲式的波形动画，同时要明确区分三种视觉状态：待机、聆听中和处理中，每个状态的界面表现要有明显差异。</v>
-      </c>
-      <c r="K45" t="str">
         <v/>
       </c>
     </row>
@@ -1994,33 +1858,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>q_scene_008_003</v>
+        <v>q_scene_016_005</v>
       </c>
       <c r="C46" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D46" t="str">
-        <v>Searching &amp; Finding 搜索与查找</v>
+        <v>计算器/换算器 ★</v>
       </c>
       <c r="E46" t="str">
-        <v>Image reverse search from camera or gallery photo</v>
+        <v>Fabric yardage calculator for sewing projects</v>
       </c>
       <c r="F46" t="str">
         <v>medium</v>
       </c>
       <c r="G46">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="H46">
-        <v>8628</v>
+        <v>0</v>
       </c>
       <c r="I46" t="str">
-        <v>Build a reverse image search screen where users can either take a photo with the camera or pick one from their gallery — after selecting, the image gets uploaded and results show up in a scrollable grid with matched items and similarity scores. The bottom sheet or modal for choosing between camera and gallery should animate smoothly, and the results screen needs a loading skeleton while the search is in progress.</v>
+        <v>[DRY-RUN] Fabric yardage calculator for sewing projects — medium</v>
       </c>
       <c r="J46" t="str">
-        <v>做一个以图搜图的页面，用户可以选择拍照或者从相册里挑图——选好图片后自动上传，搜索结果以可滚动的网格展示，每条匹配项都带有相似度评分。用来选择拍照还是从相册取图的 bottom sheet 或弹窗需要有流畅的弹出动画，结果页在搜索进行时要展示加载骨架屏。</v>
-      </c>
-      <c r="K46" t="str">
         <v/>
       </c>
     </row>
@@ -2029,33 +1890,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>q_scene_009_001</v>
+        <v>q_scene_017_001</v>
       </c>
       <c r="C47" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D47" t="str">
-        <v>Selecting &amp; Choosing 选择与选取</v>
+        <v>生活记录器 ★</v>
       </c>
       <c r="E47" t="str">
-        <v>Single-item radio selection with expanded detail preview</v>
+        <v>Dream diary with tag and emotional sentiment</v>
       </c>
       <c r="F47" t="str">
         <v>medium</v>
       </c>
       <c r="G47">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="H47">
-        <v>10484</v>
+        <v>0</v>
       </c>
       <c r="I47" t="str">
-        <v>Build a single-select radio list where tapping an option not only marks it as selected but also expands an inline detail panel beneath it — showing a short description and maybe a 2–3 line spec summary. Only one item can be expanded and selected at a time, so selecting a new one should collapse the previous detail panel with a smooth animation. The list items should have a clear visual distinction between default, selected, and expanded states.</v>
+        <v>[DRY-RUN] Dream diary with tag and emotional sentiment — medium</v>
       </c>
       <c r="J47" t="str">
-        <v>做一个单选列表，点击某个选项时，不仅要将其标记为选中状态，还要在它下方展开一个内联详情面板，面板里显示简短的描述文字以及两三行规格说明。同一时间只能有一个选项处于展开并选中的状态，选择新选项时，之前的详情面板要以流畅的动画收起。列表项在默认、选中、展开三种状态下需要有清晰明显的视觉区分。</v>
-      </c>
-      <c r="K47" t="str">
         <v/>
       </c>
     </row>
@@ -2064,33 +1922,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>q_scene_009_002</v>
+        <v>q_scene_017_002</v>
       </c>
       <c r="C48" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D48" t="str">
-        <v>Selecting &amp; Choosing 选择与选取</v>
+        <v>生活记录器 ★</v>
       </c>
       <c r="E48" t="str">
-        <v>Multi-item checkbox selection with floating bulk action bar</v>
+        <v>Period and cycle symptom recorder</v>
       </c>
       <c r="F48" t="str">
         <v>medium</v>
       </c>
       <c r="G48">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="H48">
-        <v>8546</v>
+        <v>0</v>
       </c>
       <c r="I48" t="str">
-        <v>Build a multi-item checkbox selection flow for a mobile list view — when the user long-presses any item it enters selection mode, showing checkboxes on each row. As items get checked, a floating action bar animates up from the bottom with a count badge (e.g. "3 selected") and action buttons like Delete and Move. The bar should dismiss smoothly when all items are deselected or the user taps Cancel, and there should be a Select All toggle at the top. Keep the checkboxes visually consistent with the rest of the list and make sure the floating bar doesn't obscure the last list item.</v>
+        <v>[DRY-RUN] Period and cycle symptom recorder — medium</v>
       </c>
       <c r="J48" t="str">
-        <v>做一个移动端列表的多选操作流程——用户长按任意列表项后进入选择模式，每一行显示复选框。随着用户勾选条目，底部会有一个浮动操作栏从下方动画滑出，显示已选数量角标（比如"已选 3 项"）以及删除、移动等操作按钮。当所有条目取消勾选或用户点击取消时，操作栏要平滑收起消失。列表顶部需要有一个全选切换按钮。复选框的视觉风格要和列表整体保持一致，同时要确保浮动操作栏不会遮挡最后一条列表项。</v>
-      </c>
-      <c r="K48" t="str">
         <v/>
       </c>
     </row>
@@ -2099,33 +1954,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>q_scene_009_003</v>
+        <v>q_scene_017_003</v>
       </c>
       <c r="C49" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D49" t="str">
-        <v>Selecting &amp; Choosing 选择与选取</v>
+        <v>生活记录器 ★</v>
       </c>
       <c r="E49" t="str">
-        <v>Swipe-right to select item in list card view</v>
+        <v>Baby feeding and diaper change log</v>
       </c>
       <c r="F49" t="str">
         <v>medium</v>
       </c>
       <c r="G49">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="H49">
-        <v>9118</v>
+        <v>0</v>
       </c>
       <c r="I49" t="str">
-        <v>Implement swipe-right-to-select on list cards — each card in the feed should reveal a green checkmark indicator as the user swipes right past a threshold (~40% of card width), and releasing after that threshold marks the item as selected with a subtle bounce animation. Selected cards should show a persistent teal left border and a small checkbox icon in the top-right corner. Make sure multi-select works so users can swipe-select several items before hitting a bottom action bar that appears once at least one item is selected.</v>
+        <v>[DRY-RUN] Baby feeding and diaper change log — medium</v>
       </c>
       <c r="J49" t="str">
-        <v>实现列表卡片的右滑选择功能——信息流中的每张卡片，当用户向右滑动超过一定阈值（约卡片宽度的 40%）时，应出现一个绿色勾选指示图标；松手后若已超过该阈值，则将该条目标记为已选中，并触发一个轻微的弹跳动画。已选中的卡片需要持续显示青色左边框，并在右上角展示一个小复选框图标。请确保支持多选，用户可以依次右滑选中多张卡片，只要有至少一项被选中，底部操作栏就自动浮现。</v>
-      </c>
-      <c r="K49" t="str">
         <v/>
       </c>
     </row>
@@ -2134,33 +1986,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>q_scene_010_001</v>
+        <v>q_scene_017_004</v>
       </c>
       <c r="C50" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D50" t="str">
-        <v>Filtering &amp; Sorting 筛选与排序</v>
+        <v>生活记录器 ★</v>
       </c>
       <c r="E50" t="str">
-        <v>Faceted filter panel with collapsible category groups</v>
+        <v>Pet behavior and health note logger</v>
       </c>
       <c r="F50" t="str">
         <v>medium</v>
       </c>
       <c r="G50">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="H50">
-        <v>8751</v>
+        <v>0</v>
       </c>
       <c r="I50" t="str">
-        <v>Build a faceted filter panel for a mobile app where each filter category (like Price Range, Brand, Rating, Color) is a collapsible group — tapping the header expands/collapses the options underneath with a smooth animation. Each group should show a badge count when filters are selected inside it, and there should be a global "Clear All" button plus per-group reset. Keep the panel as a bottom sheet that can be partially or fully expanded, and make sure selected filter chips are visually distinct from unselected ones.</v>
+        <v>[DRY-RUN] Pet behavior and health note logger — medium</v>
       </c>
       <c r="J50" t="str">
-        <v>做一个移动端的多维筛选面板，每个筛选类别（比如价格区间、品牌、评分、颜色）都是可折叠的分组——点击分组标题能展开或收起下方的选项，要有流畅的动画过渡。某个分组内有已选项时，分组标题上需要显示已选数量的角标；同时要有一个全局的"清除全部"按钮，以及每个分组各自的重置入口。整个面板以 bottom sheet 形式呈现，支持半展开和完全展开两种状态，已选中的筛选标签在样式上要和未选中的有明显区别。</v>
-      </c>
-      <c r="K50" t="str">
         <v/>
       </c>
     </row>
@@ -2169,33 +2018,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>q_scene_010_002</v>
+        <v>q_scene_017_005</v>
       </c>
       <c r="C51" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D51" t="str">
-        <v>Filtering &amp; Sorting 筛选与排序</v>
+        <v>生活记录器 ★</v>
       </c>
       <c r="E51" t="str">
-        <v>Active filter chips with one-tap remove and clear-all</v>
+        <v>Plant watering and care event log</v>
       </c>
       <c r="F51" t="str">
         <v>medium</v>
       </c>
       <c r="G51">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="H51">
-        <v>8798</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
-        <v>Build a row of active filter chips for a mobile filtering screen — each chip shows the selected filter label with an "×" icon on the right for one-tap removal. When there are 2 or more active filters, show a "Clear All" button at the end of the row. The chip row should scroll horizontally if it overflows. Removing the last chip should hide the entire row. Use a compact pill style with a tinted background to distinguish them from inactive filter buttons.</v>
+        <v>[DRY-RUN] Plant watering and care event log — medium</v>
       </c>
       <c r="J51" t="str">
-        <v>做一个移动端筛选页面的已选筛选条件标签栏——每个标签显示当前选中的筛选项名称，右侧带有"×"图标，点击即可移除该条件。当同时存在 2 个及以上的已选条件时，在标签栏末尾显示一个"清除全部"按钮。标签栏内容超出屏幕宽度时支持横向滚动。移除最后一个标签后，整个标签栏自动隐藏。样式采用紧凑的胶囊形态，搭配有色背景填充，以便与未选中的筛选按钮在视觉上区分开来。</v>
-      </c>
-      <c r="K51" t="str">
         <v/>
       </c>
     </row>
@@ -2204,33 +2050,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>q_scene_010_003</v>
+        <v>q_scene_018_001</v>
       </c>
       <c r="C52" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D52" t="str">
-        <v>Filtering &amp; Sorting 筛选与排序</v>
+        <v>社交辅助 ★</v>
       </c>
       <c r="E52" t="str">
-        <v>Date range picker filter with calendar visual span</v>
+        <v>Gift idea suggester by recipient personality type</v>
       </c>
       <c r="F52" t="str">
         <v>medium</v>
       </c>
       <c r="G52">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="H52">
-        <v>9121</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
-        <v>Build a date range picker filter for a mobile app where users can tap a start date and end date on a calendar view, and the selected span gets visually highlighted between the two dates — like a colored fill across the days in between. The calendar should stay visible while selecting (no auto-dismiss after first tap), and the selected range should show the start/end markers plus the filled span clearly. Should work as a filter panel that can be applied or reset.</v>
+        <v>[DRY-RUN] Gift idea suggester by recipient personality type — medium</v>
       </c>
       <c r="J52" t="str">
-        <v>做一个移动端用的日期区间选择器，用户可以在日历视图上分别点选开始日期和结束日期，两个日期之间的区间要有视觉高亮效果，比如用填充色覆盖中间的每一天。点选第一个日期后日历不能自动关闭，要保持展开状态让用户继续选结束日期。选好之后要能清楚地看到起止两端的标记以及中间的填充区间。整体作为一个筛选面板来使用，支持应用筛选和重置操作。</v>
-      </c>
-      <c r="K52" t="str">
         <v/>
       </c>
     </row>
@@ -2239,33 +2082,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>q_scene_011_001</v>
+        <v>q_scene_018_002</v>
       </c>
       <c r="C53" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D53" t="str">
-        <v>Deleting &amp; Removing 删除与移除</v>
+        <v>社交辅助 ★</v>
       </c>
       <c r="E53" t="str">
-        <v>Swipe-left delete with immediate undo snackbar</v>
+        <v>Debate argument and counterpoint idea generator</v>
       </c>
       <c r="F53" t="str">
         <v>medium</v>
       </c>
       <c r="G53">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="H53">
-        <v>9350</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
-        <v>Implement swipe-left-to-delete on list items where swiping reveals a red delete background with a trash icon, and once the swipe completes the item is removed from the list immediately — but a snackbar pops up at the bottom with an "Undo" button that stays visible for about 4 seconds. If the user taps Undo, the item snaps back into the list at its original position. The snackbar should auto-dismiss after the timeout and only then should the actual delete call go to the backend. Make sure simultaneous swipes on multiple items are handled cleanly.</v>
+        <v>[DRY-RUN] Debate argument and counterpoint idea generator — medium</v>
       </c>
       <c r="J53" t="str">
-        <v>在列表项上实现左滑删除功能：左滑时露出红色删除背景并显示垃圾桶图标，滑动完成后该条目立即从列表中移除——同时底部弹出一个带有"撤销"按钮的 snackbar，持续显示约 4 秒。如果用户点击撤销，该条目需要原位复原回列表中。snackbar 超时自动消失后，才真正向后端发起删除请求。另外要确保同时对多个列表项进行左滑操作时，各项状态互不干扰、处理逻辑干净清晰。</v>
-      </c>
-      <c r="K53" t="str">
         <v/>
       </c>
     </row>
@@ -2274,33 +2114,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>q_scene_011_002</v>
+        <v>q_scene_018_003</v>
       </c>
       <c r="C54" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D54" t="str">
-        <v>Deleting &amp; Removing 删除与移除</v>
+        <v>社交辅助 ★</v>
       </c>
       <c r="E54" t="str">
-        <v>Bulk delete via multi-select with two-step confirm dialog</v>
+        <v>Party game activity selector and rule displayer</v>
       </c>
       <c r="F54" t="str">
         <v>medium</v>
       </c>
       <c r="G54">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="H54">
-        <v>10526</v>
+        <v>0</v>
       </c>
       <c r="I54" t="str">
-        <v>Build a bulk delete flow for a mobile list screen — users can tap a "Select" button to enter multi-select mode, where each list item shows a checkbox. Once at least one item is checked, a "Delete" button appears in the bottom action bar. Tapping it opens a first confirm dialog ("Delete X items?") and only after confirming that does a second dialog appear as a final warning ("This can't be undone — proceed?"). Both dialogs should have Cancel and Confirm actions, and the whole multi-select mode should exit cleanly after deletion is complete.</v>
+        <v>[DRY-RUN] Party game activity selector and rule displayer — medium</v>
       </c>
       <c r="J54" t="str">
-        <v>帮我做一个移动端列表页的批量删除功能——用户点击"选择"按钮后进入多选模式，每个列表项左侧显示复选框。只要勾选了至少一项，底部操作栏就出现"删除"按钮。点击删除后先弹出第一个确认弹窗（"确定删除 X 项？"），用户确认后再弹出第二个最终警告弹窗（"删除后无法恢复，确定继续吗？"）。两个弹窗都要有取消和确认两个操作按钮，删除完成后多选模式要干净地自动退出。</v>
-      </c>
-      <c r="K54" t="str">
         <v/>
       </c>
     </row>
@@ -2309,33 +2146,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>q_scene_011_003</v>
+        <v>q_scene_018_004</v>
       </c>
       <c r="C55" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D55" t="str">
-        <v>Deleting &amp; Removing 删除与移除</v>
+        <v>社交辅助 ★</v>
       </c>
       <c r="E55" t="str">
-        <v>Archive instead of delete with one-tap restore</v>
+        <v>Social story generator for neurodivergent support</v>
       </c>
       <c r="F55" t="str">
         <v>medium</v>
       </c>
       <c r="G55">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="H55">
-        <v>21080</v>
+        <v>0</v>
       </c>
       <c r="I55" t="str">
-        <v>Build an archive-instead-of-delete flow for list items — when a user swipes to remove something, it should go to an archived state rather than being permanently deleted. Show a brief bottom toast or snackbar with a "Restore" button that stays visible for about 4–5 seconds, letting them undo with one tap. Archived items should also be accessible from a dedicated "Archived" section in settings or a menu so nothing is ever truly lost.</v>
+        <v>[DRY-RUN] Social story generator for neurodivergent support — medium</v>
       </c>
       <c r="J55" t="str">
-        <v>给列表条目做一个"归档代替删除"的交互流程——用户滑动移除某项时，该条目应进入归档状态，而不是被永久删除。同时在底部弹出一个简短的 toast 或 snackbar，带有"恢复"按钮，持续显示约 4–5 秒，让用户可以一键撤销。归档的条目还应该可以通过设置页面或菜单里专门的"已归档"入口访问，确保任何内容都不会真正丢失。</v>
-      </c>
-      <c r="K55" t="str">
         <v/>
       </c>
     </row>
@@ -2344,33 +2178,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>q_scene_012_001</v>
+        <v>q_scene_018_005</v>
       </c>
       <c r="C56" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D56" t="str">
-        <v>Editing Profile 编辑个人资料</v>
+        <v>社交辅助 ★</v>
       </c>
       <c r="E56" t="str">
-        <v>Display name and username change with real-time availability check</v>
+        <v>Conflict resolution communication phrase guide</v>
       </c>
       <c r="F56" t="str">
         <v>medium</v>
       </c>
       <c r="G56">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="H56">
-        <v>21195</v>
+        <v>0</v>
       </c>
       <c r="I56" t="str">
-        <v>Build the edit profile screen's display name and username fields with real-time availability checking — as the user types their username, debounce the API call by ~500ms and show an inline status indicator (green checkmark if available, red X with a short message if taken or invalid). Display name should just validate length (max 50 chars) with a live character counter. Both fields should have clear/reset icons and save should be disabled until at least one field is changed and all validations pass.</v>
+        <v>[DRY-RUN] Conflict resolution communication phrase guide — medium</v>
       </c>
       <c r="J56" t="str">
-        <v>做一下编辑个人资料页面里的昵称和用户名输入框，需要支持实时可用性检测——用户输入用户名时，对接口请求做约 500ms 的防抖处理，然后在输入框旁边展示行内状态提示（可用时显示绿色对勾，已被占用或格式不合法时显示红色叉并附上一段简短的提示文案）。昵称字段只需做长度校验，上限 50 个字符，配一个实时字符计数器。两个输入框都要有清空/重置图标，保存按钮在至少有一个字段被修改、且所有校验全部通过之前保持禁用状态。</v>
-      </c>
-      <c r="K56" t="str">
         <v/>
       </c>
     </row>
@@ -2379,33 +2210,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>q_scene_012_002</v>
+        <v>q_scene_019_001</v>
       </c>
       <c r="C57" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D57" t="str">
-        <v>Editing Profile 编辑个人资料</v>
+        <v>倒计时/纪念日</v>
       </c>
       <c r="E57" t="str">
-        <v>Profile photo upload with crop, filter and retake options</v>
+        <v>Vacation departure countdown with packing reminder</v>
       </c>
       <c r="F57" t="str">
         <v>medium</v>
       </c>
       <c r="G57">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="H57">
-        <v>20412</v>
+        <v>0</v>
       </c>
       <c r="I57" t="str">
-        <v>Build a profile photo upload flow for the Edit Profile screen — when the user taps their avatar, open a bottom sheet with options to choose from gallery or take a new photo. After selecting, show a crop screen with a circular mask and free-drag/pinch-to-zoom support. Then transition to a filter step with at least 4 preset filter thumbnails the user can preview in real time before confirming. Also include a "Retake" button on both the crop and filter screens that goes back to the source picker without losing the modal state.</v>
+        <v>[DRY-RUN] Vacation departure countdown with packing reminder — medium</v>
       </c>
       <c r="J57" t="str">
-        <v>在"编辑个人资料"页面实现一个头像上传流程——用户点击头像后，从底部弹出操作面板，提供"从相册选择"和"拍摄新照片"两个入口。选择图片后进入裁剪页面，带圆形裁剪蒙版，支持自由拖拽和双指捏合缩放。裁剪完成后跳转到滤镜步骤，至少要有4个预设滤镜缩略图，用户可以实时预览效果后再点击确认。裁剪页和滤镜页都要有一个"重拍"按钮，点击后返回来源选择面板，并且不能丢失当前弹窗的状态。</v>
-      </c>
-      <c r="K57" t="str">
         <v/>
       </c>
     </row>
@@ -2414,33 +2242,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>q_scene_012_003</v>
+        <v>q_scene_019_002</v>
       </c>
       <c r="C58" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D58" t="str">
-        <v>Editing Profile 编辑个人资料</v>
+        <v>倒计时/纪念日</v>
       </c>
       <c r="E58" t="str">
-        <v>Bio text editor with character count and formatting</v>
+        <v>Anniversary date display with years-together count</v>
       </c>
       <c r="F58" t="str">
         <v>medium</v>
       </c>
       <c r="G58">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="H58">
-        <v>17926</v>
+        <v>0</v>
       </c>
       <c r="I58" t="str">
-        <v>Build a bio text editor component for the Edit Profile screen — it should have a multiline text input that supports basic inline formatting (bold, italic, maybe a link option via a small toolbar above the keyboard), plus a live character counter showing something like "87 / 150" that turns red when the user gets close to the limit. The input should auto-expand vertically as the user types but cap at around 5 lines before scrolling internally.</v>
+        <v>[DRY-RUN] Anniversary date display with years-together count — medium</v>
       </c>
       <c r="J58" t="str">
-        <v>帮我在"编辑个人资料"页面做一个个人简介文本编辑器组件——需要一个多行输入框，支持基本的行内格式化操作（加粗、斜体，最好还能通过键盘上方的小工具栏插入链接），同时要有一个实时字符计数器，显示类似"87 / 150"这样的格式，当用户快接近字数上限时自动变红。输入框要能随着输入内容自动向下撑开，但最多展示大约5行，超出后在内部滚动。</v>
-      </c>
-      <c r="K58" t="str">
         <v/>
       </c>
     </row>
@@ -2449,33 +2274,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>q_scene_013_001</v>
+        <v>q_scene_019_003</v>
       </c>
       <c r="C59" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D59" t="str">
-        <v>Uploading &amp; Downloading 上传与下载</v>
+        <v>倒计时/纪念日</v>
       </c>
       <c r="E59" t="str">
-        <v>Single file pick with upload progress ring and cancel</v>
+        <v>Memorial and tribute date annual reminder</v>
       </c>
       <c r="F59" t="str">
         <v>medium</v>
       </c>
       <c r="G59">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H59">
-        <v>37024</v>
+        <v>0</v>
       </c>
       <c r="I59" t="str">
-        <v>Build a single file picker component for mobile where after the user selects a file, a circular progress ring animates around a file icon to show upload progress (0–100%), and there's a visible cancel button that stops the upload and resets the UI back to the initial pick state. The ring should update smoothly in real time and the cancel should abort any in-flight request, not just hide the UI.</v>
+        <v>[DRY-RUN] Memorial and tribute date annual reminder — medium</v>
       </c>
       <c r="J59" t="str">
-        <v>做一个移动端的单文件选择组件，用户选中文件后，文件图标周围出现一个圆形进度环动画，实时展示上传进度（0–100%），同时有一个显眼的取消按钮，点击后能中止上传并将界面重置回最初的选择状态。进度环要平滑地实时更新，取消操作必须真正终止正在进行中的请求，而不只是把界面隐藏掉。</v>
-      </c>
-      <c r="K59" t="str">
         <v/>
       </c>
     </row>
@@ -2484,33 +2306,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>q_scene_013_002</v>
+        <v>q_scene_019_004</v>
       </c>
       <c r="C60" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D60" t="str">
-        <v>Uploading &amp; Downloading 上传与下载</v>
+        <v>倒计时/纪念日</v>
       </c>
       <c r="E60" t="str">
-        <v>Multi-file batch upload queue with per-file status</v>
+        <v>Sobriety and clean-living streak day counter</v>
       </c>
       <c r="F60" t="str">
         <v>medium</v>
       </c>
       <c r="G60">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="H60">
-        <v>8976</v>
+        <v>0</v>
       </c>
       <c r="I60" t="str">
-        <v>Build a multi-file batch upload queue component for mobile — users should be able to select multiple files at once and see a scrollable list where each file shows its own progress bar, status label (queued / uploading / done / failed), and a cancel button. Files should upload sequentially or with a max concurrency of 2, and failed ones should have a retry option inline without restarting the whole queue.</v>
+        <v>[DRY-RUN] Sobriety and clean-living streak day counter — medium</v>
       </c>
       <c r="J60" t="str">
-        <v>做一个移动端的多文件批量上传队列组件——用户可以一次选多个文件，然后看到一个可滚动的列表，每个文件都有独立的进度条、状态标签（排队中 / 上传中 / 已完成 / 上传失败）和一个取消按钮。文件支持逐个顺序上传，或者最多同时并发上传 2 个；上传失败的文件要能直接在列表里点击重试，不能重启整个队列。</v>
-      </c>
-      <c r="K60" t="str">
         <v/>
       </c>
     </row>
@@ -2519,33 +2338,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>q_scene_013_003</v>
+        <v>q_scene_019_005</v>
       </c>
       <c r="C61" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D61" t="str">
-        <v>Uploading &amp; Downloading 上传与下载</v>
+        <v>倒计时/纪念日</v>
       </c>
       <c r="E61" t="str">
-        <v>Drag-and-drop zone with file type and size validation</v>
+        <v>Fitness challenge day-counter with progress ring</v>
       </c>
       <c r="F61" t="str">
         <v>medium</v>
       </c>
       <c r="G61">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="H61">
-        <v>10005</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
-        <v>Build a drag-and-drop upload zone for a mobile file manager app — it should accept only PDF, JPG, and PNG files and reject anything else with a clear inline error message. Max file size is 10MB per file, and if something's too large it should show a size warning right on the drop zone without navigating away. The zone itself should have a visible dashed border that highlights when a file is dragged over it, and accepted files should appear as small preview cards below the zone with a remove button on each.</v>
+        <v>[DRY-RUN] Fitness challenge day-counter with progress ring — medium</v>
       </c>
       <c r="J61" t="str">
-        <v>为移动端文件管理器做一个拖拽上传区域——只接受 PDF、JPG 和 PNG 格式的文件，其他格式一律拒绝，并在区域内直接显示清晰的错误提示。每个文件的大小上限是 10MB，如果文件太大，要在拖拽区上直接显示超限警告，不能跳转到其他页面。上传区本身要有明显的虚线边框，文件拖入时边框需要高亮显示，已接受的文件在区域下方以小卡片的形式排列预览，每张卡片上都要有一个删除按钮。</v>
-      </c>
-      <c r="K61" t="str">
         <v/>
       </c>
     </row>
@@ -2554,33 +2370,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>q_scene_014_001</v>
+        <v>q_scene_020_001</v>
       </c>
       <c r="C62" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D62" t="str">
-        <v>Copying &amp; Duplicating 复制与副本</v>
+        <v>文本处理</v>
       </c>
       <c r="E62" t="str">
-        <v>Duplicate task with independent progress state</v>
+        <v>Password generator with entropy strength meter</v>
       </c>
       <c r="F62" t="str">
         <v>medium</v>
       </c>
       <c r="G62">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="H62">
-        <v>71163</v>
+        <v>0</v>
       </c>
       <c r="I62" t="str">
-        <v>Need to implement a "duplicate task" feature in the mobile app where tapping a duplicate button on any task card creates an exact copy of that task but with its own independent progress state — so the original and the copy track completion separately. The duplicated task should appear right below the original in the list, have a visual indicator (like a small "copy" badge or icon) to distinguish it, and its progress bar/percentage should start fresh at 0% regardless of where the original is. Make sure editing or completing one doesn't affect the other.</v>
+        <v>[DRY-RUN] Password generator with entropy strength meter — medium</v>
       </c>
       <c r="J62" t="str">
-        <v>需要在移动端 App 里实现"复制任务"功能：点击任务卡片上的复制按钮，会生成该任务的一份完整副本，但两者的进度状态完全独立互不影响——原任务和副本各自单独记录完成情况。复制出来的任务应该紧接在原任务下方显示，并带有一个视觉标识（比如小"副本"角标或图标）以示区分，同时不管原任务进度到哪里，副本的进度条和百分比都要从 0% 重新开始。另外要确保编辑或完成其中一个任务时，不会对另一个产生任何影响。</v>
-      </c>
-      <c r="K62" t="str">
         <v/>
       </c>
     </row>
@@ -2589,33 +2402,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>q_scene_014_002</v>
+        <v>q_scene_020_002</v>
       </c>
       <c r="C63" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D63" t="str">
-        <v>Copying &amp; Duplicating 复制与副本</v>
+        <v>文本处理</v>
       </c>
       <c r="E63" t="str">
-        <v>Copy project template and rename for new client</v>
+        <v>Markdown to HTML live preview converter</v>
       </c>
       <c r="F63" t="str">
         <v>medium</v>
       </c>
       <c r="G63">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="H63">
-        <v>9386</v>
+        <v>0</v>
       </c>
       <c r="I63" t="str">
-        <v>Need to build a "duplicate project" flow in the mobile app where users can long-press any existing project template card to trigger a copy action, then immediately get a rename modal so they can set a new client name before the duplicate is saved. The renamed copy should appear at the top of the project list with a subtle "new" badge, and the original template should stay untouched. Keep the modal simple — just a text input pre-filled with "Copy of [original name]" that the user can edit.</v>
+        <v>[DRY-RUN] Markdown to HTML live preview converter — medium</v>
       </c>
       <c r="J63" t="str">
-        <v>需要在移动端 App 里做一个「复制项目」的流程：用户长按任意现有项目模板卡片，触发复制操作，随即弹出一个重命名弹窗，让用户在保存副本前填好新的客户名称。重命名后的副本应出现在项目列表顶部，并带有一个低调的「新」角标，原模板保持不变。弹窗保持简洁，只需一个文本输入框，预填内容为「[原名称] 的副本」，用户可自行修改。</v>
-      </c>
-      <c r="K63" t="str">
         <v/>
       </c>
     </row>
@@ -2624,33 +2434,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>q_scene_014_003</v>
+        <v>q_scene_020_003</v>
       </c>
       <c r="C64" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D64" t="str">
-        <v>Copying &amp; Duplicating 复制与副本</v>
+        <v>文本处理</v>
       </c>
       <c r="E64" t="str">
-        <v>Clone recipe with serving-scaled ingredient list</v>
+        <v>JSON formatter and syntax validator</v>
       </c>
       <c r="F64" t="str">
         <v>medium</v>
       </c>
       <c r="G64">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="H64">
-        <v>8629</v>
+        <v>0</v>
       </c>
       <c r="I64" t="str">
-        <v>Build a "Clone Recipe" feature for the mobile app where tapping a clone button on any recipe card creates a full duplicate — but before saving, a modal pops up letting the user set the target serving size, and the ingredient quantities in the clone automatically scale proportionally based on the original serving count. The cloned recipe should be saved as a new editable entry with a name like "Copy of [Original Name]" and land in the same category as the source.</v>
+        <v>[DRY-RUN] JSON formatter and syntax validator — medium</v>
       </c>
       <c r="J64" t="str">
-        <v>在移动端实现一个「克隆食谱」功能：点击任意食谱卡片上的克隆按钮后，系统会生成一份完整副本——但在保存之前，先弹出一个模态框让用户设置目标份量，食材用量会根据原始份量自动按比例换算。克隆后的食谱以「[原始名称] 的副本」命名，作为一条新的可编辑条目保存，并归入与源食谱相同的分类下。</v>
-      </c>
-      <c r="K64" t="str">
         <v/>
       </c>
     </row>
@@ -2659,33 +2466,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>q_scene_015_001</v>
+        <v>q_scene_020_004</v>
       </c>
       <c r="C65" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D65" t="str">
-        <v>Misc 其他</v>
+        <v>文本处理</v>
       </c>
       <c r="E65" t="str">
-        <v>Onboarding walkthrough with skip-and-resume progress</v>
+        <v>CSV to table viewer and inline editor</v>
       </c>
       <c r="F65" t="str">
         <v>medium</v>
       </c>
       <c r="G65">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="H65">
-        <v>9445</v>
+        <v>0</v>
       </c>
       <c r="I65" t="str">
-        <v>Build an onboarding walkthrough for a mobile app where users can skip the flow at any point but their progress is saved so they can resume from where they left off later. The walkthrough should have around 5–6 steps with a visible progress indicator (dots or a step counter), and when a user skips, show a small persistent banner or tooltip somewhere in the main UI that lets them jump back in. On resume, it should animate back into the correct step rather than restarting from the beginning.</v>
+        <v>[DRY-RUN] CSV to table viewer and inline editor — medium</v>
       </c>
       <c r="J65" t="str">
-        <v>帮我做一个移动端 App 的新手引导流程，用户可以在任意步骤跳过，但进度要保存下来，下次可以从中断的地方继续。引导一共大概 5 到 6 步，需要有明显的进度指示器（小圆点或步骤计数器都行）。用户跳过之后，在主界面某个位置保留一个小悬浮条或提示气泡，让他们随时可以跳回来继续。恢复引导时，要带动画直接跳到之前中断的那一步，而不是从头开始重放。</v>
-      </c>
-      <c r="K65" t="str">
         <v/>
       </c>
     </row>
@@ -2694,33 +2498,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>q_scene_015_002</v>
+        <v>q_scene_020_005</v>
       </c>
       <c r="C66" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D66" t="str">
-        <v>Misc 其他</v>
+        <v>文本处理</v>
       </c>
       <c r="E66" t="str">
-        <v>Empty state first-action CTA with illustration</v>
+        <v>QR code generator from any text or URL</v>
       </c>
       <c r="F66" t="str">
         <v>medium</v>
       </c>
       <c r="G66">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="H66">
-        <v>10646</v>
+        <v>0</v>
       </c>
       <c r="I66" t="str">
-        <v>Build an empty state screen for a mobile app where there's no content yet — needs a centered illustration (SVG or Lottie, ideally something friendly/neutral), a short headline, a one-line subtext, and a primary CTA button that triggers the first action the user should take. The illustration should sit above the text block, the CTA should be full-width at the bottom of the content area (not pinned to screen bottom), and the whole thing should be vertically centered in the available space. Keep it reusable so I can swap the illustration, headline, and button label via props.</v>
+        <v>[DRY-RUN] QR code generator from any text or URL — medium</v>
       </c>
       <c r="J66" t="str">
-        <v>帮我做一个移动端的空状态页面，用于还没有任何内容的场景——中间需要放一个插画（SVG 或 Lottie 都行，风格尽量友好、中性一点），下面是一行简短的标题、一行说明文字，最后是一个主操作按钮，引导用户完成第一步操作。布局上插画在上、文字块在下，CTA 按钮通栏显示在内容区底部（不要吸附在屏幕最底部），整体在可用空间内垂直居中。组件要做成可复用的，插画、标题和按钮文案都通过 props 传入，方便替换。</v>
-      </c>
-      <c r="K66" t="str">
         <v/>
       </c>
     </row>
@@ -2729,33 +2530,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>q_scene_015_003</v>
+        <v>q_scene_021_001</v>
       </c>
       <c r="C67" t="str">
-        <v>交互方式</v>
+        <v>实用工具</v>
       </c>
       <c r="D67" t="str">
-        <v>Misc 其他</v>
+        <v>随机生成器</v>
       </c>
       <c r="E67" t="str">
-        <v>Pull-to-refresh with skeleton loading animation</v>
+        <v>Story plot and character prompt generator for writers</v>
       </c>
       <c r="F67" t="str">
         <v>medium</v>
       </c>
       <c r="G67">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="H67">
-        <v>9607</v>
+        <v>0</v>
       </c>
       <c r="I67" t="str">
-        <v>Add pull-to-refresh to the feed screen, and instead of a spinner just showing the real content when it loads, swap in skeleton loading cards during the refresh state. The skeletons should match the shape of the actual list items (thumbnail on the left, two lines of text on the right), and animate with a shimmer effect. Once the data resolves, fade the skeletons out and fade the real cards in.</v>
+        <v>[DRY-RUN] Story plot and character prompt generator for writers — medium</v>
       </c>
       <c r="J67" t="str">
-        <v>在 feed 页面加上下拉刷新功能，刷新过程中不要显示转圈 loading，改成用骨架屏卡片占位。骨架屏的布局要和真实列表项保持一致——左边是缩略图区域，右边是两行文字——并且带上 shimmer 扫光动效。数据加载完成后，骨架屏淡出，真实卡片淡入替换上去。</v>
-      </c>
-      <c r="K67" t="str">
         <v/>
       </c>
     </row>
@@ -2764,33 +2562,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>q_scene_016_001</v>
+        <v>q_scene_021_002</v>
       </c>
       <c r="C68" t="str">
         <v>实用工具</v>
       </c>
       <c r="D68" t="str">
-        <v>计算器/换算器 ★</v>
+        <v>随机生成器</v>
       </c>
       <c r="E68" t="str">
-        <v>Currency converter with live exchange rates</v>
+        <v>Team random pair-up and group assignment generator</v>
       </c>
       <c r="F68" t="str">
         <v>medium</v>
       </c>
       <c r="G68">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="H68">
-        <v>10670</v>
+        <v>0</v>
       </c>
       <c r="I68" t="str">
-        <v>Build a mobile currency converter screen that fetches live exchange rates from an API — need a clean input field at the top where users type an amount, then two currency selector dropdowns (from/to) with flag icons, and the converted result displayed large below. Add a swap button between the two selectors to flip currencies instantly. The rate should auto-refresh every 60 seconds and show a small timestamp like "Updated 2 min ago" so users know how fresh the data is.</v>
+        <v>[DRY-RUN] Team random pair-up and group assignment generator — medium</v>
       </c>
       <c r="J68" t="str">
-        <v>做一个移动端的货币换算页面，需要实时从接口拉取汇率数据——顶部放一个简洁的金额输入框，用户在里面输入数字，然后下面是两个带国旗图标的货币选择下拉框，分别对应源货币和目标货币，换算结果用大字显示在下方。两个选择框中间加一个切换按钮，点击可以瞬间互换两种货币的位置。汇率每60秒自动刷新一次，并在页面上显示一个小提示，比如"2分钟前更新"，让用户知道数据的时效性。</v>
-      </c>
-      <c r="K68" t="str">
         <v/>
       </c>
     </row>
@@ -2799,33 +2594,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>q_scene_016_002</v>
+        <v>q_scene_021_003</v>
       </c>
       <c r="C69" t="str">
         <v>实用工具</v>
       </c>
       <c r="D69" t="str">
-        <v>计算器/换算器 ★</v>
+        <v>随机生成器</v>
       </c>
       <c r="E69" t="str">
-        <v>Tip and bill splitter with custom share per person</v>
+        <v>Random chore assignment wheel for household</v>
       </c>
       <c r="F69" t="str">
         <v>medium</v>
       </c>
       <c r="G69">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="H69">
-        <v>9019</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
-        <v>Build a tip and bill splitter screen where users can enter the total bill amount, select a tip percentage (with a custom input option), and then split the cost across multiple people — but each person should be able to have a custom share percentage or fixed amount rather than always splitting evenly. Show a summary at the bottom with each person's name and what they owe, updating in real time as values change.</v>
+        <v>[DRY-RUN] Random chore assignment wheel for household — medium</v>
       </c>
       <c r="J69" t="str">
-        <v>做一个小费与账单分摊页面，用户可以输入账单总金额，选择小费比例（支持自定义输入），然后将费用分摊给多个人——但每个人可以单独设置自己的分摊比例或固定金额，不必强制平均分。页面底部展示汇总明细，列出每位成员的姓名和应付金额，所有数值随输入实时更新。</v>
-      </c>
-      <c r="K69" t="str">
         <v/>
       </c>
     </row>
@@ -2834,33 +2626,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>q_scene_016_003</v>
+        <v>q_scene_021_004</v>
       </c>
       <c r="C70" t="str">
         <v>实用工具</v>
       </c>
       <c r="D70" t="str">
-        <v>计算器/换算器 ★</v>
+        <v>随机生成器</v>
       </c>
       <c r="E70" t="str">
-        <v>BMI and ideal weight calculator</v>
+        <v>Pet name idea generator by personality</v>
       </c>
       <c r="F70" t="str">
         <v>medium</v>
       </c>
       <c r="G70">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="H70">
-        <v>9147</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
-        <v>Build a BMI and ideal weight calculator screen for a mobile utility app. It should take height and weight as inputs (with a toggle to switch between metric and imperial units), calculate BMI in real-time as the user types, and display the result with a color-coded category label (underweight, normal, overweight, obese). Below that, show an ideal weight range based on the user's height using a couple of common formulas. Keep the layout clean and card-based, nothing cluttered.</v>
+        <v>[DRY-RUN] Pet name idea generator by personality — medium</v>
       </c>
       <c r="J70" t="str">
-        <v>帮我做一个移动端工具类应用的BMI及理想体重计算页面。需要输入身高和体重，并提供公制/英制单位的切换开关，用户输入时实时计算BMI，结果用颜色区分不同的体重分类标签（偏瘦、正常、超重、肥胖）。下方根据用户身高，用几个常见公式算出理想体重范围并展示出来。整体布局要简洁，用卡片式设计，不要太杂乱。</v>
-      </c>
-      <c r="K70" t="str">
         <v/>
       </c>
     </row>
@@ -2869,33 +2658,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>q_scene_016_004</v>
+        <v>q_scene_021_005</v>
       </c>
       <c r="C71" t="str">
         <v>实用工具</v>
       </c>
       <c r="D71" t="str">
-        <v>计算器/换算器 ★</v>
+        <v>随机生成器</v>
       </c>
       <c r="E71" t="str">
-        <v>Mortgage and loan EMI calculator with amortization chart</v>
+        <v>D&amp;D dice roller with encounter table generator</v>
       </c>
       <c r="F71" t="str">
         <v>medium</v>
       </c>
       <c r="G71">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="H71">
-        <v>9303</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
-        <v>Build a mortgage/loan EMI calculator screen for mobile where users can input principal amount, annual interest rate, and loan tenure (in months or years with a toggle), then instantly see the calculated monthly EMI, total interest payable, and total payment amount. Below the inputs, show a scrollable amortization schedule table breaking down each month's principal vs interest portion and remaining balance. Also add a donut or bar chart visualizing the principal-to-interest ratio. Keep the layout clean with a sticky input card at the top and the chart + table scrolling underneath.</v>
+        <v>[DRY-RUN] D&amp;D dice roller with encounter table generator — medium</v>
       </c>
       <c r="J71" t="str">
-        <v>做一个移动端的房贷/贷款等额还款计算器页面，用户可以输入贷款本金、年利率和还款期限（支持月/年切换），实时显示计算出的每月还款额、应付总利息和还款总金额。输入区下方展示一个可滚动的还款计划明细表，按月拆分每期的本金偿还部分、利息部分以及剩余未还余额。同时加一个环形图或柱状图，直观呈现本金与利息的占比关系。整体布局保持简洁，顶部输入卡片固定吸顶，图表和明细表在下方跟随滚动。</v>
-      </c>
-      <c r="K71" t="str">
         <v/>
       </c>
     </row>
@@ -2904,33 +2690,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>q_scene_017_001</v>
+        <v>q_scene_022_001</v>
       </c>
       <c r="C72" t="str">
         <v>实用工具</v>
       </c>
       <c r="D72" t="str">
-        <v>生活记录器 ★</v>
+        <v>无障碍辅助</v>
       </c>
       <c r="E72" t="str">
-        <v>Daily mood tracker with emoji and freetext note</v>
+        <v>Simplified UI cognitive accessibility mode</v>
       </c>
       <c r="F72" t="str">
         <v>medium</v>
       </c>
       <c r="G72">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="H72">
-        <v>9375</v>
+        <v>0</v>
       </c>
       <c r="I72" t="str">
-        <v>Build a daily mood tracker screen where users can tap one of 5 emoji icons (ranging from awful to great) to log their current mood, then optionally add a short freetext note below. The selected emoji should have a highlighted/active state so it's clear which one is picked, and the note input should be a simple multiline text field with a character limit around 200. Each day's entry should be saved and accessible in a scrollable log at the bottom showing the date, emoji, and note preview.</v>
+        <v>[DRY-RUN] Simplified UI cognitive accessibility mode — medium</v>
       </c>
       <c r="J72" t="str">
-        <v>做一个每日心情记录页面，用户可以点击5个表情图标（从很糟糕到非常棒）来记录当前心情，下方可以选填一段简短的文字备注。被选中的表情要有高亮/激活状态，让人一眼看出选的是哪个；备注输入框用普通的多行文本框就行，字数限制在200字左右。每天的记录要能保存下来，页面底部有一个可滚动的日志列表，显示日期、表情和备注的预览内容。</v>
-      </c>
-      <c r="K72" t="str">
         <v/>
       </c>
     </row>
@@ -2939,33 +2722,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>q_scene_017_002</v>
+        <v>q_scene_022_002</v>
       </c>
       <c r="C73" t="str">
         <v>实用工具</v>
       </c>
       <c r="D73" t="str">
-        <v>生活记录器 ★</v>
+        <v>无障碍辅助</v>
       </c>
       <c r="E73" t="str">
-        <v>Food photo diary with calorie estimation</v>
+        <v>Auto-captioning and subtitle overlay for video</v>
       </c>
       <c r="F73" t="str">
         <v>medium</v>
       </c>
       <c r="G73">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H73">
-        <v>8767</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
-        <v>Build a food photo diary screen where users can tap a "+" button to add a meal entry — each entry should show the food photo, meal name, estimated calories, and timestamp. The calorie estimation should appear as an AI-generated badge overlaid on the photo thumbnail. Keep the layout as a scrollable daily feed grouped by date, with a daily calorie total pinned at the top of each day's section.</v>
+        <v>[DRY-RUN] Auto-captioning and subtitle overlay for video — medium</v>
       </c>
       <c r="J73" t="str">
-        <v>做一个饮食照片日记页面，用户点击"+"按钮可以新增一条饮食记录，每条记录需要展示食物照片、餐食名称、预估热量和记录时间。热量估算值要以 AI 生成的角标形式叠加显示在照片缩略图上。整体采用按日期分组的可滚动信息流布局，每个日期分组的顶部固定显示当天的热量总计。</v>
-      </c>
-      <c r="K73" t="str">
         <v/>
       </c>
     </row>
@@ -2974,33 +2754,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>q_scene_017_003</v>
+        <v>q_scene_022_003</v>
       </c>
       <c r="C74" t="str">
         <v>实用工具</v>
       </c>
       <c r="D74" t="str">
-        <v>生活记录器 ★</v>
+        <v>无障碍辅助</v>
       </c>
       <c r="E74" t="str">
-        <v>Water intake daily logger with goal ring</v>
+        <v>Voice control navigation and command input</v>
       </c>
       <c r="F74" t="str">
         <v>medium</v>
       </c>
       <c r="G74">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="H74">
-        <v>8223</v>
+        <v>0</v>
       </c>
       <c r="I74" t="str">
-        <v>Build a mobile water intake logger screen with a circular goal ring at the top showing daily progress (e.g., 1.2L / 2.0L goal) that animates as the user logs drinks. Below the ring, show a list of today's entries with timestamps and ml amounts, and include quick-add buttons for common amounts (150ml, 250ml, 500ml). The ring should change color or pulse when the daily goal is hit.</v>
+        <v>[DRY-RUN] Voice control navigation and command input — medium</v>
       </c>
       <c r="J74" t="str">
-        <v>做一个手机端的每日饮水记录页面，顶部放一个圆形进度环，实时显示当天的饮水进度（比如已喝1.2L，目标2.0L），每次记录喝水后进度环要有动画效果。环的下方展示今天的饮水记录列表，每条记录显示时间和毫升数，同时提供常用水量的快捷添加按钮（150ml、250ml、500ml）。达成每日目标时，进度环要变色或者有脉冲动效提示。</v>
-      </c>
-      <c r="K74" t="str">
         <v/>
       </c>
     </row>
@@ -3009,33 +2786,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>q_scene_017_004</v>
+        <v>q_scene_022_004</v>
       </c>
       <c r="C75" t="str">
         <v>实用工具</v>
       </c>
       <c r="D75" t="str">
-        <v>生活记录器 ★</v>
+        <v>无障碍辅助</v>
       </c>
       <c r="E75" t="str">
-        <v>Sleep onset and wake tracker with quality score</v>
+        <v>Haptic feedback intensity and pattern adjuster</v>
       </c>
       <c r="F75" t="str">
         <v>medium</v>
       </c>
       <c r="G75">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="H75">
-        <v>9926</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
-        <v>Build a sleep tracker screen where users can log their bedtime and wake time, and the app automatically calculates a quality score (0–100) based on total sleep duration and consistency with their target schedule. The UI should show a simple card with two time-picker buttons (Fell Asleep / Woke Up), a circular progress indicator for the quality score, and a weekly bar chart below summarizing the past 7 nights. Keep it minimal — no sign-in, just local storage.</v>
+        <v>[DRY-RUN] Haptic feedback intensity and pattern adjuster — medium</v>
       </c>
       <c r="J75" t="str">
-        <v>做一个睡眠记录页面，用户可以手动输入入睡时间和起床时间，App 自动根据总睡眠时长以及与目标作息的吻合程度计算出一个质量评分（0 到 100 分）。界面要有一张简洁的卡片，上面放两个时间选择按钮（分别是"入睡时间"和"起床时间"），中间用一个圆形进度条展示质量评分，卡片下方用柱状图汇总最近 7 天的睡眠情况。整体风格保持简约，不需要登录，数据存本地就行。</v>
-      </c>
-      <c r="K75" t="str">
         <v/>
       </c>
     </row>
@@ -3044,33 +2818,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>q_scene_018_001</v>
+        <v>q_scene_022_005</v>
       </c>
       <c r="C76" t="str">
         <v>实用工具</v>
       </c>
       <c r="D76" t="str">
-        <v>社交辅助 ★</v>
+        <v>无障碍辅助</v>
       </c>
       <c r="E76" t="str">
-        <v>Random icebreaker question generator for groups</v>
+        <v>Motor accessibility switch control mode</v>
       </c>
       <c r="F76" t="str">
         <v>medium</v>
       </c>
       <c r="G76">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="H76">
-        <v>9542</v>
+        <v>0</v>
       </c>
       <c r="I76" t="str">
-        <v>Build a random icebreaker question generator screen for a mobile app — there should be a big "Shuffle" button in the center that animates a card flip to reveal a new question each tap. Questions should be grouped by category (e.g. "Funny", "Deep", "Work-friendly") with a filter row at the top so users can pick which categories are in the random pool. Also add a small "Save to favorites" icon on each card so users can bookmark questions they like.</v>
+        <v>[DRY-RUN] Motor accessibility switch control mode — medium</v>
       </c>
       <c r="J76" t="str">
-        <v>做一个手机 App 上的随机破冰问题生成页面——页面中央要有一个大大的"随机一题"按钮，每次点击都会触发卡片翻转动画，翻过来显示一道新问题。问题按分类整理（比如"搞笑""走心""职场友好"等），顶部有一排筛选标签，让用户自己选择哪些分类参与随机抽取。另外每张卡片上要有一个小小的"收藏"图标，方便用户把喜欢的问题存起来。</v>
-      </c>
-      <c r="K76" t="str">
         <v/>
       </c>
     </row>
@@ -3079,33 +2850,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>q_scene_018_002</v>
+        <v>q_scene_023_001</v>
       </c>
       <c r="C77" t="str">
         <v>实用工具</v>
       </c>
       <c r="D77" t="str">
-        <v>社交辅助 ★</v>
+        <v>其他长尾微工具</v>
       </c>
       <c r="E77" t="str">
-        <v>Compliment generator for team appreciation wall</v>
+        <v>Bubble level for hanging pictures and furniture</v>
       </c>
       <c r="F77" t="str">
         <v>medium</v>
       </c>
       <c r="G77">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H77">
-        <v>9501</v>
+        <v>0</v>
       </c>
       <c r="I77" t="str">
-        <v>Build a compliment generator screen for a team appreciation wall feature — user picks a teammate's name and selects a category (like "teamwork", "creativity", "reliability"), then the app generates a short personalized compliment they can post to a shared wall feed. Include a "regenerate" button to swap out the suggestion, and keep the UI card-style with the generated text displayed in a highlighted bubble before posting. Should feel light and fun, not corporate.</v>
+        <v>[DRY-RUN] Bubble level for hanging pictures and furniture — medium</v>
       </c>
       <c r="J77" t="str">
-        <v>做一个团队表扬墙功能里的夸夸生成页面——用户先选一个队友的名字，再选一个分类（比如"团队协作""创意力""靠谱度"之类的），然后 app 自动生成一段简短的个性化夸赞文案，用户可以把它发到大家共享的表扬墙动态里。要有一个"换一条"按钮方便替换当前生成的内容，整体用卡片式布局，生成的文字在发布前以高亮气泡的形式展示出来。风格要轻松好玩，不要有那种死板的企业感。</v>
-      </c>
-      <c r="K77" t="str">
         <v/>
       </c>
     </row>
@@ -3114,33 +2882,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>q_scene_018_003</v>
+        <v>q_scene_023_002</v>
       </c>
       <c r="C78" t="str">
         <v>实用工具</v>
       </c>
       <c r="D78" t="str">
-        <v>社交辅助 ★</v>
+        <v>其他长尾微工具</v>
       </c>
       <c r="E78" t="str">
-        <v>Conversation starter for first-date or networking</v>
+        <v>Screen ruler calibrated to physical device size</v>
       </c>
       <c r="F78" t="str">
         <v>medium</v>
       </c>
       <c r="G78">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="H78">
-        <v>10505</v>
+        <v>0</v>
       </c>
       <c r="I78" t="str">
-        <v>Build a conversation starter screen for a social utility app — users pick a context (first date, networking event, or casual meetup) and get 3–5 suggested icebreaker questions they can swipe through or tap to save. Each card should show the question in large text with a subtle category tag (e.g., "Fun", "Thoughtful", "Bold"), and there should be a shuffle button to load a new batch. Keep the UI clean and friendly, no more than 2 colors plus white, and make the cards feel tappable with a slight shadow and rounded corners.</v>
+        <v>[DRY-RUN] Screen ruler calibrated to physical device size — medium</v>
       </c>
       <c r="J78" t="str">
-        <v>做一个社交工具类 App 的破冰话题启动页——用户先选择使用场景（初次约会、商务社交活动或日常聚会），然后获得 3 到 5 个推荐的破冰问题，支持左右滑动浏览或点击收藏。每张卡片用大号字体显示问题内容，并附带一个低调的分类标签（比如"有趣""走心""大胆"），另外需要一个"换一批"按钮来随机加载新的问题组合。整体 UI 要简洁亲切，配色不超过两种加白色，卡片加上轻微阴影和圆角，让人一眼就有想点的感觉。</v>
-      </c>
-      <c r="K78" t="str">
         <v/>
       </c>
     </row>
@@ -3149,33 +2914,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>q_scene_018_004</v>
+        <v>q_scene_023_003</v>
       </c>
       <c r="C79" t="str">
         <v>实用工具</v>
       </c>
       <c r="D79" t="str">
-        <v>社交辅助 ★</v>
+        <v>其他长尾微工具</v>
       </c>
       <c r="E79" t="str">
-        <v>Meeting agenda and talking-point preparer</v>
+        <v>Metronome with BPM tap-input and sound selector</v>
       </c>
       <c r="F79" t="str">
         <v>medium</v>
       </c>
       <c r="G79">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="H79">
-        <v>9668</v>
+        <v>0</v>
       </c>
       <c r="I79" t="str">
-        <v>Build a meeting prep screen where users can input the meeting title, attendees, and a few bullet points about the context, then the app generates a structured agenda with suggested talking points for each section. The agenda should be displayed in an expandable card list so users can tap each agenda item to see/edit the talking points underneath. Also add a "Copy to Clipboard" button at the bottom so they can paste the whole thing into a calendar invite or message.</v>
+        <v>[DRY-RUN] Metronome with BPM tap-input and sound selector — medium</v>
       </c>
       <c r="J79" t="str">
-        <v>做一个会议准备页面，用户可以输入会议标题、参会人员以及几条背景要点，然后由应用自动生成一份结构化的议程，并为每个议程板块提供建议发言要点。议程以可展开的卡片列表形式呈现，用户点击每条议程项即可查看或编辑其下方的发言要点。页面底部还需要加一个"复制到剪贴板"按钮，方便用户将整份议程粘贴到日历邀请或消息中。</v>
-      </c>
-      <c r="K79" t="str">
         <v/>
       </c>
     </row>
@@ -3184,33 +2946,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>q_scene_019_001</v>
+        <v>q_scene_023_004</v>
       </c>
       <c r="C80" t="str">
         <v>实用工具</v>
       </c>
       <c r="D80" t="str">
-        <v>倒计时/纪念日</v>
+        <v>其他长尾微工具</v>
       </c>
       <c r="E80" t="str">
-        <v>Wedding countdown with vendor checklist integration</v>
+        <v>Compass with magnetic declination adjustment</v>
       </c>
       <c r="F80" t="str">
         <v>medium</v>
       </c>
       <c r="G80">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="H80">
-        <v>134317</v>
+        <v>0</v>
       </c>
       <c r="I80" t="str">
-        <v>Build a wedding countdown screen that shows days remaining until the wedding date at the top (large, prominent display), and below it a scrollable vendor checklist grouped by category — like Venue, Catering, Photography, Flowers, etc. Each vendor item should have a checkbox to mark as booked, a due date field, and a status badge (Pending / Confirmed / Paid). The checklist progress should feed into a small circular progress ring next to the countdown so users can see at a glance how much planning is done. Tapping a vendor row should expand it to show notes and a contact field.</v>
+        <v>[DRY-RUN] Compass with magnetic declination adjustment — medium</v>
       </c>
       <c r="J80" t="str">
-        <v>做一个婚礼倒计时页面，顶部用大字醒目地显示距婚礼还有多少天，下方是一个可滚动的供应商清单，按类别分组，比如场地、餐饮、摄影、鲜花布置等。每个供应商条目要有一个勾选框来标记是否已预订、一个截止日期字段，以及一个状态标签，分别对应"待处理""已确认""已付款"三种状态。清单的完成进度要同步到倒计时旁边的一个小圆形进度环上，让用户一眼就能看出整体筹备进展。点击某个供应商条目后，该行应展开显示备注信息和联系方式填写区。</v>
-      </c>
-      <c r="K80" t="str">
         <v/>
       </c>
     </row>
@@ -3219,33 +2978,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>q_scene_019_002</v>
+        <v>q_scene_023_005</v>
       </c>
       <c r="C81" t="str">
         <v>实用工具</v>
       </c>
       <c r="D81" t="str">
-        <v>倒计时/纪念日</v>
+        <v>其他长尾微工具</v>
       </c>
       <c r="E81" t="str">
-        <v>New Year event live countdown ticker</v>
+        <v>Mirror with zoom, freeze-frame and grid overlay</v>
       </c>
       <c r="F81" t="str">
         <v>medium</v>
       </c>
       <c r="G81">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="H81">
-        <v>9388</v>
+        <v>0</v>
       </c>
       <c r="I81" t="str">
-        <v>Build a live countdown ticker for a New Year event screen — it should display days, hours, minutes, and seconds in large bold digits that update every second in real time. The ticker needs to animate each digit flip individually (like a slot machine or flip clock effect) when the number changes. Also include a short celebratory animation or confetti burst that triggers automatically when the countdown hits zero.</v>
+        <v>[DRY-RUN] Mirror with zoom, freeze-frame and grid overlay — medium</v>
       </c>
       <c r="J81" t="str">
-        <v>做一个新年活动页面的实时倒计时组件，需要显示天、时、分、秒，数字要又大又粗，每秒实时刷新。每当数字发生变化时，要逐位触发翻转动画，效果类似老虎机滚轮或翻页时钟那种感觉。另外，倒计时归零的瞬间要自动播放一段庆祝动画或彩纸爆炸效果。</v>
-      </c>
-      <c r="K81" t="str">
         <v/>
       </c>
     </row>
@@ -3254,33 +3010,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>q_scene_019_003</v>
+        <v>q_scene_024_001</v>
       </c>
       <c r="C82" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D82" t="str">
-        <v>倒计时/纪念日</v>
+        <v>闪卡/单词记忆 ★</v>
       </c>
       <c r="E82" t="str">
-        <v>Project deadline countdown with milestone markers</v>
+        <v>Chemistry periodic table element quiz</v>
       </c>
       <c r="F82" t="str">
         <v>medium</v>
       </c>
       <c r="G82">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="H82">
-        <v>71792</v>
+        <v>0</v>
       </c>
       <c r="I82" t="str">
-        <v>Build a project deadline countdown screen where the main focus is a large days-remaining counter at the top, and below it a vertical timeline showing milestone markers between today and the final deadline — each milestone should display its name, due date, and a small status indicator (upcoming / in progress / done). Tapping a milestone should expand it to show a short description. Keep the whole thing scrollable and make sure completed milestones are visually muted compared to active ones.</v>
+        <v>[DRY-RUN] Chemistry periodic table element quiz — medium</v>
       </c>
       <c r="J82" t="str">
-        <v>做一个项目截止日期倒计时页面，核心内容是顶部一个大号的"剩余天数"计数器，下方是一条竖向时间线，展示从今天到最终截止日期之间的各个里程碑节点——每个节点要显示名称、截止日期和一个小状态标识（未开始 / 进行中 / 已完成）。点击某个里程碑后可以展开查看简短说明。整个页面支持滚动，已完成的里程碑在视觉上要比当前进行中的明显弱化。</v>
-      </c>
-      <c r="K82" t="str">
         <v/>
       </c>
     </row>
@@ -3289,33 +3042,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>q_scene_019_004</v>
+        <v>q_scene_024_002</v>
       </c>
       <c r="C83" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D83" t="str">
-        <v>倒计时/纪念日</v>
+        <v>闪卡/单词记忆 ★</v>
       </c>
       <c r="E83" t="str">
-        <v>Baby due date countdown with week-by-week guide</v>
+        <v>Programming language keyword syntax card</v>
       </c>
       <c r="F83" t="str">
         <v>medium</v>
       </c>
       <c r="G83">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="H83">
-        <v>133659</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
-        <v>Build a baby due date countdown screen that shows the days remaining until the due date at the top in a large, prominent display, then below it shows the current pregnancy week (e.g. "Week 14") with a brief weekly milestone description — things like fetal size, key developments, what the mom might be feeling. The week guide should scroll as a card list so users can peek ahead at upcoming weeks. Include a way to set or edit the due date, and make the overall vibe warm and soft — pastel colors, rounded cards, nothing clinical-looking.</v>
+        <v>[DRY-RUN] Programming language keyword syntax card — medium</v>
       </c>
       <c r="J83" t="str">
-        <v>做一个宝宝预产期倒计时页面，顶部用大号醒目的数字显示距离预产期还有多少天，下方展示当前孕周（比如"第14周"），并附上该周的简短里程碑介绍——包括胎儿大小、关键发育情况、准妈妈可能有的身体感受等。孕周指南以卡片列表的形式滚动展示，方便用户提前浏览后续各周的内容。页面需要提供设置或修改预产期的入口，整体风格要温馨柔和——用莫兰迪色系或马卡龙色调，卡片圆角设计，不要有任何冷冰冰的医疗感。</v>
-      </c>
-      <c r="K83" t="str">
         <v/>
       </c>
     </row>
@@ -3324,33 +3074,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>q_scene_020_001</v>
+        <v>q_scene_024_003</v>
       </c>
       <c r="C84" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D84" t="str">
-        <v>文本处理</v>
+        <v>闪卡/单词记忆 ★</v>
       </c>
       <c r="E84" t="str">
-        <v>Language translator with dialect selector</v>
+        <v>History date and event memory flashcard</v>
       </c>
       <c r="F84" t="str">
         <v>medium</v>
       </c>
       <c r="G84">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="H84">
-        <v>132692</v>
+        <v>0</v>
       </c>
       <c r="I84" t="str">
-        <v>Build a language translator screen for a mobile utility app that includes a dialect selector — so for example, if someone picks Spanish, they can then choose between Latin American, Castilian, or regional variants before translating. The layout should have a source language panel on top and target language panel below, each with their own dialect dropdown that appears only when the selected language actually has dialect options. Keep the translate button centered between the two panels and make the dialect selector feel like a subtle secondary control, not cluttering the main input area.</v>
+        <v>[DRY-RUN] History date and event memory flashcard — medium</v>
       </c>
       <c r="J84" t="str">
-        <v>做一个移动端工具类应用的语言翻译界面，需要支持方言选择——比如用户选了西班牙语之后，可以进一步选择拉丁美洲西班牙语、卡斯蒂利亚西班牙语或其他地区变体，再进行翻译。布局上源语言区域在上、目标语言区域在下，两个区域各自有一个方言下拉选择器，只在当前所选语言确实存在方言分支时才显示出来。翻译按钮居中放在两个区域之间，方言选择器的视觉权重要轻一些，作为次级控件存在，不能让主输入区域显得凌乱。</v>
-      </c>
-      <c r="K84" t="str">
         <v/>
       </c>
     </row>
@@ -3359,33 +3106,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>q_scene_020_002</v>
+        <v>q_scene_024_004</v>
       </c>
       <c r="C85" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D85" t="str">
-        <v>文本处理</v>
+        <v>闪卡/单词记忆 ★</v>
       </c>
       <c r="E85" t="str">
-        <v>Word, character count and reading time estimator</v>
+        <v>Legal definition card for bar exam prep</v>
       </c>
       <c r="F85" t="str">
         <v>medium</v>
       </c>
       <c r="G85">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="H85">
-        <v>7949</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
-        <v>Build a text stats panel for a mobile utility app — as the user types into a textarea, it should live-update word count, character count (with and without spaces), and an estimated reading time (assume 200 wpm average). Display these three stats as small labeled cards in a row beneath the input. The reading time should show in "X min read" format and round up to at least 1 min even for very short text.</v>
+        <v>[DRY-RUN] Legal definition card for bar exam prep — medium</v>
       </c>
       <c r="J85" t="str">
-        <v>为一款移动工具应用做一个文本统计面板——用户在文本框里打字时，实时更新单词数、字符数（含空格和不含空格两种）以及预计阅读时间（按平均每分钟200词计算）。把这三个统计数据以小卡片的形式横排显示在输入框下方，每张卡片带有标签说明。阅读时间格式为"X分钟阅读"，不足1分钟的一律向上取整为1分钟。</v>
-      </c>
-      <c r="K85" t="str">
         <v/>
       </c>
     </row>
@@ -3394,33 +3138,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>q_scene_020_003</v>
+        <v>q_scene_025_001</v>
       </c>
       <c r="C86" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D86" t="str">
-        <v>文本处理</v>
+        <v>备考自测/刷题 ★</v>
       </c>
       <c r="E86" t="str">
-        <v>Text-to-speech with voice and speed control</v>
+        <v>Bar exam multiple choice question bank</v>
       </c>
       <c r="F86" t="str">
         <v>medium</v>
       </c>
       <c r="G86">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H86">
-        <v>8954</v>
+        <v>0</v>
       </c>
       <c r="I86" t="str">
-        <v>Add a text-to-speech panel to the text editor screen — it needs a play/pause button, a speed slider (0.5x to 2x), and a voice picker dropdown with at least 3 voice options (male, female, neutral). The controls should sit in a bottom sheet that slides up when the user taps a speaker icon in the toolbar. Make sure the speed and voice selections persist across sessions using local storage.</v>
+        <v>[DRY-RUN] Bar exam multiple choice question bank — medium</v>
       </c>
       <c r="J86" t="str">
-        <v>在文本编辑器页面加一个文字转语音面板——需要包含播放/暂停按钮、一个速度滑块（范围 0.5x 到 2x），以及一个至少有三个选项的音色下拉菜单（男声、女声、中性）。这些控件放在一个底部抽屉里，用户点击工具栏上的扬声器图标时从底部滑出。速度和音色的选择要通过 localStorage 持久化，下次打开仍然保留上次的设置。</v>
-      </c>
-      <c r="K86" t="str">
         <v/>
       </c>
     </row>
@@ -3429,33 +3170,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>q_scene_020_004</v>
+        <v>q_scene_025_002</v>
       </c>
       <c r="C87" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D87" t="str">
-        <v>文本处理</v>
+        <v>备考自测/刷题 ★</v>
       </c>
       <c r="E87" t="str">
-        <v>Case converter (upper/lower/title/sentence)</v>
+        <v>USMLE Step 1 clinical case quiz</v>
       </c>
       <c r="F87" t="str">
         <v>medium</v>
       </c>
       <c r="G87">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="H87">
-        <v>8451</v>
+        <v>0</v>
       </c>
       <c r="I87" t="str">
-        <v>Build a case converter screen for a text utility mobile app — needs four conversion modes: UPPERCASE, lowercase, Title Case, and Sentence case. The UI should have a text input area at the top, then a row of four toggle buttons below it for switching modes, and the converted result should update in real-time as the user types or taps a mode button. Add a copy-to-clipboard button next to the output. Keep the layout clean and single-screen, no extra navigation needed.</v>
+        <v>[DRY-RUN] USMLE Step 1 clinical case quiz — medium</v>
       </c>
       <c r="J87" t="str">
-        <v>帮我做一个文字工具类手机应用里的大小写转换页面，需要支持四种转换模式：全大写、全小写、首字母大写和句首大写。界面顶部放一个文本输入框，下面一排四个切换按钮用来选择模式，用户在输入文字或点击模式按钮时，转换结果要实时更新显示出来。在输出结果旁边加一个一键复制按钮。整体布局保持简洁，单屏展示，不需要额外的导航跳转。</v>
-      </c>
-      <c r="K87" t="str">
         <v/>
       </c>
     </row>
@@ -3464,33 +3202,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>q_scene_021_001</v>
+        <v>q_scene_025_003</v>
       </c>
       <c r="C88" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D88" t="str">
-        <v>随机生成器</v>
+        <v>备考自测/刷题 ★</v>
       </c>
       <c r="E88" t="str">
-        <v>Baby name generator by origin, meaning and popularity</v>
+        <v>PMP project management scenario questions</v>
       </c>
       <c r="F88" t="str">
         <v>medium</v>
       </c>
       <c r="G88">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="H88">
-        <v>8443</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
-        <v>Build a baby name generator screen for a mobile utility app. Users should be able to filter names by origin (e.g. Latin, Hebrew, Japanese, Celtic), meaning keywords (like "strength" or "light"), and a popularity toggle that lets them choose between trending names vs. rare/unique ones. The results should show each name with its origin, meaning, and a small popularity badge. Include a "Save to Favorites" button on each card and a randomize button that picks a name based on the current filters.</v>
+        <v>[DRY-RUN] PMP project management scenario questions — medium</v>
       </c>
       <c r="J88" t="str">
-        <v>为一款移动端工具应用做一个宝宝取名生成页面。用户可以按名字的来源（比如拉丁语、希伯来语、日语、凯尔特语）、含义关键词（比如"力量"或"光明"）进行筛选，还有一个热度切换开关，让用户选择是看流行名字还是冷门独特的名字。结果列表里每个名字都要展示其来源、含义以及一个小的热度标签。每张名字卡片上要有"收藏"按钮，另外还要有一个随机按钮，能根据当前筛选条件随机推荐一个名字。</v>
-      </c>
-      <c r="K88" t="str">
         <v/>
       </c>
     </row>
@@ -3499,33 +3234,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>q_scene_021_002</v>
+        <v>q_scene_025_004</v>
       </c>
       <c r="C89" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D89" t="str">
-        <v>随机生成器</v>
+        <v>备考自测/刷题 ★</v>
       </c>
       <c r="E89" t="str">
-        <v>Random travel destination picker by budget and season</v>
+        <v>CPA financial accounting exam drill</v>
       </c>
       <c r="F89" t="str">
         <v>medium</v>
       </c>
       <c r="G89">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="H89">
-        <v>8384</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
-        <v>Build a random travel destination picker screen where users set a budget range (using a dual-handle slider) and select a travel season (spring/summer/fall/winter as toggle chips), then hit a "Surprise Me" button that animates a card flip to reveal a destination — show the destination name, a thumbnail, estimated cost range, and best activities. Should feel snappy and fun, not like a boring form.</v>
+        <v>[DRY-RUN] CPA financial accounting exam drill — medium</v>
       </c>
       <c r="J89" t="str">
-        <v>做一个随机旅行目的地抽签页面，用户可以用双滑块设置预算范围，用切换标签选择出行季节（春夏秋冬四个选项），然后点击"给我惊喜"按钮，触发一个卡片翻转动画来揭晓目的地——展示目的地名称、缩略图、大概花费区间和最佳玩法。整体要有那种轻快好玩的感觉，别搞得像个无聊的表单。</v>
-      </c>
-      <c r="K89" t="str">
         <v/>
       </c>
     </row>
@@ -3534,33 +3266,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>q_scene_021_003</v>
+        <v>q_scene_026_001</v>
       </c>
       <c r="C90" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D90" t="str">
-        <v>随机生成器</v>
+        <v>学习打卡/进度追踪 ★</v>
       </c>
       <c r="E90" t="str">
-        <v>Yes/No decision oracle with tarot-style reveal</v>
+        <v>Workout skill progression milestone tracker</v>
       </c>
       <c r="F90" t="str">
         <v>medium</v>
       </c>
       <c r="G90">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="H90">
-        <v>9278</v>
+        <v>0</v>
       </c>
       <c r="I90" t="str">
-        <v>Build a Yes/No decision oracle screen where the user types in a question, taps a "Ask the Oracle" button, and gets a tarot-card-style flip animation that reveals either YES or NO. The card should start face-down with a mystical back design, then do a 3D horizontal flip to show the answer with a glowing border — green for YES, red for NO. Add a short cryptic one-liner beneath the answer (randomly picked from a pool of like 20 phrases). Keep the overall vibe dark and mystical — deep purple/navy background, gold accents, serif or gothic font for the answer text.</v>
+        <v>[DRY-RUN] Workout skill progression milestone tracker — medium</v>
       </c>
       <c r="J90" t="str">
-        <v>做一个「是/否」神谕决策页面：用户输入一个问题，点击「请示神谕」按钮后，触发一张塔罗牌风格的翻牌动画，揭示「是」或「否」的答案。牌面初始朝下，背面是神秘花纹图案，然后做一个3D水平翻转，正面显示答案，并带有发光边框效果——「是」用绿色，「否」用红色。答案下方随机显示一句简短的神秘感台词，从大约20句备选语录里随机抽取。整体风格要暗黑神秘——深紫色或深蓝色背景，金色点缀，答案文字使用衬线体或哥特风格字体。</v>
-      </c>
-      <c r="K90" t="str">
         <v/>
       </c>
     </row>
@@ -3569,33 +3298,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>q_scene_021_004</v>
+        <v>q_scene_026_002</v>
       </c>
       <c r="C91" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D91" t="str">
-        <v>随机生成器</v>
+        <v>学习打卡/进度追踪 ★</v>
       </c>
       <c r="E91" t="str">
-        <v>Random meal picker by cuisine, mood and dietary need</v>
+        <v>Music practice session log with song milestone</v>
       </c>
       <c r="F91" t="str">
         <v>medium</v>
       </c>
       <c r="G91">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="H91">
-        <v>12032</v>
+        <v>0</v>
       </c>
       <c r="I91" t="str">
-        <v>Build a random meal picker screen for a mobile utility app — users should be able to select filters like cuisine type (e.g. Japanese, Mexican, Italian), current mood (e.g. comfort food, adventurous, light), and dietary needs (vegetarian, gluten-free, etc.), then hit a big "Pick My Meal" button that spins or animates before landing on a result card showing the meal name, a short description, and an option to re-roll. Keep the filter UI compact — maybe chips or toggle pills — so it doesn't take up too much vertical space before the action button.</v>
+        <v>[DRY-RUN] Music practice session log with song milestone — medium</v>
       </c>
       <c r="J91" t="str">
-        <v>做一个手机工具类应用里的随机选餐页面——用户可以设置筛选条件，比如菜系类型（日料、墨西哥菜、意大利菜之类的）、当前心情（想吃家常菜、想尝鲜、还是吃点清淡的），以及饮食需求（素食、无麸质等），然后点一个大大的"帮我选一餐"按钮，按钮触发后要有旋转或动画效果，最终落定在一张结果卡片上，显示餐品名称、简短介绍，以及一个重新抽取的选项。筛选条件的 UI 要尽量紧凑，用标签胶囊或者切换pill的形式就好，不要在操作按钮之前占用太多纵向空间。</v>
-      </c>
-      <c r="K91" t="str">
         <v/>
       </c>
     </row>
@@ -3604,33 +3330,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>q_scene_022_001</v>
+        <v>q_scene_026_003</v>
       </c>
       <c r="C92" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D92" t="str">
-        <v>无障碍辅助</v>
+        <v>学习打卡/进度追踪 ★</v>
       </c>
       <c r="E92" t="str">
-        <v>High-contrast mode with customizable color pair</v>
+        <v>Math topic mastery heatmap calendar</v>
       </c>
       <c r="F92" t="str">
         <v>medium</v>
       </c>
       <c r="G92">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="H92">
-        <v>8079</v>
+        <v>0</v>
       </c>
       <c r="I92" t="str">
-        <v>Add a high-contrast mode to the accessibility settings screen — users should be able to pick their own foreground/background color pair from a preset list (at least 4 options like white-on-black, yellow-on-black, black-on-yellow, green-on-black) plus a custom color picker for advanced users. The selected pair should apply globally across the app's text, icons, and card backgrounds. Make sure there's a live preview tile in the settings panel so users can see how the contrast looks before confirming.</v>
+        <v>[DRY-RUN] Math topic mastery heatmap calendar — medium</v>
       </c>
       <c r="J92" t="str">
-        <v>在无障碍设置页面加一个高对比度模式——用户可以从预设列表里选择自己喜欢的前景色/背景色组合，至少提供4个选项，比如黑底白字、黑底黄字、黄底黑字、黑底绿字，另外还要给进阶用户提供一个自定义颜色选择器。选好的配色方案要全局生效，覆盖整个应用的文字、图标和卡片背景。同时在设置面板里加一个实时预览区，让用户在确认之前能直接看到对比效果。</v>
-      </c>
-      <c r="K92" t="str">
         <v/>
       </c>
     </row>
@@ -3639,33 +3362,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>q_scene_022_002</v>
+        <v>q_scene_026_004</v>
       </c>
       <c r="C93" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D93" t="str">
-        <v>无障碍辅助</v>
+        <v>学习打卡/进度追踪 ★</v>
       </c>
       <c r="E93" t="str">
-        <v>Font size and line-spacing accessibility slider</v>
+        <v>Grammar rule completion progress ring</v>
       </c>
       <c r="F93" t="str">
         <v>medium</v>
       </c>
       <c r="G93">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="H93">
-        <v>12958</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
-        <v>Build an accessibility settings screen for a mobile utility app that includes two sliders — one for font size (range: 12px–24px) and one for line spacing (range: 1.0x–2.0x). Each slider should show a live preview text block below it so users can immediately see how their selection affects readability. The sliders need clear tick marks or step increments, and the current value should display next to the label. Keep the layout vertical and touch-friendly with enough padding between the two controls so they don't feel cramped on smaller screens.</v>
+        <v>[DRY-RUN] Grammar rule completion progress ring — medium</v>
       </c>
       <c r="J93" t="str">
-        <v>为一款移动工具类应用构建一个无障碍设置页面，包含两个滑块控件——一个用于调节字体大小（范围：12px 至 24px），另一个用于调节行间距（范围：1.0x 至 2.0x）。每个滑块下方需要有一个实时预览文本块，让用户能立即看到当前设置对阅读体验的影响。滑块要有清晰的刻度标记或步进间隔，当前数值需显示在标签旁边。整体布局保持垂直排列，操作区域要对触控友好，两个控件之间留出足够的间距，确保在小屏手机上也不会显得局促拥挤。</v>
-      </c>
-      <c r="K93" t="str">
         <v/>
       </c>
     </row>
@@ -3674,33 +3394,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>q_scene_022_003</v>
+        <v>q_scene_027_001</v>
       </c>
       <c r="C94" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D94" t="str">
-        <v>无障碍辅助</v>
+        <v>课程目录/课堂界面</v>
       </c>
       <c r="E94" t="str">
-        <v>Screen reader optimized navigation flow</v>
+        <v>Course enrollment confirmation and onboarding guide</v>
       </c>
       <c r="F94" t="str">
         <v>medium</v>
       </c>
       <c r="G94">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="H94">
-        <v>13266</v>
+        <v>0</v>
       </c>
       <c r="I94" t="str">
-        <v>Need to set up a screen reader optimized navigation flow for an accessibility utility app. The main requirement is that every interactive element has a proper `accessibilityLabel` and `accessibilityHint`, and the tab order follows a logical top-to-bottom, left-to-right sequence without any focus traps. There's a bottom nav bar with 4 tabs and a few modal sheets — make sure focus moves correctly into the modal when it opens and returns to the trigger element when it dismisses. Using React Native, so TalkBack and VoiceOver both need to work consistently.</v>
+        <v>[DRY-RUN] Course enrollment confirmation and onboarding guide — medium</v>
       </c>
       <c r="J94" t="str">
-        <v>需要为一款无障碍辅助应用配置一套针对屏幕阅读器优化的导航流程。核心要求是每个可交互元素都必须正确设置 `accessibilityLabel` 和 `accessibilityHint`，同时焦点顺序要严格按照从上到下、从左到右的逻辑排列，不能出现焦点陷阱。底部导航栏有 4 个 tab，另外还有几个 modal 弹层——需要确保 modal 打开时焦点能正确移入其中，关闭后焦点能回到触发该 modal 的元素上。项目用的是 React Native，TalkBack 和 VoiceOver 两端的表现都要保持一致。</v>
-      </c>
-      <c r="K94" t="str">
         <v/>
       </c>
     </row>
@@ -3709,33 +3426,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>q_scene_022_004</v>
+        <v>q_scene_027_002</v>
       </c>
       <c r="C95" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D95" t="str">
-        <v>无障碍辅助</v>
+        <v>课程目录/课堂界面</v>
       </c>
       <c r="E95" t="str">
-        <v>Color-blind mode with palette simulation preview</v>
+        <v>Instructor profile with credential and ratings</v>
       </c>
       <c r="F95" t="str">
         <v>medium</v>
       </c>
       <c r="G95">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="H95">
-        <v>71515</v>
+        <v>0</v>
       </c>
       <c r="I95" t="str">
-        <v>Add a color-blind mode feature to the accessibility settings screen — users should be able to toggle between the main types (deuteranopia, protanopia, tritanopia) and see a live palette preview that simulates how the app's primary color scheme looks under each mode. The preview should show a small swatch grid of the app's key UI colors transformed in real time as they switch types, and the selected mode should persist across sessions. Keep the toggle and preview section compact enough to fit cleanly in a single settings card without scrolling.</v>
+        <v>[DRY-RUN] Instructor profile with credential and ratings — medium</v>
       </c>
       <c r="J95" t="str">
-        <v>在无障碍设置页面新增色盲模式功能——用户可以在几种主要类型（绿色盲、红色盲、蓝黄色盲）之间自由切换，同时通过实时调色板预览查看应用主色方案在各模式下的模拟效果。预览区域需展示一个小色块网格，在用户切换类型时实时呈现应用核心 UI 颜色的变化；已选模式应跨会话持久保存。切换控件与预览区域整体要保持紧凑，能在单个设置卡片内完整展示，不出现滚动条。</v>
-      </c>
-      <c r="K95" t="str">
         <v/>
       </c>
     </row>
@@ -3744,33 +3458,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>q_scene_023_001</v>
+        <v>q_scene_027_003</v>
       </c>
       <c r="C96" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D96" t="str">
-        <v>其他长尾微工具</v>
+        <v>课程目录/课堂界面</v>
       </c>
       <c r="E96" t="str">
-        <v>Parking meter timer with move-car push alert</v>
+        <v>Student discussion board with threaded replies</v>
       </c>
       <c r="F96" t="str">
         <v>medium</v>
       </c>
       <c r="G96">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="H96">
-        <v>72468</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
-        <v>Build a parking meter timer screen for a mobile utility app — user sets a duration (e.g. 1h 30min) using a simple picker or +/- buttons, hits start, and sees a countdown with a big circular progress ring. At 10 minutes remaining, fire a local push notification saying "Time to move your car!" even if the app is backgrounded. Include a quick-extend button (+15 min) on the active timer screen so users can bump the time without restarting. Keep the UI clean and minimal — just the timer, the extend button, and a cancel option.</v>
+        <v>[DRY-RUN] Student discussion board with threaded replies — medium</v>
       </c>
       <c r="J96" t="str">
-        <v>做一个停车计时器页面，用于手机工具类 App。用户通过简单的滚轮选择器或加减按钮设定时长（比如 1 小时 30 分钟），点击开始后，界面显示一个大圆形进度环倒计时。剩余 10 分钟时，触发一条本地推送通知，提示"快去挪车了！"，即使 App 已退到后台也要能正常发出。计时进行中的页面上要有一个快速加时按钮（+15 分钟），让用户不用重新开始就能直接延长时间。整体 UI 保持简洁清爽，页面上只放倒计时、加时按钮和取消选项就好。</v>
-      </c>
-      <c r="K96" t="str">
         <v/>
       </c>
     </row>
@@ -3779,33 +3490,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>q_scene_023_002</v>
+        <v>q_scene_027_004</v>
       </c>
       <c r="C97" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D97" t="str">
-        <v>其他长尾微工具</v>
+        <v>课程目录/课堂界面</v>
       </c>
       <c r="E97" t="str">
-        <v>Noise level decibel meter with peak record</v>
+        <v>Assignment submission portal with rubric view</v>
       </c>
       <c r="F97" t="str">
         <v>medium</v>
       </c>
       <c r="G97">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="H97">
-        <v>134050</v>
+        <v>0</v>
       </c>
       <c r="I97" t="str">
-        <v>Build a decibel meter screen for a utility app — it should show the current noise level in dB with a large animated gauge or bar that responds in real time to the microphone input. There needs to be a peak dB value that gets recorded and displayed separately (something like "Peak: 87 dB") and stays visible until the user taps a reset button. Keep the UI dark-themed with color zones on the meter (green for quiet, yellow for moderate, red for loud).</v>
+        <v>[DRY-RUN] Assignment submission portal with rubric view — medium</v>
       </c>
       <c r="J97" t="str">
-        <v>做一个工具类应用的分贝仪页面——要用一个大号的动态仪表盘或进度条实时显示当前噪音分贝值，数据直接来自麦克风输入。需要单独记录并展示峰值分贝，格式类似"峰值：87 dB"，保持显示直到用户点击重置按钮才清除。整体用深色主题，仪表上要有颜色分区：安静区域显示绿色、中等音量显示黄色、嘈杂时显示红色。</v>
-      </c>
-      <c r="K97" t="str">
         <v/>
       </c>
     </row>
@@ -3814,33 +3522,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>q_scene_023_003</v>
+        <v>q_scene_028_001</v>
       </c>
       <c r="C98" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D98" t="str">
-        <v>其他长尾微工具</v>
+        <v>知识速查/公式表</v>
       </c>
       <c r="E98" t="str">
-        <v>QR code scanner with link history and export</v>
+        <v>Algorithm complexity cheatsheet (Big-O notation)</v>
       </c>
       <c r="F98" t="str">
         <v>medium</v>
       </c>
       <c r="G98">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="H98">
-        <v>9399</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
-        <v>Build a mobile QR code scanner screen that opens the camera full-screen with a scan-frame overlay, then on successful scan shows a bottom sheet with the decoded URL and two action buttons — "Open Link" and "Save to History". The history tab should list past scans with timestamp, favicon if it's a URL, and a long-press context menu for copy/delete. Add an export button that dumps the full history as a CSV file to the device's downloads folder.</v>
+        <v>[DRY-RUN] Algorithm complexity cheatsheet (Big-O notation) — medium</v>
       </c>
       <c r="J98" t="str">
-        <v>做一个手机端二维码扫描页面，打开后全屏调用摄像头，并在画面中叠加一个扫描框。扫描成功后从底部弹出一个 bottom sheet，展示解码出的 URL，并提供"打开链接"和"保存到历史"两个操作按钮。历史记录标签页需列出所有扫描记录，显示时间戳，如果是网址还要带网站图标，同时支持长按呼出右键菜单，提供复制和删除选项。另外要有一个导出按钮，可以把完整的历史记录以 CSV 格式保存到设备的下载文件夹。</v>
-      </c>
-      <c r="K98" t="str">
         <v/>
       </c>
     </row>
@@ -3849,33 +3554,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>q_scene_023_004</v>
+        <v>q_scene_028_002</v>
       </c>
       <c r="C99" t="str">
-        <v>实用工具</v>
+        <v>教育学习</v>
       </c>
       <c r="D99" t="str">
-        <v>其他长尾微工具</v>
+        <v>知识速查/公式表</v>
       </c>
       <c r="E99" t="str">
-        <v>Flashlight with SOS Morse blink mode</v>
+        <v>Financial ratios and interpretation guide</v>
       </c>
       <c r="F99" t="str">
         <v>medium</v>
       </c>
       <c r="G99">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="H99">
-        <v>9625</v>
+        <v>0</v>
       </c>
       <c r="I99" t="str">
-        <v>Build a flashlight screen for a mobile utility app — needs a big centered toggle button to turn the torch on/off, plus a dedicated SOS mode button that triggers the standard Morse code blink pattern (3 short, 3 long, 3 short) using the device flash. The SOS blink should loop continuously until the user taps stop, and while it's running the toggle button should be disabled/grayed out so they can't conflict. Keep the UI dark-themed with minimal chrome — just the two controls and maybe a small status label showing "ON / OFF / SOS Active".</v>
+        <v>[DRY-RUN] Financial ratios and interpretation guide — medium</v>
       </c>
       <c r="J99" t="str">
-        <v>做一个手电筒页面，用于移动端工具类应用——需要一个居中的大号切换按钮来开关手电筒，另外还要有一个专门的 SOS 模式按钮，点击后通过设备闪光灯触发标准摩斯密码闪烁（三短三长三短）。SOS 闪烁要持续循环，直到用户点击停止为止，期间主切换按钮需要变灰禁用，防止两者冲突。整体走深色主题风格，界面尽量简洁，只保留这两个控件，加一个小状态标签显示"开启 / 关闭 / SOS 进行中"就够了。</v>
-      </c>
-      <c r="K99" t="str">
         <v/>
       </c>
     </row>
@@ -3884,33 +3586,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>q_scene_024_001</v>
+        <v>q_scene_028_003</v>
       </c>
       <c r="C100" t="str">
         <v>教育学习</v>
       </c>
       <c r="D100" t="str">
-        <v>闪卡/单词记忆 ★</v>
+        <v>知识速查/公式表</v>
       </c>
       <c r="E100" t="str">
-        <v>English GRE vocabulary with usage sentences</v>
+        <v>Medical drug dosage quick reference table</v>
       </c>
       <c r="F100" t="str">
         <v>medium</v>
       </c>
       <c r="G100">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="H100">
-        <v>7995</v>
+        <v>0</v>
       </c>
       <c r="I100" t="str">
-        <v>Build a flashcard screen for a GRE vocabulary app where each card shows the word on the front and flips to reveal the definition plus two example sentences showing real usage. Cards should support swipe-left to mark as "needs review" and swipe-right to mark as "learned", with a small progress bar at the top showing how many words are done in the current session.</v>
+        <v>[DRY-RUN] Medical drug dosage quick reference table — medium</v>
       </c>
       <c r="J100" t="str">
-        <v>做一个GRE词汇app的单词卡页面，每张卡片正面显示单词，翻转后展示释义以及两个体现实际用法的例句。卡片要支持左滑标记为"待复习"、右滑标记为"已掌握"，页面顶部放一个小进度条，显示本轮学习中已完成的单词数。</v>
-      </c>
-      <c r="K100" t="str">
         <v/>
       </c>
     </row>
@@ -3919,33 +3618,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>q_scene_024_002</v>
+        <v>q_scene_028_004</v>
       </c>
       <c r="C101" t="str">
         <v>教育学习</v>
       </c>
       <c r="D101" t="str">
-        <v>闪卡/单词记忆 ★</v>
+        <v>知识速查/公式表</v>
       </c>
       <c r="E101" t="str">
-        <v>Japanese kanji stroke order flashcard</v>
+        <v>Cooking temperature and conversion guide</v>
       </c>
       <c r="F101" t="str">
         <v>medium</v>
       </c>
       <c r="G101">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="H101">
-        <v>14562</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
-        <v>Build a flashcard screen for Japanese kanji stroke order practice — each card should show the kanji on the front, and on flip, display an animated stroke-by-stroke drawing sequence with numbered stroke indicators. Include a swipe-right/swipe-left gesture for known/unknown sorting, and a small progress bar at the top showing how many cards are left in the deck. Keep the card design clean with a white card on a soft neutral background, and make sure the stroke animation can be replayed by tapping the kanji.</v>
+        <v>[DRY-RUN] Cooking temperature and conversion guide — medium</v>
       </c>
       <c r="J101" t="str">
-        <v>做一个练习日语汉字笔顺的闪卡页面——每张卡片正面显示汉字，翻转后展示逐笔动态绘制的笔顺动画，并带有笔画编号标注。支持向右滑动标记"已掌握"、向左滑动标记"未掌握"的手势操作，顶部显示一个小进度条，表示当前牌组还剩多少张卡片。卡片设计保持简洁，白色卡片搭配柔和的中性色背景，点击汉字可以重新播放笔顺动画。</v>
-      </c>
-      <c r="K101" t="str">
         <v/>
       </c>
     </row>
@@ -3954,33 +3650,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>q_scene_024_003</v>
+        <v>q_scene_029_001</v>
       </c>
       <c r="C102" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D102" t="str">
-        <v>闪卡/单词记忆 ★</v>
+        <v>待办清单/任务管理 ★</v>
       </c>
       <c r="E102" t="str">
-        <v>Spanish irregular verb conjugation deck</v>
+        <v>Recurring task scheduler with flexible repeat rules</v>
       </c>
       <c r="F102" t="str">
         <v>medium</v>
       </c>
       <c r="G102">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H102">
-        <v>10263</v>
+        <v>0</v>
       </c>
       <c r="I102" t="str">
-        <v>Build a flashcard deck screen for Spanish irregular verb conjugations — each card should show the infinitive on the front and flip to reveal the full conjugation table (yo/tú/él/nosotros/vosotros/ellos) on the back. Include a swipe-right/swipe-left gesture for "got it" vs "needs review", and add a small progress bar at the top showing how many cards are left in the current session. The deck should be filterable by tense (present, preterite, subjunctive at minimum).</v>
+        <v>[DRY-RUN] Recurring task scheduler with flexible repeat rules — medium</v>
       </c>
       <c r="J102" t="str">
-        <v>做一个西班牙语不规则动词变位的闪卡练习界面——每张卡片正面显示动词原形，点击翻转后背面展示完整的变位表（yo/tú/él/nosotros/vosotros/ellos）。支持左右滑动手势，向右滑代表"已掌握"，向左滑代表"需要复习"，并在顶部加一个小进度条，显示当前练习轮次还剩多少张卡片。卡片组要能按时态筛选，至少包含现在时、简单过去时和虚拟式这几个选项。</v>
-      </c>
-      <c r="K102" t="str">
         <v/>
       </c>
     </row>
@@ -3989,33 +3682,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>q_scene_024_004</v>
+        <v>q_scene_029_002</v>
       </c>
       <c r="C103" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D103" t="str">
-        <v>闪卡/单词记忆 ★</v>
+        <v>待办清单/任务管理 ★</v>
       </c>
       <c r="E103" t="str">
-        <v>Medical terminology card for nurses</v>
+        <v>Task dependency chain with critical path view</v>
       </c>
       <c r="F103" t="str">
         <v>medium</v>
       </c>
       <c r="G103">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="H103">
-        <v>12255</v>
+        <v>0</v>
       </c>
       <c r="I103" t="str">
-        <v>Build a flashcard screen for a medical terminology app aimed at nurses. Each card should show the term on the front and flip to reveal the definition, pronunciation guide, and a short clinical usage example on the back. Include a progress bar at the top showing how many cards are left in the deck, and add two buttons at the bottom — "Got it" and "Review again" — to sort cards into learned vs. needs-review piles. Keep the layout clean and readable since nurses might be using this on a quick break.</v>
+        <v>[DRY-RUN] Task dependency chain with critical path view — medium</v>
       </c>
       <c r="J103" t="str">
-        <v>帮我做一个面向护士群体的医学术语记忆卡片界面。每张卡片正面显示术语，点击后翻转到背面，展示该术语的释义、发音指南以及一个简短的临床使用示例。页面顶部要有一个进度条，显示当前牌组还剩多少张卡片未完成。底部放两个按钮——"已掌握"和"再复习一遍"——用来把卡片分别归入"已学会"和"待复习"两个堆里。整体布局要简洁清晰、易于阅读，因为护士们可能是在短暂休息的间隙快速刷卡用的。</v>
-      </c>
-      <c r="K103" t="str">
         <v/>
       </c>
     </row>
@@ -4024,33 +3714,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>q_scene_025_001</v>
+        <v>q_scene_029_003</v>
       </c>
       <c r="C104" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D104" t="str">
-        <v>备考自测/刷题 ★</v>
+        <v>待办清单/任务管理 ★</v>
       </c>
       <c r="E104" t="str">
-        <v>IELTS reading comprehension mock test</v>
+        <v>Team task assignment with workload heatmap</v>
       </c>
       <c r="F104" t="str">
         <v>medium</v>
       </c>
       <c r="G104">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="H104">
-        <v>10638</v>
+        <v>0</v>
       </c>
       <c r="I104" t="str">
-        <v>Build a mobile screen for an IELTS reading comprehension mock test — it should show a passage on the top half with a sticky scrollable area, and the questions below it with multiple choice options (A–D). Include a timer in the top bar counting down from 20 minutes, and a progress indicator showing something like "Question 3 / 14". When the user taps an answer, highlight it immediately and let them move to the next question with a bottom nav button.</v>
+        <v>[DRY-RUN] Team task assignment with workload heatmap — medium</v>
       </c>
       <c r="J104" t="str">
-        <v>做一个雅思阅读理解模拟考试的手机端页面——上半部分展示阅读文章，这块区域固定在屏幕上方、内容可以独立滚动；下半部分显示题目和A到D四个单选选项。顶部栏里放一个从20分钟开始倒计时的计时器，以及类似"第3题 / 共14题"这样的答题进度提示。用户点击某个选项后立即高亮显示该选项，底部放一个导航按钮，点击后跳转到下一题。</v>
-      </c>
-      <c r="K104" t="str">
         <v/>
       </c>
     </row>
@@ -4059,33 +3746,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>q_scene_025_002</v>
+        <v>q_scene_029_004</v>
       </c>
       <c r="C105" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D105" t="str">
-        <v>备考自测/刷题 ★</v>
+        <v>待办清单/任务管理 ★</v>
       </c>
       <c r="E105" t="str">
-        <v>TOEFL listening transcription practice set</v>
+        <v>Deadline countdown with effort estimator</v>
       </c>
       <c r="F105" t="str">
         <v>medium</v>
       </c>
       <c r="G105">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="H105">
-        <v>9759</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
-        <v>Build a TOEFL listening transcription practice screen for a mobile study app. The screen should play an audio clip and show a text input area where users type out what they hear word by word — include a submit button that highlights correctly transcribed words in green and missed or wrong words in red. Add a progress indicator at the top showing which question out of the total set the user is on, and a "replay" button that lets them re-listen up to 3 times before the answer is locked in.</v>
+        <v>[DRY-RUN] Deadline countdown with effort estimator — medium</v>
       </c>
       <c r="J105" t="str">
-        <v>帮我做一个移动端备考应用里的托福听力听写练习页面。页面需要能播放一段音频，同时提供一个文本输入框让用户逐字把听到的内容打出来——提交后要用绿色高亮显示听写正确的单词，用红色标出漏听或写错的部分。页面顶部加一个进度条，显示当前是第几题、共几题；另外加一个"重听"按钮，允许用户最多重听3次，超过次数后答案自动锁定不可修改。</v>
-      </c>
-      <c r="K105" t="str">
         <v/>
       </c>
     </row>
@@ -4094,33 +3778,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>q_scene_025_003</v>
+        <v>q_scene_030_001</v>
       </c>
       <c r="C106" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D106" t="str">
-        <v>备考自测/刷题 ★</v>
+        <v>番茄钟/专注计时 ★</v>
       </c>
       <c r="E106" t="str">
-        <v>SAT math section timed drill simulator</v>
+        <v>90-minute deep work flow block timer</v>
       </c>
       <c r="F106" t="str">
         <v>medium</v>
       </c>
       <c r="G106">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="H106">
-        <v>10286</v>
+        <v>0</v>
       </c>
       <c r="I106" t="str">
-        <v>Build a SAT math timed drill screen for a mobile study app — the UI should show a single question at a time with a countdown timer at the top (38 minutes for the full module, but also support a "quick drill" mode that sets a per-question timer of ~90 seconds). Include a progress bar showing how many questions are left out of 44, answer choice buttons (A–D) that highlight on tap and lock after selection, and a bottom nav with Previous/Next. After the session ends, show a results summary with score, time used, and which questions were skipped or wrong.</v>
+        <v>[DRY-RUN] 90-minute deep work flow block timer — medium</v>
       </c>
       <c r="J106" t="str">
-        <v>做一个移动端备考App里的SAT数学限时刷题界面——每次只展示一道题，顶部有倒计时（完整模块38分钟，同时支持"快速刷题"模式，按题单独计时，每题约90秒）。需要一个进度条显示当前做到第几题、总共44题，答案选项按钮（A–D）点击后高亮并锁定不允许更改，底部导航栏提供上一题和下一题。刷完一整轮后跳转到成绩总结页，展示得分、总用时，以及哪些题被跳过或答错了。</v>
-      </c>
-      <c r="K106" t="str">
         <v/>
       </c>
     </row>
@@ -4129,33 +3810,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>q_scene_025_004</v>
+        <v>q_scene_030_002</v>
       </c>
       <c r="C107" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D107" t="str">
-        <v>备考自测/刷题 ★</v>
+        <v>番茄钟/专注计时 ★</v>
       </c>
       <c r="E107" t="str">
-        <v>GMAT critical reasoning practice questions</v>
+        <v>Team synchronized pomodoro for remote pair</v>
       </c>
       <c r="F107" t="str">
         <v>medium</v>
       </c>
       <c r="G107">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H107">
-        <v>9950</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
-        <v>Build a GMAT critical reasoning practice screen for a mobile study app — show one question at a time with the passage text up top, 5 answer choices below, and a "Submit" button that reveals the correct answer with a brief explanation. Include a progress indicator at the top showing something like "Q 3 / 20" and a bookmark icon so users can save tricky questions for later review.</v>
+        <v>[DRY-RUN] Team synchronized pomodoro for remote pair — medium</v>
       </c>
       <c r="J107" t="str">
-        <v>为移动端备考 App 开发一个 GMAT 批判性推理练习页面——每次只呈现一道题，上方显示题目材料段落，下方排列 5 个答案选项，点击"提交"按钮后显示正确答案并附一段简短解析。在页面顶部加一个做题进度指示器，格式类似"第 3 题 / 共 20 题"，同时提供一个书签图标，让用户可以收藏难题，方便之后回头复习。</v>
-      </c>
-      <c r="K107" t="str">
         <v/>
       </c>
     </row>
@@ -4164,33 +3842,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>q_scene_026_001</v>
+        <v>q_scene_030_003</v>
       </c>
       <c r="C108" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D108" t="str">
-        <v>学习打卡/进度追踪 ★</v>
+        <v>番茄钟/专注计时 ★</v>
       </c>
       <c r="E108" t="str">
-        <v>30-day language learning streak calendar</v>
+        <v>Distraction capture log during focus session</v>
       </c>
       <c r="F108" t="str">
         <v>medium</v>
       </c>
       <c r="G108">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="H108">
-        <v>8729</v>
+        <v>0</v>
       </c>
       <c r="I108" t="str">
-        <v>Build a 30-day language learning streak calendar component for a mobile app — each day should be a small circle or tile that shows either completed, missed, or upcoming state with distinct colors. When a user taps a completed day, show a small popup with what they studied that day (e.g. "15 vocab words"). Include a streak counter at the top that animates when it increments, and if the user breaks their streak, the counter resets but the calendar should still show historical completed days in a faded style so progress isn't completely lost visually.</v>
+        <v>[DRY-RUN] Distraction capture log during focus session — medium</v>
       </c>
       <c r="J108" t="str">
-        <v>帮我做一个移动端的30天语言学习打卡日历组件——每一天用一个小圆圈或方块来表示，分别用不同颜色标识"已完成"、"已中断"和"未到来"三种状态。用户点击某个已完成的日期时，弹出一个小气泡提示，显示当天学了什么内容，比如"背了15个单词"。顶部要有一个连续打卡天数的计数器，数字增加时要有动画效果。如果用户断了打卡记录，计数器归零重置，但日历上历史已完成的天数不要消失，改用半透明或褪色的样式保留下来，让用户能看到自己之前积累的进度。</v>
-      </c>
-      <c r="K108" t="str">
         <v/>
       </c>
     </row>
@@ -4199,33 +3874,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>q_scene_026_002</v>
+        <v>q_scene_030_004</v>
       </c>
       <c r="C109" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D109" t="str">
-        <v>学习打卡/进度追踪 ★</v>
+        <v>番茄钟/专注计时 ★</v>
       </c>
       <c r="E109" t="str">
-        <v>Reading challenge with book count goal ring</v>
+        <v>Weekly pomodoro stats chart by day</v>
       </c>
       <c r="F109" t="str">
         <v>medium</v>
       </c>
       <c r="G109">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="H109">
-        <v>9961</v>
+        <v>0</v>
       </c>
       <c r="I109" t="str">
-        <v>Build a reading challenge screen where users set a yearly book count goal and track progress through an animated ring chart — the ring fills up as they log completed books. Show the current count vs. goal in the center of the ring (e.g. "7 / 24 books"), and below the ring include a scrollable list of logged books with cover thumbnails and finish dates. The ring should animate smoothly when a new book is added, and the color should shift from a muted tone to a vibrant one as the user gets closer to their goal.</v>
+        <v>[DRY-RUN] Weekly pomodoro stats chart by day — medium</v>
       </c>
       <c r="J109" t="str">
-        <v>做一个阅读挑战页面，用户可以设定全年读书目标数量，并通过一个动态环形图表来追踪进度——每记录一本读完的书，环形就会相应填充。环形中央显示当前进度与目标的对比（例如"7 / 24 本"），环形下方是一个可滚动的已读书单列表，每条记录包含书籍封面缩略图和完成日期。每次新增一本书时，环形应有流畅的过渡动画，同时颜色随着完成进度的提升逐渐从低饱和度的暗淡色调过渡到鲜艳明亮的颜色。</v>
-      </c>
-      <c r="K109" t="str">
         <v/>
       </c>
     </row>
@@ -4234,33 +3906,30 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>q_scene_026_003</v>
+        <v>q_scene_031_001</v>
       </c>
       <c r="C110" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D110" t="str">
-        <v>学习打卡/进度追踪 ★</v>
+        <v>日程/倒计时 ★</v>
       </c>
       <c r="E110" t="str">
-        <v>Programming skill-level progress map</v>
+        <v>Shared family or couple calendar</v>
       </c>
       <c r="F110" t="str">
         <v>medium</v>
       </c>
       <c r="G110">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="H110">
-        <v>8683</v>
+        <v>0</v>
       </c>
       <c r="I110" t="str">
-        <v>Build a programming skill-level progress map screen for a mobile learning app. It should show a tree or roadmap layout where each node represents a skill (like Variables, Loops, Functions, OOP, etc.) with a visual indicator of mastery level — something like a fill percentage or colored ring. Nodes should lock/unlock based on prerequisites, and tapping a node opens a small detail sheet showing the skill name, current level, and a "Practice Now" button. Keep it scrollable vertically and make sure completed nodes look visually distinct from locked ones.</v>
+        <v>[DRY-RUN] Shared family or couple calendar — medium</v>
       </c>
       <c r="J110" t="str">
-        <v>帮我做一个移动端编程学习 App 的技能树进度地图页面。布局用树形或路线图的形式，每个节点代表一个技能点，比如变量、循环、函数、面向对象等，节点上要有掌握程度的可视化指示，比如填充进度条或彩色圆环。节点要根据前置依赖来控制解锁和锁定状态，点击节点后从底部弹出一个小面板，显示技能名称、当前等级以及一个"立即练习"按钮。整个页面支持纵向滚动，已完成的节点和锁定节点在视觉上要有明显区别。</v>
-      </c>
-      <c r="K110" t="str">
         <v/>
       </c>
     </row>
@@ -4269,33 +3938,30 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>q_scene_026_004</v>
+        <v>q_scene_031_002</v>
       </c>
       <c r="C111" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D111" t="str">
-        <v>学习打卡/进度追踪 ★</v>
+        <v>日程/倒计时 ★</v>
       </c>
       <c r="E111" t="str">
-        <v>Daily vocabulary streak with XP and level-up</v>
+        <v>Team availability overlay for meeting scheduling</v>
       </c>
       <c r="F111" t="str">
         <v>medium</v>
       </c>
       <c r="G111">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="H111">
-        <v>9063</v>
+        <v>0</v>
       </c>
       <c r="I111" t="str">
-        <v>Build a daily vocabulary streak tracker screen for a mobile learning app — users earn XP for each day they complete their word review, and hitting streak milestones (7, 30, 100 days) triggers a level-up animation with a new badge. The screen should show the current streak count prominently, an XP progress bar toward the next level, and a small calendar-style row showing the last 7 days with filled/empty indicators. Keep the layout tight enough to sit at the top of a home screen as a motivational card.</v>
+        <v>[DRY-RUN] Team availability overlay for meeting scheduling — medium</v>
       </c>
       <c r="J111" t="str">
-        <v>做一个移动端学习应用的每日词汇连续打卡追踪界面——用户每天完成单词复习就能获得经验值，连续打卡达到里程碑天数（7天、30天、100天）时触发升级动画并解锁新徽章。界面需要醒目地展示当前连续天数、一个指向下一等级的经验值进度条，以及一排日历样式的近7天打卡记录（已打卡和未打卡用不同状态标识）。整体布局要足够紧凑，能作为激励卡片放在主页顶部。</v>
-      </c>
-      <c r="K111" t="str">
         <v/>
       </c>
     </row>
@@ -4304,33 +3970,30 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>q_scene_027_001</v>
+        <v>q_scene_031_003</v>
       </c>
       <c r="C112" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D112" t="str">
-        <v>课程目录/课堂界面</v>
+        <v>日程/倒计时 ★</v>
       </c>
       <c r="E112" t="str">
-        <v>Online course chapter list with completion checkmarks</v>
+        <v>Event RSVP tracker with response counter</v>
       </c>
       <c r="F112" t="str">
         <v>medium</v>
       </c>
       <c r="G112">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="H112">
-        <v>12412</v>
+        <v>0</v>
       </c>
       <c r="I112" t="str">
-        <v>Build a mobile course chapter list screen where each chapter row shows a title, a short subtitle or duration, and a checkmark icon on the right that fills in green when the chapter is completed. Tapping a locked chapter should show a subtle lock icon instead of the checkmark. The list should support sections (e.g., "Module 1", "Module 2") with a collapsible header that shows how many chapters in that module are done out of total, like "3/5 completed".</v>
+        <v>[DRY-RUN] Event RSVP tracker with response counter — medium</v>
       </c>
       <c r="J112" t="str">
-        <v>做一个移动端课程章节列表页面，每一行显示章节标题、简短副标题或时长，右侧有一个勾选图标，章节完成后图标变为绿色填充状态。点击已锁定的章节时，右侧应改为显示一个低调的锁形图标，而不是勾选图标。列表需要支持按模块分组（比如"模块一""模块二"），每个分组有一个可折叠的标题栏，显示该模块已完成章节数与总章节数的比例，例如"3/5 已完成"。</v>
-      </c>
-      <c r="K112" t="str">
         <v/>
       </c>
     </row>
@@ -4339,33 +4002,30 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>q_scene_027_002</v>
+        <v>q_scene_031_004</v>
       </c>
       <c r="C113" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D113" t="str">
-        <v>课程目录/课堂界面</v>
+        <v>日程/倒计时 ★</v>
       </c>
       <c r="E113" t="str">
-        <v>Live class lobby with participant list and chat</v>
+        <v>Meeting preparation checklist auto-linked to event</v>
       </c>
       <c r="F113" t="str">
         <v>medium</v>
       </c>
       <c r="G113">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="H113">
-        <v>8650</v>
+        <v>0</v>
       </c>
       <c r="I113" t="str">
-        <v>Build a live class lobby screen for a mobile education app. It should show a participant list on one side (with avatars, names, and a mic/camera status indicator per user) and a live chat panel below or alongside it. The host should have a distinct badge or label. Chat messages need to auto-scroll to the latest entry, and there should be a pinned message area at the top for announcements. Keep the layout usable on smaller phone screens — maybe a tab switch between "Participants" and "Chat" if space is tight.</v>
+        <v>[DRY-RUN] Meeting preparation checklist auto-linked to event — medium</v>
       </c>
       <c r="J113" t="str">
-        <v>帮我做一个移动端教育应用的直播课堂等候室页面。需要在一侧显示参与者列表，每个用户要有头像、名字，以及麦克风和摄像头的状态图标；下方或旁边配一个实时聊天面板。主持人要有明显的徽章或标签加以区分。聊天消息要能自动滚动到最新一条，顶部还需要有一个置顶公告区域。整体布局要在小屏手机上也能正常使用——如果空间不够，可以考虑用"参与者"和"聊天"两个标签页来切换。</v>
-      </c>
-      <c r="K113" t="str">
         <v/>
       </c>
     </row>
@@ -4374,33 +4034,30 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>q_scene_027_003</v>
+        <v>q_scene_032_001</v>
       </c>
       <c r="C114" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D114" t="str">
-        <v>课程目录/课堂界面</v>
+        <v>数据仪表盘/报表 ★</v>
       </c>
       <c r="E114" t="str">
-        <v>Video lesson player with timestamp chapter markers</v>
+        <v>Inventory level and low-stock alert dashboard</v>
       </c>
       <c r="F114" t="str">
         <v>medium</v>
       </c>
       <c r="G114">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H114">
-        <v>8137</v>
+        <v>0</v>
       </c>
       <c r="I114" t="str">
-        <v>Build a mobile video lesson player screen that has a chapter marker timeline below the video — tapping a chapter jumps to that timestamp. The chapter list should show chapter title, duration, and a "completed" checkmark once the user has watched past that section. Keep the player controls minimal (play/pause, seek bar, speed toggle) and show the current chapter name overlaid at the top of the video while it's playing.</v>
+        <v>[DRY-RUN] Inventory level and low-stock alert dashboard — medium</v>
       </c>
       <c r="J114" t="str">
-        <v>做一个移动端视频课程播放页，视频下方有章节标记时间轴，点击某个章节可以直接跳转到对应时间点。章节列表需要显示章节标题、时长，以及用户看完该段内容后自动出现的"已完成"勾选标记。播放器控件保持简洁，只保留播放/暂停、进度条和倍速切换，同时在播放过程中将当前章节名称以悬浮文字的形式覆盖显示在视频顶部。</v>
-      </c>
-      <c r="K114" t="str">
         <v/>
       </c>
     </row>
@@ -4409,33 +4066,30 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>q_scene_027_004</v>
+        <v>q_scene_032_002</v>
       </c>
       <c r="C115" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D115" t="str">
-        <v>课程目录/课堂界面</v>
+        <v>数据仪表盘/报表 ★</v>
       </c>
       <c r="E115" t="str">
-        <v>PDF lecture note viewer with annotation tools</v>
+        <v>Employee attendance and leave balance report</v>
       </c>
       <c r="F115" t="str">
         <v>medium</v>
       </c>
       <c r="G115">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="H115">
-        <v>8380</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
-        <v>Build a PDF lecture note viewer screen for a mobile learning app. It needs a clean full-screen PDF rendering area with a floating toolbar at the bottom that has highlight, underline, and freehand draw tools. Users should be able to tap any annotation to add a text note/comment, and all annotations should be saved per-document. Add a thumbnail strip on the side for quick page navigation, and make sure the toolbar collapses when the user is just scrolling through pages.</v>
+        <v>[DRY-RUN] Employee attendance and leave balance report — medium</v>
       </c>
       <c r="J115" t="str">
-        <v>帮我做一个移动端学习 App 里的 PDF 讲义阅读页面。需要一个干净的全屏 PDF 渲染区域，底部有一个悬浮工具栏，包含高亮、下划线和手写涂鸦工具。用户点击任意批注后可以添加文字备注或评论，所有批注要按文档分别保存。侧边加一个缩略图栏方便快速跳页，另外用户在正常翻页滚动时工具栏要自动收起。</v>
-      </c>
-      <c r="K115" t="str">
         <v/>
       </c>
     </row>
@@ -4444,33 +4098,30 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>q_scene_028_001</v>
+        <v>q_scene_032_003</v>
       </c>
       <c r="C116" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D116" t="str">
-        <v>知识速查/公式表</v>
+        <v>数据仪表盘/报表 ★</v>
       </c>
       <c r="E116" t="str">
-        <v>Math formula cheatsheet (algebra, calculus, geometry)</v>
+        <v>Project health and burn-down chart</v>
       </c>
       <c r="F116" t="str">
         <v>medium</v>
       </c>
       <c r="G116">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H116">
-        <v>9321</v>
+        <v>0</v>
       </c>
       <c r="I116" t="str">
-        <v>Build a math formula cheatsheet screen for a mobile learning app with three tab sections: Algebra, Calculus, and Geometry. Each tab should show a scrollable list of formula cards — each card displays the formula name, the formula itself rendered in a clean monospace or math-style font, and a short one-line description. Add a search bar at the top that filters formulas across all three tabs in real time. Keep the layout minimal and readable, dark background preferred, with subtle category color accents per tab.</v>
+        <v>[DRY-RUN] Project health and burn-down chart — medium</v>
       </c>
       <c r="J116" t="str">
-        <v>为移动端学习应用做一个数学公式速查页面，包含三个标签页：代数、微积分和几何。每个标签页展示一个可滚动的公式卡片列表，每张卡片显示公式名称、用简洁的等宽字体或数学风格字体渲染的公式本身，以及一行简短的说明。顶部加一个搜索栏，可以实时跨三个标签页筛选公式。整体布局保持简洁易读，优先使用深色背景，每个标签页配有对应的细微分类色彩点缀。</v>
-      </c>
-      <c r="K116" t="str">
         <v/>
       </c>
     </row>
@@ -4479,33 +4130,30 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>q_scene_028_002</v>
+        <v>q_scene_032_004</v>
       </c>
       <c r="C117" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D117" t="str">
-        <v>知识速查/公式表</v>
+        <v>数据仪表盘/报表 ★</v>
       </c>
       <c r="E117" t="str">
-        <v>Physics constant and equation reference card</v>
+        <v>Financial P&amp;L monthly summary dashboard</v>
       </c>
       <c r="F117" t="str">
         <v>medium</v>
       </c>
       <c r="G117">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="H117">
-        <v>8857</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
-        <v>Build a physics reference card screen for a mobile study app — it should display commonly used constants (speed of light, Planck's constant, gravitational constant, etc.) alongside key equations grouped by topic (mechanics, electromagnetism, thermodynamics). Each card should show the symbol, full name, value/formula, and SI units. Add a search bar at the top so users can filter by keyword, and make constants vs. equations switchable via a segmented tab. Keep the layout compact and scannable — this is meant for quick lookup during problem-solving, not deep reading.</v>
+        <v>[DRY-RUN] Financial P&amp;L monthly summary dashboard — medium</v>
       </c>
       <c r="J117" t="str">
-        <v>做一个手机学习App里的物理速查卡片页面——要展示常用物理常数（光速、普朗克常数、万有引力常数等），同时按主题分组列出重要公式（力学、电磁学、热力学）。每张卡片上显示符号、全称、数值或公式，以及对应的国际单位制单位。顶部加一个搜索栏，方便用户按关键词筛选内容；用分段选项卡在"常数"和"公式"之间切换。整体布局要紧凑、便于快速扫读——这个页面是给用户解题时随手查数据用的，不是用来慢慢阅读的。</v>
-      </c>
-      <c r="K117" t="str">
         <v/>
       </c>
     </row>
@@ -4514,33 +4162,30 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>q_scene_028_003</v>
+        <v>q_scene_033_001</v>
       </c>
       <c r="C118" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D118" t="str">
-        <v>知识速查/公式表</v>
+        <v>笔记/文档编辑</v>
       </c>
       <c r="E118" t="str">
-        <v>Chemistry reaction types and balancing quick guide</v>
+        <v>Research note with web clip and citation</v>
       </c>
       <c r="F118" t="str">
         <v>medium</v>
       </c>
       <c r="G118">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="H118">
-        <v>10012</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
-        <v>Build a chemistry quick-reference screen for a mobile study app covering the main reaction types — synthesis, decomposition, single/double displacement, combustion — each with a short description and a tappable example equation. Include a balancing guide section with step-by-step rules and a visual "before/after" equation display that highlights which atoms changed count. Use a clean card layout with color-coded reaction type labels, and make sure the equation text renders properly with subscript numbers.</v>
+        <v>[DRY-RUN] Research note with web clip and citation — medium</v>
       </c>
       <c r="J118" t="str">
-        <v>帮我在移动端学习 App 里做一个化学速查页面，涵盖主要反应类型——化合反应、分解反应、单置换/双置换反应、燃烧反应——每种类型附一段简短说明，并提供一个可点击的示例方程式。页面还要有一个配平指南模块，包含分步操作规则，以及一个"配平前/后"方程式的可视化对比展示，高亮标出原子数量发生变化的部分。整体用卡片式布局，反应类型标签用不同颜色区分，方程式中的下标数字要能正确渲染显示。</v>
-      </c>
-      <c r="K118" t="str">
         <v/>
       </c>
     </row>
@@ -4549,33 +4194,30 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>q_scene_028_004</v>
+        <v>q_scene_033_002</v>
       </c>
       <c r="C119" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="D119" t="str">
-        <v>知识速查/公式表</v>
+        <v>笔记/文档编辑</v>
       </c>
       <c r="E119" t="str">
-        <v>Grammar rule and exception summary card</v>
+        <v>Real-time collaborative document editing</v>
       </c>
       <c r="F119" t="str">
         <v>medium</v>
       </c>
       <c r="G119">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="H119">
-        <v>8751</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
-        <v>Build a grammar rule summary card component for a mobile learning app where each card displays the main rule at the top in bold, followed by a structured exceptions section below it with a visually distinct background (like a light yellow or amber tint) so users can clearly tell the exceptions apart from the main rule. The card should support expanding/collapsing the exceptions section via a tap, and include small example sentences for both the rule and each exception. Keep it compact enough to scroll through multiple cards in a list view.</v>
+        <v>[DRY-RUN] Real-time collaborative document editing — medium</v>
       </c>
       <c r="J119" t="str">
-        <v>做一个用于移动端学习应用的语法规则卡片组件，每张卡片顶部以加粗文字显示主要规则，下方是一个"例外情况"区域，用浅黄色或琥珀色背景加以区分，让用户一眼就能区分主规则和例外内容。例外区域支持点击展开或收起，主规则和每条例外下方都要附带简短的例句。整体要足够紧凑，方便在列表页面中上下滑动浏览多张卡片。</v>
-      </c>
-      <c r="K119" t="str">
         <v/>
       </c>
     </row>
@@ -4584,33 +4226,30 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>q_scene_029_001</v>
+        <v>q_scene_033_003</v>
       </c>
       <c r="C120" t="str">
         <v>办公效率</v>
       </c>
       <c r="D120" t="str">
-        <v>待办清单/任务管理 ★</v>
+        <v>笔记/文档编辑</v>
       </c>
       <c r="E120" t="str">
-        <v>GTD inbox capture with weekly review dashboard</v>
+        <v>Note template gallery with one-click apply</v>
       </c>
       <c r="F120" t="str">
         <v>medium</v>
       </c>
       <c r="G120">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="H120">
-        <v>9205</v>
+        <v>0</v>
       </c>
       <c r="I120" t="str">
-        <v>Build a GTD-style inbox capture screen with a quick-add floating button that lets users dump tasks instantly without categorizing them — just a text input with optional voice note. Below that, add a weekly review dashboard section that shows inbox items needing processing, completed tasks grouped by day, and a simple habit streak counter. The review view should have a "Process All" flow where users can swipe each inbox item to assign it a project or defer it. Keep the UI clean and minimal, dark mode by default.</v>
+        <v>[DRY-RUN] Note template gallery with one-click apply — medium</v>
       </c>
       <c r="J120" t="str">
-        <v>做一个GTD风格的收件箱捕捉页面，右下角放一个快速添加的悬浮按钮，让用户能随手把任务丢进去，不用分类——就一个文字输入框，可选录音备注。下面加一个每周回顾的看板区域，展示待处理的收件箱条目、按天分组的已完成任务，以及一个简单的习惯连续打卡计数。回顾视图里要有一个"全部处理"流程，用户可以对每条收件箱任务左右滑动，把它分配到某个项目或者推迟处理。整体UI保持简洁克制，默认深色模式。</v>
-      </c>
-      <c r="K120" t="str">
         <v/>
       </c>
     </row>
@@ -4619,33 +4258,30 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>q_scene_029_002</v>
+        <v>q_scene_033_004</v>
       </c>
       <c r="C121" t="str">
         <v>办公效率</v>
       </c>
       <c r="D121" t="str">
-        <v>待办清单/任务管理 ★</v>
+        <v>笔记/文档编辑</v>
       </c>
       <c r="E121" t="str">
-        <v>Kanban board with custom columns and WIP limits</v>
+        <v>Folder and notebook hierarchy organiser</v>
       </c>
       <c r="F121" t="str">
         <v>medium</v>
       </c>
       <c r="G121">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="H121">
-        <v>8838</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
-        <v>Build a Kanban board screen for the mobile task app where users can create and rename columns (e.g., Backlog, In Progress, Review, Done) and set a WIP limit per column — when the limit is hit, the column header should turn red and block adding more cards until something is moved out. Cards should be draggable between columns with a smooth snap animation, and each card shows the task title, assignee avatar, and due date. Keep the layout horizontally scrollable so users can have up to 6–8 columns without crowding.</v>
+        <v>[DRY-RUN] Folder and notebook hierarchy organiser — medium</v>
       </c>
       <c r="J121" t="str">
-        <v>为移动端任务 App 做一个看板界面，用户可以自由创建和重命名列（比如待办、进行中、审核中、已完成），并且可以给每列单独设置 WIP 上限——当某列卡片数量达到上限时，列标题变红，同时禁止继续添加卡片，直到有卡片被移走为止。卡片支持在各列之间拖拽移动，需要有流畅的吸附动画。每张卡片上展示任务标题、负责人头像和截止日期。整体布局要支持横向滚动，让用户放 6 到 8 列也不会显得拥挤。</v>
-      </c>
-      <c r="K121" t="str">
         <v/>
       </c>
     </row>
@@ -4654,33 +4290,30 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>q_scene_029_003</v>
+        <v>q_scene_034_001</v>
       </c>
       <c r="C122" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D122" t="str">
-        <v>待办清单/任务管理 ★</v>
+        <v>饮水/服药/习惯提醒 ★</v>
       </c>
       <c r="E122" t="str">
-        <v>Eisenhower matrix priority quad view</v>
+        <v>Hydration reminder with interval push notification</v>
       </c>
       <c r="F122" t="str">
         <v>medium</v>
       </c>
       <c r="G122">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="H122">
-        <v>8378</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
-        <v>Build an Eisenhower matrix quad view for the task management app — four quadrants (Urgent+Important, Not Urgent+Important, Urgent+Not Important, Not Urgent+Not Important) displayed in a 2x2 grid that fills the screen. Each quadrant should have a distinct background color and a label at the top, and tasks should appear as small draggable cards inside the correct quadrant. Users need to be able to drag a task card from one quadrant to another to reassign its priority, and tapping a card opens an edit sheet. Keep it mobile-first with enough padding so the cards don't feel cramped on smaller screens.</v>
+        <v>[DRY-RUN] Hydration reminder with interval push notification — medium</v>
       </c>
       <c r="J122" t="str">
-        <v>在任务管理应用里实现一个艾森豪威尔矩阵的四象限视图——四个象限分别是"紧急+重要"、"不紧急+重要"、"紧急+不重要"、"不紧急+不重要"，以 2x2 的网格布局铺满整个屏幕。每个象限要有各自不同的背景色，顶部显示对应标签，任务以小卡片的形式展示在对应象限内，卡片可以拖拽。用户能把任务卡片从一个象限拖到另一个象限来重新分配优先级，点击卡片则弹出编辑面板。整体以移动端优先，确保卡片周围有足够的内边距，在小屏幕上也不会显得拥挤。</v>
-      </c>
-      <c r="K122" t="str">
         <v/>
       </c>
     </row>
@@ -4689,33 +4322,30 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>q_scene_030_001</v>
+        <v>q_scene_034_002</v>
       </c>
       <c r="C123" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D123" t="str">
-        <v>番茄钟/专注计时 ★</v>
+        <v>饮水/服药/习惯提醒 ★</v>
       </c>
       <c r="E123" t="str">
-        <v>Classic 25/5 pomodoro with session count log</v>
+        <v>Pill identification via photo reference</v>
       </c>
       <c r="F123" t="str">
         <v>medium</v>
       </c>
       <c r="G123">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="H123">
-        <v>10235</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
-        <v>Build a classic pomodoro timer screen with the standard 25-minute work / 5-minute break cycle. The main view should show a large circular countdown display, a start/pause/reset button, and a clear label indicating whether it's a work session or break. Below the timer, keep a running session log that shows each completed pomodoro with its start time and session number — so the user can see at a glance how many rounds they've done today. After every 4 sessions, automatically switch to a 15-minute long break instead of the short one.</v>
+        <v>[DRY-RUN] Pill identification via photo reference — medium</v>
       </c>
       <c r="J123" t="str">
-        <v>做一个经典的番茄钟计时器页面，采用标准的25分钟专注／5分钟休息循环。主界面要有一个大圆形倒计时显示区、开始／暂停／重置按钮，以及一个清晰的标签说明当前是专注阶段还是休息阶段。计时器下方保留一个持续更新的会话记录，显示每个已完成番茄钟的开始时间和序号，让用户一眼就能看出今天完成了几轮。每完成4个番茄钟后，自动切换为15分钟的长休息，而不是短休息。</v>
-      </c>
-      <c r="K123" t="str">
         <v/>
       </c>
     </row>
@@ -4724,33 +4354,30 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>q_scene_030_002</v>
+        <v>q_scene_034_003</v>
       </c>
       <c r="C124" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D124" t="str">
-        <v>番茄钟/专注计时 ★</v>
+        <v>饮水/服药/习惯提醒 ★</v>
       </c>
       <c r="E124" t="str">
-        <v>Custom focus/break ratio timer</v>
+        <v>Refill reminder based on days-supply remaining</v>
       </c>
       <c r="F124" t="str">
         <v>medium</v>
       </c>
       <c r="G124">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="H124">
-        <v>12802</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
-        <v>Build a custom focus/break ratio timer screen for a Pomodoro-style productivity app. Users should be able to set any focus-to-break ratio (not just the standard 25/5) using two separate numeric inputs or sliders — something like 45 min focus / 10 min break. The timer display should clearly show which phase is active (focus or break) with a distinct color change between the two states, and there should be a circular progress ring that resets and refills for each phase. Also include a small ratio summary label below the ring showing the current set ratio like "45:10".</v>
+        <v>[DRY-RUN] Refill reminder based on days-supply remaining — medium</v>
       </c>
       <c r="J124" t="str">
-        <v>为番茄钟风格的专注应用构建一个可自定义专注/休息比例的计时器界面。用户可以通过两个独立的数字输入框或滑块自由设置专注与休息的时长比例，不限于标准的25/5分钟，比如45分钟专注搭配10分钟休息。计时器界面需要通过明显的颜色切换来区分当前所处阶段（专注还是休息），同时要有一个圆形进度环，每个阶段切换时自动重置并重新填充。另外在进度环下方加一个小的比例标签，显示当前设定的时长比，比如"45:10"。</v>
-      </c>
-      <c r="K124" t="str">
         <v/>
       </c>
     </row>
@@ -4759,33 +4386,30 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>q_scene_030_003</v>
+        <v>q_scene_034_004</v>
       </c>
       <c r="C125" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D125" t="str">
-        <v>番茄钟/专注计时 ★</v>
+        <v>饮水/服药/习惯提醒 ★</v>
       </c>
       <c r="E125" t="str">
-        <v>Ambient focus sound player integration</v>
+        <v>Side effect and symptom log linked to medication</v>
       </c>
       <c r="F125" t="str">
         <v>medium</v>
       </c>
       <c r="G125">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="H125">
-        <v>9986</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
-        <v>Need to add an ambient sound player to the focus timer screen — things like rain, white noise, café background, etc. The player should sit at the bottom of the screen as a compact persistent bar that doesn't interfere with the timer UI, with a sound selector (horizontal scroll or bottom sheet), a volume slider, and it should auto-pause when the Pomodoro session ends. Also needs to keep playing during the break countdown if the user wants. Any clean approach for managing that audio state alongside the timer state?</v>
+        <v>[DRY-RUN] Side effect and symptom log linked to medication — medium</v>
       </c>
       <c r="J125" t="str">
-        <v>想在专注计时器页面加一个环境音播放器，比如雨声、白噪音、咖啡馆背景音这类。播放器要以一个紧凑的常驻条形式固定在屏幕底部，不能影响计时器主界面，需要有音效选择器（横向滚动或者 bottom sheet 都行）、音量滑块，并且在番茄钟结束时自动暂停。另外如果用户希望休息倒计时阶段也继续播放的话，也要能支持。有什么比较清爽的方案来统一管理音频状态和计时器状态吗？</v>
-      </c>
-      <c r="K125" t="str">
         <v/>
       </c>
     </row>
@@ -4794,33 +4418,30 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>q_scene_031_001</v>
+        <v>q_scene_035_001</v>
       </c>
       <c r="C126" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D126" t="str">
-        <v>日程/倒计时 ★</v>
+        <v>运动记录/健身计划 ★</v>
       </c>
       <c r="E126" t="str">
-        <v>Daily schedule time-block drag-and-drop planner</v>
+        <v>Yoga session flow and pose sequence tracker</v>
       </c>
       <c r="F126" t="str">
         <v>medium</v>
       </c>
       <c r="G126">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="H126">
-        <v>7483</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
-        <v>Build a daily schedule screen with draggable time blocks — each block should snap to 15-minute intervals on a vertical timeline from 6am to midnight. Users can tap to create a new task block, drag to reposition it, and long-press the bottom edge to resize it. Each block should show the task name and duration, and overlapping blocks should highlight in red to warn the user.</v>
+        <v>[DRY-RUN] Yoga session flow and pose sequence tracker — medium</v>
       </c>
       <c r="J126" t="str">
-        <v>做一个每日日程页面，支持可拖拽的时间块——每个时间块在竖向时间轴上按15分钟间隔进行吸附，时间轴从早上6点延伸到午夜。用户可以点击空白区域创建新任务块，拖动来调整位置，长按时间块底部边缘来缩放时长。每个时间块上需要显示任务名称和持续时间，若出现时间块重叠的情况，需用红色高亮来提醒用户。</v>
-      </c>
-      <c r="K126" t="str">
         <v/>
       </c>
     </row>
@@ -4829,33 +4450,30 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>q_scene_031_002</v>
+        <v>q_scene_035_002</v>
       </c>
       <c r="C127" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D127" t="str">
-        <v>日程/倒计时 ★</v>
+        <v>运动记录/健身计划 ★</v>
       </c>
       <c r="E127" t="str">
-        <v>Weekly agenda with event color coding</v>
+        <v>HIIT workout timer with round counter</v>
       </c>
       <c r="F127" t="str">
         <v>medium</v>
       </c>
       <c r="G127">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="H127">
-        <v>11052</v>
+        <v>0</v>
       </c>
       <c r="I127" t="str">
-        <v>Build a weekly agenda view for a mobile scheduling app where each event is color-coded by category (e.g. work, personal, health, travel). The week should display as a horizontal 7-day strip at the top with day labels, and tapping a day scrolls to that day's event list below. Each event card should show a left-side colored bar matching its category, the event title, and time range. Make sure the color assignment is consistent — same category always gets the same color — and include a small legend somewhere accessible, like a filter row just below the day strip.</v>
+        <v>[DRY-RUN] HIIT workout timer with round counter — medium</v>
       </c>
       <c r="J127" t="str">
-        <v>做一个移动端日程 App 的周视图页面，每个日程按分类（比如工作、个人、健康、出行）用不同颜色区分。页面顶部展示一个横向的七天条，带有星期/日期标签，点击某天后下方的日程列表会自动滚动到对应日期的内容。每张日程卡片左侧要有一条与分类颜色一致的彩色竖条，卡片上显示事件标题和时间段。颜色要保持统一，同一分类始终对应同一种颜色，同时在容易看到的地方放一个小图例，比如在七天条正下方加一排分类筛选标签。</v>
-      </c>
-      <c r="K127" t="str">
         <v/>
       </c>
     </row>
@@ -4864,33 +4482,30 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>q_scene_031_003</v>
+        <v>q_scene_035_003</v>
       </c>
       <c r="C128" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D128" t="str">
-        <v>日程/倒计时 ★</v>
+        <v>运动记录/健身计划 ★</v>
       </c>
       <c r="E128" t="str">
-        <v>Recurring meeting schedule with exception handling</v>
+        <v>Gym check-in and personal record log</v>
       </c>
       <c r="F128" t="str">
         <v>medium</v>
       </c>
       <c r="G128">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="H128">
-        <v>8165</v>
+        <v>0</v>
       </c>
       <c r="I128" t="str">
-        <v>Build a recurring meeting scheduler screen for a mobile productivity app — users should be able to set a repeat pattern (daily, weekly, monthly, custom) and then mark specific occurrences as exceptions (skip, reschedule to a different time, or edit just that one instance without affecting the whole series). The UI needs a clear visual distinction between regular occurrences and modified/skipped ones in the schedule list view, and tapping an exception should show what was changed from the original.</v>
+        <v>[DRY-RUN] Gym check-in and personal record log — medium</v>
       </c>
       <c r="J128" t="str">
-        <v>为移动端效率应用做一个周期性会议排程页面——用户可以设置重复规则（每天、每周、每月或自定义），然后对其中某几次单独标记为例外情况（跳过、改到其他时间，或者只修改那一次而不影响整个系列）。在日程列表视图里，普通重复项和被修改过或已跳过的例外项要有明显的视觉区分，点击例外项后要能看到它相对于原始安排具体改了哪些内容。</v>
-      </c>
-      <c r="K128" t="str">
         <v/>
       </c>
     </row>
@@ -4899,33 +4514,30 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>q_scene_032_001</v>
+        <v>q_scene_035_004</v>
       </c>
       <c r="C129" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D129" t="str">
-        <v>数据仪表盘/报表 ★</v>
+        <v>运动记录/健身计划 ★</v>
       </c>
       <c r="E129" t="str">
-        <v>Sales performance KPI real-time dashboard</v>
+        <v>Progressive overload plan with week-over-week compare</v>
       </c>
       <c r="F129" t="str">
         <v>medium</v>
       </c>
       <c r="G129">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="H129">
-        <v>9935</v>
+        <v>0</v>
       </c>
       <c r="I129" t="str">
-        <v>Build a real-time sales KPI dashboard screen for a mobile app — needs to show today's revenue, conversion rate, and deal count at the top as bold metric cards, then a line chart below tracking hourly sales trends for the current day. The data should auto-refresh every 30 seconds with a subtle loading indicator, and each KPI card should have a small percentage badge showing change vs. yesterday. Keep the layout clean and scannable for a sales manager checking numbers on the go.</v>
+        <v>[DRY-RUN] Progressive overload plan with week-over-week compare — medium</v>
       </c>
       <c r="J129" t="str">
-        <v>做一个移动端 App 的实时销售 KPI 看板页面——顶部用加粗的数据卡片分别展示今日营收、转化率和成交量，下方放一个折线图，追踪当天每小时的销售走势。数据每隔 30 秒自动刷新，刷新时显示一个低调的加载提示，每张 KPI 卡片上要有一个小角标，标出与昨日相比的涨跌幅。整体布局要简洁、一目了然，方便销售经理随时随地快速看数。</v>
-      </c>
-      <c r="K129" t="str">
         <v/>
       </c>
     </row>
@@ -4934,33 +4546,30 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>q_scene_032_002</v>
+        <v>q_scene_036_001</v>
       </c>
       <c r="C130" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D130" t="str">
-        <v>数据仪表盘/报表 ★</v>
+        <v>体重/经期/睡眠追踪 ★</v>
       </c>
       <c r="E130" t="str">
-        <v>Website traffic and funnel analytics overview</v>
+        <v>Sleep onset and wake time recorder</v>
       </c>
       <c r="F130" t="str">
         <v>medium</v>
       </c>
       <c r="G130">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="H130">
-        <v>9491</v>
+        <v>0</v>
       </c>
       <c r="I130" t="str">
-        <v>Build a mobile dashboard screen for website traffic and funnel analytics — it should show key metrics at the top (sessions, unique visitors, bounce rate) as summary cards, then a line chart for traffic trends over time with a date range selector (7d / 30d / custom), and below that a funnel visualization showing drop-off rates across stages like Visit → Sign Up → Activation → Purchase. The funnel should display both absolute numbers and conversion percentages between steps. Keep the layout scrollable and optimized for portrait mode on mobile.</v>
+        <v>[DRY-RUN] Sleep onset and wake time recorder — medium</v>
       </c>
       <c r="J130" t="str">
-        <v>做一个移动端的网站流量与漏斗分析仪表盘页面——顶部用摘要卡片展示核心指标（会话数、独立访客数、跳出率），下方是一个带日期范围选择器的流量趋势折线图（支持7天、30天和自定义区间），再往下是一个漏斗图，展示各阶段的流失情况，流程包括访问→注册→激活→购买。漏斗图需要同时显示每个步骤的绝对数量和相邻步骤之间的转化率。整体布局支持滚动，针对手机竖屏模式进行优化。</v>
-      </c>
-      <c r="K130" t="str">
         <v/>
       </c>
     </row>
@@ -4969,33 +4578,30 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>q_scene_032_003</v>
+        <v>q_scene_036_002</v>
       </c>
       <c r="C131" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D131" t="str">
-        <v>数据仪表盘/报表 ★</v>
+        <v>体重/经期/睡眠追踪 ★</v>
       </c>
       <c r="E131" t="str">
-        <v>Social media engagement metrics report</v>
+        <v>Sleep quality score from wearable sync</v>
       </c>
       <c r="F131" t="str">
         <v>medium</v>
       </c>
       <c r="G131">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="H131">
-        <v>8789</v>
+        <v>0</v>
       </c>
       <c r="I131" t="str">
-        <v>Build a social media engagement metrics report screen for the dashboard app. It should show key stats like likes, shares, comments, and reach grouped by platform (Instagram, Twitter, LinkedIn) with a date range filter at the top. Include a line chart for trend over time and a summary card section below it. Keep the layout scrollable and make sure the charts are tap-to-expand for a closer look on mobile.</v>
+        <v>[DRY-RUN] Sleep quality score from wearable sync — medium</v>
       </c>
       <c r="J131" t="str">
-        <v>帮我在 dashboard 应用里做一个社交媒体互动数据报告页面。需要展示点赞、转发、评论和触达人数这几个核心指标，按平台（Instagram、Twitter、LinkedIn）分组显示，顶部有日期范围筛选器。页面里要包含一个折线图来展示数据趋势，折线图下方放汇总数据卡片区域。整体布局要支持滚动，图表在手机上点击后可以放大查看详情。</v>
-      </c>
-      <c r="K131" t="str">
         <v/>
       </c>
     </row>
@@ -5004,33 +4610,30 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>q_scene_033_001</v>
+        <v>q_scene_036_003</v>
       </c>
       <c r="C132" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D132" t="str">
-        <v>笔记/文档编辑</v>
+        <v>体重/经期/睡眠追踪 ★</v>
       </c>
       <c r="E132" t="str">
-        <v>Daily note with auto-date header and tag</v>
+        <v>Cycle irregularity pattern alert</v>
       </c>
       <c r="F132" t="str">
         <v>medium</v>
       </c>
       <c r="G132">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="H132">
-        <v>8085</v>
+        <v>0</v>
       </c>
       <c r="I132" t="str">
-        <v>Build a daily note screen where tapping "New Daily Note" automatically inserts today's date as a bold header (formatted like "Tuesday, May 12 2026") at the top of the editor, and below that adds a pre-filled tag row with a default `#daily` tag that the user can tap to add more tags. The editor should be a plain text area with basic markdown support, and the date header should be read-only so it can't be accidentally deleted.</v>
+        <v>[DRY-RUN] Cycle irregularity pattern alert — medium</v>
       </c>
       <c r="J132" t="str">
-        <v>做一个每日笔记页面，点击"新建每日笔记"后，编辑器顶部自动插入当天日期作为加粗标题（格式类似"Tuesday, May 12 2026"），标题下方有一行预填的标签栏，默认带一个 `#daily` 标签，用户可以点击继续添加更多标签。编辑区域是普通文本框，支持基础 Markdown 语法，日期标题设为只读，避免被误删。</v>
-      </c>
-      <c r="K132" t="str">
         <v/>
       </c>
     </row>
@@ -5039,33 +4642,30 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>q_scene_033_002</v>
+        <v>q_scene_036_004</v>
       </c>
       <c r="C133" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D133" t="str">
-        <v>笔记/文档编辑</v>
+        <v>体重/经期/睡眠追踪 ★</v>
       </c>
       <c r="E133" t="str">
-        <v>Markdown editor with split live preview</v>
+        <v>Pregnancy week-by-week milestone tracker</v>
       </c>
       <c r="F133" t="str">
         <v>medium</v>
       </c>
       <c r="G133">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="H133">
-        <v>8985</v>
+        <v>0</v>
       </c>
       <c r="I133" t="str">
-        <v>Build a split-pane Markdown editor for mobile where the left side is an editable text input and the right side renders the live HTML preview in real time as the user types. The two panes should be scrolled in sync so the preview always tracks the current editing position. Include a toolbar above the editor with quick-insert buttons for common Markdown syntax (bold, italic, heading, code block, link). On smaller screens, add a toggle button to switch between editor-only and preview-only mode since both panes at full width gets cramped.</v>
+        <v>[DRY-RUN] Pregnancy week-by-week milestone tracker — medium</v>
       </c>
       <c r="J133" t="str">
-        <v>做一个移动端的左右分栏 Markdown 编辑器，左栏是可编辑的文本输入区，右栏实时渲染 HTML 预览，用户每输入一个字符预览就同步更新。两个分栏需要保持滚动联动，让预览区始终跟随当前编辑位置。编辑器上方加一排工具栏，提供常用 Markdown 语法的快捷插入按钮，包括加粗、斜体、标题、代码块和链接。在小屏设备上，增加一个切换按钮，让用户可以在纯编辑模式和纯预览模式之间来回切换，因为两栏同时铺满屏幕会太拥挤。</v>
-      </c>
-      <c r="K133" t="str">
         <v/>
       </c>
     </row>
@@ -5074,33 +4674,30 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>q_scene_033_003</v>
+        <v>q_scene_037_001</v>
       </c>
       <c r="C134" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="D134" t="str">
-        <v>笔记/文档编辑</v>
+        <v>健康数据看板</v>
       </c>
       <c r="E134" t="str">
-        <v>Voice-to-text dictation note</v>
+        <v>Sleep quality trend chart by week</v>
       </c>
       <c r="F134" t="str">
         <v>medium</v>
       </c>
       <c r="G134">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="H134">
-        <v>7760</v>
+        <v>0</v>
       </c>
       <c r="I134" t="str">
-        <v>Build a voice dictation screen for a notes app — there should be a large mic button in the center that pulses with an animation while recording, and the transcribed text appears in real-time in a scrollable text area above it. Include a stop/pause toggle and a "Done" button that saves the note. Keep the UI minimal, dark background preferred.</v>
+        <v>[DRY-RUN] Sleep quality trend chart by week — medium</v>
       </c>
       <c r="J134" t="str">
-        <v>帮我做一个笔记应用的语音听写页面——中间放一个大的麦克风按钮，录音时要有脉冲动画效果，上方有一个可滚动的文本区域，实时显示转录出来的文字。需要包含暂停/继续的切换按钮，以及一个保存笔记的"完成"按钮。整体风格尽量简洁，preferably深色背景。</v>
-      </c>
-      <c r="K134" t="str">
         <v/>
       </c>
     </row>
@@ -5109,33 +4706,30 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>q_scene_034_001</v>
+        <v>q_scene_037_002</v>
       </c>
       <c r="C135" t="str">
         <v>健康管理</v>
       </c>
       <c r="D135" t="str">
-        <v>饮水/服药/习惯提醒 ★</v>
+        <v>健康数据看板</v>
       </c>
       <c r="E135" t="str">
-        <v>Daily water intake goal with glass-tap log</v>
+        <v>Nutrition macro balance visual wheel</v>
       </c>
       <c r="F135" t="str">
         <v>medium</v>
       </c>
       <c r="G135">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="H135">
-        <v>8334</v>
+        <v>0</v>
       </c>
       <c r="I135" t="str">
-        <v>Build a daily water intake screen where users set a goal (e.g. 2000ml) and log each glass by tapping a cup icon — each tap adds a fixed amount (250ml default, but user can change it in settings). Show a circular progress ring that fills as they drink, display the current ml vs goal, and keep a scrollable log below with timestamps for each entry so they can delete accidental taps.</v>
+        <v>[DRY-RUN] Nutrition macro balance visual wheel — medium</v>
       </c>
       <c r="J135" t="str">
-        <v>做一个每日饮水记录页面，用户可以自行设置目标饮水量（比如2000ml），每次喝水时点击杯子图标来添加记录——每次点击默认增加250ml，但用户可以在设置里修改这个单次饮水量。页面上用一个圆形进度环来展示当前进度，随着饮水量增加逐渐填满，同时显示已喝毫升数与目标的对比。进度环下方有一个可滚动的饮水记录列表，每条记录带有时间戳，用户可以删除误操作的条目。</v>
-      </c>
-      <c r="K135" t="str">
         <v/>
       </c>
     </row>
@@ -5144,33 +4738,30 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>q_scene_034_002</v>
+        <v>q_scene_037_003</v>
       </c>
       <c r="C136" t="str">
         <v>健康管理</v>
       </c>
       <c r="D136" t="str">
-        <v>饮水/服药/习惯提醒 ★</v>
+        <v>健康数据看板</v>
       </c>
       <c r="E136" t="str">
-        <v>Custom medication schedule with dose reminder</v>
+        <v>Hydration vs energy level correlation chart</v>
       </c>
       <c r="F136" t="str">
         <v>medium</v>
       </c>
       <c r="G136">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="H136">
-        <v>10434</v>
+        <v>0</v>
       </c>
       <c r="I136" t="str">
-        <v>Build a custom medication schedule screen where users can add multiple medications, each with its own name, dosage amount, and frequency (daily, weekly, or custom interval). Each medication entry should support setting specific reminder times throughout the day, and when a reminder fires, show a notification with a snooze option and a "Mark as Taken" button that logs the dose with a timestamp. The schedule overview should display today's upcoming doses in a timeline-style list, with visual indicators for taken, missed, and upcoming statuses.</v>
+        <v>[DRY-RUN] Hydration vs energy level correlation chart — medium</v>
       </c>
       <c r="J136" t="str">
-        <v>做一个自定义用药计划页面，用户可以添加多种药物，每种药物分别设置药品名称、剂量和服药频率（每天、每周或自定义间隔）。每条用药记录支持设置当天多个提醒时间，提醒触发时弹出通知，通知中包含"稍后提醒"选项和"标记为已服药"按钮，点击后记录服药时间戳。计划总览页面以时间轴形式展示今日待服药项，并用不同视觉标识区分已服药、已错过和待服药三种状态。</v>
-      </c>
-      <c r="K136" t="str">
         <v/>
       </c>
     </row>
@@ -5179,33 +4770,30 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>q_scene_034_003</v>
+        <v>q_scene_037_004</v>
       </c>
       <c r="C137" t="str">
         <v>健康管理</v>
       </c>
       <c r="D137" t="str">
-        <v>饮水/服药/习惯提醒 ★</v>
+        <v>健康数据看板</v>
       </c>
       <c r="E137" t="str">
-        <v>Morning routine habit stacker checklist</v>
+        <v>Resting heart rate over-time trend</v>
       </c>
       <c r="F137" t="str">
         <v>medium</v>
       </c>
       <c r="G137">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="H137">
-        <v>8079</v>
+        <v>0</v>
       </c>
       <c r="I137" t="str">
-        <v>Build a morning routine habit stacker checklist screen for a health habit reminder app — each habit item should have a checkbox, a customizable label, and a small streak counter showing consecutive days completed. The list should support drag-to-reorder so users can stack habits in their preferred sequence, and completed items should visually fade or slide to the bottom of the list. Add a progress ring at the top showing how many habits are done out of total for today.</v>
+        <v>[DRY-RUN] Resting heart rate over-time trend — medium</v>
       </c>
       <c r="J137" t="str">
-        <v>帮我做一个健康打卡提醒应用的早晨习惯清单页面——每个习惯条目要有一个复选框、可自定义的标签文字，以及一个显示连续完成天数的小连击计数器。列表需要支持拖拽排序，让用户可以按自己喜欢的顺序排列习惯；已完成的条目要有视觉反馈，比如淡出或滑动到列表底部。页面顶部加一个进度环，显示今天的习惯总数以及已完成的数量。</v>
-      </c>
-      <c r="K137" t="str">
         <v/>
       </c>
     </row>
@@ -5214,33 +4802,30 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>q_scene_035_001</v>
+        <v>q_scene_038_001</v>
       </c>
       <c r="C138" t="str">
         <v>健康管理</v>
       </c>
       <c r="D138" t="str">
-        <v>运动记录/健身计划 ★</v>
+        <v>冥想/呼吸练习</v>
       </c>
       <c r="E138" t="str">
-        <v>Workout session log with sets, reps and weight</v>
+        <v>Visualization and safe-place meditation</v>
       </c>
       <c r="F138" t="str">
         <v>medium</v>
       </c>
       <c r="G138">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="H138">
-        <v>8845</v>
+        <v>0</v>
       </c>
       <c r="I138" t="str">
-        <v>Build a workout session log screen where users can track exercises with sets, reps, and weight per set. Each exercise should have a collapsible card showing a set-by-set table (columns: set number, weight in kg/lbs, reps, and a checkmark to mark it done). There should be an "Add Set" button at the bottom of each card and a floating "Finish Workout" button at the bottom of the screen. Keep the layout compact enough to scroll through multiple exercises without it feeling cluttered.</v>
+        <v>[DRY-RUN] Visualization and safe-place meditation — medium</v>
       </c>
       <c r="J138" t="str">
-        <v>做一个训练记录页面，用户可以在里面记录每个动作的组数、次数和重量。每个动作用一个可折叠的卡片展示，卡片里有一张按组展示的表格，列包括：组号、重量（支持公斤/磅）、次数，以及一个标记该组是否完成的勾选项。每张卡片底部要有一个"添加组数"按钮，页面底部有一个悬浮的"完成训练"按钮。整体布局要紧凑一些，多个动作叠在一起滚动时不要显得太乱。</v>
-      </c>
-      <c r="K138" t="str">
         <v/>
       </c>
     </row>
@@ -5249,33 +4834,30 @@
         <v>138</v>
       </c>
       <c r="B139" t="str">
-        <v>q_scene_035_002</v>
+        <v>q_scene_038_002</v>
       </c>
       <c r="C139" t="str">
         <v>健康管理</v>
       </c>
       <c r="D139" t="str">
-        <v>运动记录/健身计划 ★</v>
+        <v>冥想/呼吸练习</v>
       </c>
       <c r="E139" t="str">
-        <v>Running route and pace GPS tracker</v>
+        <v>Progressive muscle relaxation guide</v>
       </c>
       <c r="F139" t="str">
         <v>medium</v>
       </c>
       <c r="G139">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="H139">
-        <v>8177</v>
+        <v>0</v>
       </c>
       <c r="I139" t="str">
-        <v>Build a GPS running tracker screen that shows the user's live route drawn on a map as they run, with a real-time pace display (min/km) and total distance counter overlaid at the bottom. The map should auto-center and rotate to follow the user's heading. Add a start/pause/stop control bar and when the run ends, show a summary card with average pace, total time, and a static snapshot of the route.</v>
+        <v>[DRY-RUN] Progressive muscle relaxation guide — medium</v>
       </c>
       <c r="J139" t="str">
-        <v>做一个GPS跑步追踪页面，在用户跑步过程中将实时路线动态绘制在地图上，底部叠加显示当前配速（分钟/公里）和累计跑步距离。地图需要自动居中，并根据用户的前进方向实时旋转。页面下方加一个开始、暂停、停止的控制栏，跑步结束后展示一张汇总卡片，内容包括平均配速、总用时以及本次路线的静态截图。</v>
-      </c>
-      <c r="K139" t="str">
         <v/>
       </c>
     </row>
@@ -5284,33 +4866,30 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>q_scene_035_003</v>
+        <v>q_scene_038_003</v>
       </c>
       <c r="C140" t="str">
         <v>健康管理</v>
       </c>
       <c r="D140" t="str">
-        <v>运动记录/健身计划 ★</v>
+        <v>冥想/呼吸练习</v>
       </c>
       <c r="E140" t="str">
-        <v>Cycling ride distance and elevation recorder</v>
+        <v>Box breathing for anxiety relief</v>
       </c>
       <c r="F140" t="str">
         <v>medium</v>
       </c>
       <c r="G140">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="H140">
-        <v>17187</v>
+        <v>0</v>
       </c>
       <c r="I140" t="str">
-        <v>Build a cycling ride tracker screen that records total distance and elevation gain in real time during a ride. The main view should show a large distance counter (in km) at the top, an elevation gain metric below it, and a live route map preview in the middle. Add a start/pause/stop button bar at the bottom — when stopped, it should auto-navigate to a ride summary screen showing distance, elevation, duration, and a mini chart of elevation profile over the route.</v>
+        <v>[DRY-RUN] Box breathing for anxiety relief — medium</v>
       </c>
       <c r="J140" t="str">
-        <v>做一个骑行记录页面，能在骑行过程中实时记录总里程和累计爬升。主界面顶部放一个大号的距离计数器（单位公里），下方显示爬升数据，中间是实时路线地图预览。底部加一排开始／暂停／停止按钮——点击停止后自动跳转到骑行总结页，展示里程、爬升、骑行时长，以及一张沿路线绘制的迷你海拔剖面图。</v>
-      </c>
-      <c r="K140" t="str">
         <v/>
       </c>
     </row>
@@ -5319,33 +4898,30 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>q_scene_036_001</v>
+        <v>q_scene_038_004</v>
       </c>
       <c r="C141" t="str">
         <v>健康管理</v>
       </c>
       <c r="D141" t="str">
-        <v>体重/经期/睡眠追踪 ★</v>
+        <v>冥想/呼吸练习</v>
       </c>
       <c r="E141" t="str">
-        <v>Weight trend graph with goal overlay line</v>
+        <v>Wim Hof breathwork instructor session</v>
       </c>
       <c r="F141" t="str">
         <v>medium</v>
       </c>
       <c r="G141">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="H141">
-        <v>9753</v>
+        <v>0</v>
       </c>
       <c r="I141" t="str">
-        <v>Build a weight trend graph component for a health tracking app where users can see their logged weight entries plotted as a smooth line chart over a selectable time range (7 days, 30 days, 3 months), with a dashed horizontal goal weight line overlaid on the same chart. The goal line should be visually distinct — maybe a different color like green or orange — and include a small label showing the target value. Tapping a data point should show a tooltip with the exact date and weight. Keep the chart clean and minimal, no heavy grid lines.</v>
+        <v>[DRY-RUN] Wim Hof breathwork instructor session — medium</v>
       </c>
       <c r="J141" t="str">
-        <v>帮我做一个健康追踪应用里的体重趋势图组件，用户可以查看自己记录的体重数据，以平滑折线图的形式展示，时间范围可以切换（7天、30天、3个月）。图表上要叠加一条虚线表示目标体重，颜色要和折线有明显区分，比如绿色或橙色，旁边带一个小标签显示目标数值。点击数据点时弹出 tooltip，显示具体日期和对应体重。整体风格要简洁清爽，不要密集的网格线。</v>
-      </c>
-      <c r="K141" t="str">
         <v/>
       </c>
     </row>
@@ -5354,33 +4930,30 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>q_scene_036_002</v>
+        <v>q_scene_039_001</v>
       </c>
       <c r="C142" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D142" t="str">
-        <v>体重/经期/睡眠追踪 ★</v>
+        <v>行程规划器 ★</v>
       </c>
       <c r="E142" t="str">
-        <v>Menstrual cycle calendar with phase prediction</v>
+        <v>Hotel and flight integration with booking links</v>
       </c>
       <c r="F142" t="str">
         <v>medium</v>
       </c>
       <c r="G142">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="H142">
-        <v>9762</v>
+        <v>0</v>
       </c>
       <c r="I142" t="str">
-        <v>Build a menstrual cycle calendar screen for a health tracking app — it should show the current month in a standard calendar grid with color-coded day markers for the different cycle phases (period, fertile window, ovulation day, luteal phase). Based on the user's logged period start/end dates, the app should predict the next cycle and overlay those predicted phase ranges on the calendar. Tapping a day should open a small bottom sheet with the phase name, a short description of what to expect, and a note input field. Keep the color palette soft and feminine but readable.</v>
+        <v>[DRY-RUN] Hotel and flight integration with booking links — medium</v>
       </c>
       <c r="J142" t="str">
-        <v>做一个女性健康追踪应用的月经周期日历页面——用标准日历网格展示当前月份，不同周期阶段（经期、易孕窗口期、排卵日、黄体期）用不同颜色的标记区分。根据用户记录的经期开始和结束日期，自动预测下一个周期，并把预测的各阶段范围叠加显示在日历上。点击某一天时，从底部弹出一个小浮层，显示当前所处阶段的名称、简短说明，以及一个可以输入备注的文本框。整体配色要柔和、有女性气息，同时保证可读性。</v>
-      </c>
-      <c r="K142" t="str">
         <v/>
       </c>
     </row>
@@ -5389,33 +4962,30 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>q_scene_036_003</v>
+        <v>q_scene_039_002</v>
       </c>
       <c r="C143" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D143" t="str">
-        <v>体重/经期/睡眠追踪 ★</v>
+        <v>行程规划器 ★</v>
       </c>
       <c r="E143" t="str">
-        <v>Ovulation window and fertility tracker</v>
+        <v>Local transport option per itinerary leg</v>
       </c>
       <c r="F143" t="str">
         <v>medium</v>
       </c>
       <c r="G143">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="H143">
-        <v>71901</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
-        <v>Build an ovulation window and fertility tracker screen for the period tracking app. The main view should show a horizontal calendar strip that highlights the fertile window days (like days 10–16) in a distinct color — maybe a warm gradient — and marks the predicted ovulation day with a special icon. Below the calendar, add a daily fertility status card that shows the current cycle day, a fertility level indicator (low / medium / peak), and a short tip or note. Also need a small BBT (basal body temperature) log input so users can tap to enter their morning temp, and that data should feed into a mini chart below the status card. Keep the layout clean and scrollable — no crowding.</v>
+        <v>[DRY-RUN] Local transport option per itinerary leg — medium</v>
       </c>
       <c r="J143" t="str">
-        <v>帮我在经期追踪应用里做一个排卵窗口和生育期监测页面。主视图要有一个横向日历条，把易孕窗口（比如第10到16天）用明显的颜色标出来——可以用暖色渐变——同时在预测排卵日上加一个特殊图标。日历下面放一张当日生育状态卡片，显示当前周期天数、受孕概率等级（低／中／高峰）以及一条简短的小提示。还需要一个基础体温记录入口，用户可以点击输入早晨测量的体温，数据要同步反映到状态卡片下方的小折线图里。整体布局要简洁、可滚动，不要显得拥挤。</v>
-      </c>
-      <c r="K143" t="str">
         <v/>
       </c>
     </row>
@@ -5424,33 +4994,30 @@
         <v>143</v>
       </c>
       <c r="B144" t="str">
-        <v>q_scene_037_001</v>
+        <v>q_scene_039_003</v>
       </c>
       <c r="C144" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D144" t="str">
-        <v>健康数据看板</v>
+        <v>行程规划器 ★</v>
       </c>
       <c r="E144" t="str">
-        <v>Daily vitals summary (heart rate, BP, SpO2, temp)</v>
+        <v>Activity and experience booking browser</v>
       </c>
       <c r="F144" t="str">
         <v>medium</v>
       </c>
       <c r="G144">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="H144">
-        <v>8958</v>
+        <v>0</v>
       </c>
       <c r="I144" t="str">
-        <v>Build a daily vitals summary card for the health dashboard that displays heart rate, blood pressure, SpO2, and body temperature in a single scrollable row of metric tiles. Each tile should show the current value, a small trend arrow (up/down/stable compared to yesterday), and a color indicator that turns red when the value is outside a normal range. Tapping a tile should expand an inline mini chart showing the last 24 hours of readings for that metric.</v>
+        <v>[DRY-RUN] Activity and experience booking browser — medium</v>
       </c>
       <c r="J144" t="str">
-        <v>在健康仪表盘里做一个每日生命体征汇总卡片，把心率、血压、SpO2 和体温放在一行可横向滚动的指标磁贴里展示。每个磁贴需要显示当前数值、一个小趋势箭头（与昨天相比标注升高／降低／平稳），以及一个颜色指示器，当数值超出正常范围时自动变红。点击某个磁贴后，要在原位展开一个内联迷你图表，显示该指标过去 24 小时的历史读数。</v>
-      </c>
-      <c r="K144" t="str">
         <v/>
       </c>
     </row>
@@ -5459,33 +5026,30 @@
         <v>144</v>
       </c>
       <c r="B145" t="str">
-        <v>q_scene_037_002</v>
+        <v>q_scene_040_001</v>
       </c>
       <c r="C145" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D145" t="str">
-        <v>健康数据看板</v>
+        <v>打包清单/旅行准备</v>
       </c>
       <c r="E145" t="str">
-        <v>Weekly health score trend overview</v>
+        <v>Reusable saved template with edit and duplicate</v>
       </c>
       <c r="F145" t="str">
         <v>medium</v>
       </c>
       <c r="G145">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="H145">
-        <v>8049</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
-        <v>Build a weekly health score trend overview screen for the health dashboard app. It should show a 7-day line chart with the overall health score per day, and below it a summary row with min/max/average values for the week. The chart should highlight today's point with a distinct color and show a subtle filled area under the line. Keep it mobile-friendly with smooth scroll if the user wants to swipe back to previous weeks.</v>
+        <v>[DRY-RUN] Reusable saved template with edit and duplicate — medium</v>
       </c>
       <c r="J145" t="str">
-        <v>为健康仪表盘应用构建一个每周健康评分趋势总览页面。需要展示一个7天的折线图，显示每天的整体健康评分，图表下方有一行本周数据汇总，包含最小值、最大值和平均值。折线图中今天的数据点要用醒目的颜色高亮显示，折线下方带有淡色填充区域。整体需适配移动端，支持左右滑动查看往周数据，滑动过渡要流畅。</v>
-      </c>
-      <c r="K145" t="str">
         <v/>
       </c>
     </row>
@@ -5494,33 +5058,30 @@
         <v>145</v>
       </c>
       <c r="B146" t="str">
-        <v>q_scene_037_003</v>
+        <v>q_scene_040_002</v>
       </c>
       <c r="C146" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D146" t="str">
-        <v>健康数据看板</v>
+        <v>打包清单/旅行准备</v>
       </c>
       <c r="E146" t="str">
-        <v>Medication adherence rate dashboard</v>
+        <v>Visa and document checklist by destination</v>
       </c>
       <c r="F146" t="str">
         <v>medium</v>
       </c>
       <c r="G146">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="H146">
-        <v>9770</v>
+        <v>0</v>
       </c>
       <c r="I146" t="str">
-        <v>Build a medication adherence rate dashboard screen for a health tracking mobile app. It should show a circular progress indicator for today's adherence percentage, a weekly bar chart breaking down taken vs. missed doses per day, and a list of upcoming medications with their scheduled times. Keep the layout clean and scrollable — the chart and progress ring should be visible above the fold, and missed doses should be visually flagged in red.</v>
+        <v>[DRY-RUN] Visa and document checklist by destination — medium</v>
       </c>
       <c r="J146" t="str">
-        <v>为健康追踪移动应用开发一个服药依从率仪表盘页面。需要有一个圆形进度指示器展示今日的服药依从率百分比，一个按天拆分已服与漏服剂量对比的周柱状图，以及一个列出待服药物和对应计划时间的清单。整体布局保持简洁并支持滚动，柱状图和进度环需在首屏范围内可见，漏服的剂量要用红色进行醒目标注。</v>
-      </c>
-      <c r="K146" t="str">
         <v/>
       </c>
     </row>
@@ -5529,33 +5090,30 @@
         <v>146</v>
       </c>
       <c r="B147" t="str">
-        <v>q_scene_038_001</v>
+        <v>q_scene_040_003</v>
       </c>
       <c r="C147" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D147" t="str">
-        <v>冥想/呼吸练习</v>
+        <v>打包清单/旅行准备</v>
       </c>
       <c r="E147" t="str">
-        <v>Guided body scan relaxation session</v>
+        <v>Travel medication and first-aid kit reminder</v>
       </c>
       <c r="F147" t="str">
         <v>medium</v>
       </c>
       <c r="G147">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="H147">
-        <v>8232</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
-        <v>Build a guided body scan relaxation session screen for a meditation app. The screen should show a simple human body outline that highlights each body part (feet → legs → torso → shoulders → head) in sync with the audio narration, with a soft glow effect on the active region. Include a progress bar at the bottom showing overall session progress, and a floating pause/resume button that doesn't cover the body illustration. Session duration should be configurable (10, 20, or 30 min) via a picker shown before the session starts.</v>
+        <v>[DRY-RUN] Travel medication and first-aid kit reminder — medium</v>
       </c>
       <c r="J147" t="str">
-        <v>为冥想应用开发一个引导式身体扫描放松练习界面。界面中央展示一个简洁的人体轮廓图，随着音频旁白的进度依次高亮对应的身体部位（脚部→腿部→躯干→肩部→头部），当前激活区域需带有柔和的发光效果。底部设置一个整体进度条，显示本次练习的完成进度；同时提供一个悬浮的暂停/继续按钮，位置不得遮挡人体示意图。练习开始前通过一个选择器让用户设定本次时长，可选10分钟、20分钟或30分钟。</v>
-      </c>
-      <c r="K147" t="str">
         <v/>
       </c>
     </row>
@@ -5564,33 +5122,30 @@
         <v>147</v>
       </c>
       <c r="B148" t="str">
-        <v>q_scene_038_002</v>
+        <v>q_scene_041_001</v>
       </c>
       <c r="C148" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D148" t="str">
-        <v>冥想/呼吸练习</v>
+        <v>地图/路线导航</v>
       </c>
       <c r="E148" t="str">
-        <v>4-7-8 breathing technique timer with visual</v>
+        <v>Multi-modal journey planner (walk + metro + bus)</v>
       </c>
       <c r="F148" t="str">
         <v>medium</v>
       </c>
       <c r="G148">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="H148">
-        <v>12109</v>
+        <v>0</v>
       </c>
       <c r="I148" t="str">
-        <v>Build a 4-7-8 breathing timer screen for a meditation app — the user inhales for 4 seconds, holds for 7, exhales for 8. Need an animated circle that expands during inhale, stays full during hold, and contracts during exhale, with a text label showing the current phase and a countdown number inside the circle. Should loop automatically for a set number of cycles (default 4), and show a subtle progress indicator for how many cycles are left. Keep it minimal and calming — dark background, soft glow on the circle.</v>
+        <v>[DRY-RUN] Multi-modal journey planner (walk + metro + bus) — medium</v>
       </c>
       <c r="J148" t="str">
-        <v>做一个冥想 App 里的 4-7-8 呼吸计时器页面——用户吸气 4 秒、屏息 7 秒、呼气 8 秒。需要一个动画圆圈，吸气时缓缓扩大，屏息时保持撑满状态，呼气时再慢慢收缩，圆圈内部显示当前阶段的倒计时数字，并配有文字标注当前处于哪个阶段。完成一轮后自动进入下一轮，默认共循环 4 次，同时用一个低调的进度指示器显示还剩几轮。整体风格要简洁、平静——深色背景，圆圈带柔和的光晕效果。</v>
-      </c>
-      <c r="K148" t="str">
         <v/>
       </c>
     </row>
@@ -5599,33 +5154,30 @@
         <v>148</v>
       </c>
       <c r="B149" t="str">
-        <v>q_scene_038_003</v>
+        <v>q_scene_041_002</v>
       </c>
       <c r="C149" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="D149" t="str">
-        <v>冥想/呼吸练习</v>
+        <v>地图/路线导航</v>
       </c>
       <c r="E149" t="str">
-        <v>Loving-kindness compassion meditation</v>
+        <v>Scenic road trip route alternative</v>
       </c>
       <c r="F149" t="str">
         <v>medium</v>
       </c>
       <c r="G149">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="H149">
-        <v>10480</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
-        <v>Build a Loving-Kindness Compassion Meditation screen for the app — it should have a soft animated pulse (like a gentle heart glow) in the center that syncs with the guided breathing rhythm. The screen needs to cycle through the four classic phrases ("May I be happy", "May I be safe", etc.) with smooth fade transitions, and let the user expand the meditation outward from self → loved ones → strangers → all beings using a simple swipe or tap progression. Keep the UI minimal, warm tones (soft pinks/purples), and make sure the phrase text and the pulse animation stay visually in sync.</v>
+        <v>[DRY-RUN] Scenic road trip route alternative — medium</v>
       </c>
       <c r="J149" t="str">
-        <v>为应用开发一个慈心冥想页面——屏幕中央需要有一个柔和的动态脉冲效果，类似温柔的心形光晕，节奏与引导呼吸保持同步。页面要能循环展示四句经典慈心语（"愿我快乐""愿我平安"等），切换时带有流畅的淡入淡出过渡，同时支持用户通过简单的滑动或点击，将冥想对象由自身逐步向外扩展——自己→亲人→陌生人→所有众生。整体UI保持简洁，色调温暖（柔和的粉色和紫色系），确保文字显示与脉冲动画在视觉上始终保持同步联动。</v>
-      </c>
-      <c r="K149" t="str">
         <v/>
       </c>
     </row>
@@ -5634,33 +5186,30 @@
         <v>149</v>
       </c>
       <c r="B150" t="str">
-        <v>q_scene_039_001</v>
+        <v>q_scene_041_003</v>
       </c>
       <c r="C150" t="str">
         <v>出行助手</v>
       </c>
       <c r="D150" t="str">
-        <v>行程规划器 ★</v>
+        <v>地图/路线导航</v>
       </c>
       <c r="E150" t="str">
-        <v>Day-by-day multi-city itinerary builder</v>
+        <v>Offline map area download and offline navigation</v>
       </c>
       <c r="F150" t="str">
         <v>medium</v>
       </c>
       <c r="G150">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="H150">
-        <v>9293</v>
+        <v>0</v>
       </c>
       <c r="I150" t="str">
-        <v>Build a day-by-day multi-city itinerary builder screen for a travel planner app. The UI should show a horizontal city tab bar at the top so users can switch between cities, and below that a vertical day list where each day has a collapsible card showing time-blocked activities. Users need to be able to drag-reorder activities within a day and tap a "+" button per day to add a new stop. Keep it mobile-first, and make sure the city tabs visually indicate how many days are assigned to each city.</v>
+        <v>[DRY-RUN] Offline map area download and offline navigation — medium</v>
       </c>
       <c r="J150" t="str">
-        <v>帮我做一个旅行规划应用里的多城市按天行程编排界面。页面顶部要有一个横向的城市标签栏，方便用户在不同城市之间切换；下方是按天排列的纵向列表，每一天用一张可折叠卡片展示，卡片里按时间段显示各项活动安排。用户要能在同一天内通过拖拽来调整活动顺序，每天还要有一个"+"按钮用于新增景点或停留地。整体以移动端优先来设计，城市标签上要能直观地看出该城市分配了几天的行程。</v>
-      </c>
-      <c r="K150" t="str">
         <v/>
       </c>
     </row>
@@ -5669,33 +5218,30 @@
         <v>150</v>
       </c>
       <c r="B151" t="str">
-        <v>q_scene_039_002</v>
+        <v>q_scene_042_001</v>
       </c>
       <c r="C151" t="str">
         <v>出行助手</v>
       </c>
       <c r="D151" t="str">
-        <v>行程规划器 ★</v>
+        <v>天气/实时信息查询</v>
       </c>
       <c r="E151" t="str">
-        <v>POI drag-and-drop schedule organiser</v>
+        <v>Air quality index with health recommendation</v>
       </c>
       <c r="F151" t="str">
         <v>medium</v>
       </c>
       <c r="G151">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="H151">
-        <v>11422</v>
+        <v>0</v>
       </c>
       <c r="I151" t="str">
-        <v>Build a drag-and-drop day planner screen where each POI shows up as a card with its name, estimated visit duration, and a small category icon. Users should be able to reorder POIs within a day by long-pressing and dragging, and also drag a card from one day column to another. When a card is dropped, auto-recalculate the travel time gaps between stops and highlight any conflict (like overlapping time slots) in red. Keep the layout scrollable vertically per day column and make sure the drag ghost looks clean — semi-transparent card with a slight drop shadow.</v>
+        <v>[DRY-RUN] Air quality index with health recommendation — medium</v>
       </c>
       <c r="J151" t="str">
-        <v>做一个支持拖拽的行程规划页面，每个景点以卡片形式展示，包含景点名称、预计游览时长和一个小类别图标。用户可以在同一天的列表里长按拖动来调整景点顺序，也可以把卡片从一天的列拖到另一天的列。卡片放下后，自动重新计算各个停靠点之间的交通时间间隔，并将有冲突的地方（比如时间段重叠）用红色高亮标出。每一天的列要支持纵向滚动，拖拽时的浮层要好看一些——半透明卡片加轻微投影效果。</v>
-      </c>
-      <c r="K151" t="str">
         <v/>
       </c>
     </row>
@@ -5704,33 +5250,30 @@
         <v>151</v>
       </c>
       <c r="B152" t="str">
-        <v>q_scene_039_003</v>
+        <v>q_scene_042_002</v>
       </c>
       <c r="C152" t="str">
         <v>出行助手</v>
       </c>
       <c r="D152" t="str">
-        <v>行程规划器 ★</v>
+        <v>天气/实时信息查询</v>
       </c>
       <c r="E152" t="str">
-        <v>Trip budget tracker with per-day spend limit</v>
+        <v>UV index and sun protection timing reminder</v>
       </c>
       <c r="F152" t="str">
         <v>medium</v>
       </c>
       <c r="G152">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="H152">
-        <v>9592</v>
+        <v>0</v>
       </c>
       <c r="I152" t="str">
-        <v>Build a trip budget tracker screen for the travel planner app — users set a total trip budget and a per-day spend limit when creating a trip, then log individual expenses during the trip. The main view should show a daily progress bar that fills up as they add expenses, turns red when they're over the daily limit, and also display a running total vs overall budget at the top. Expense entries need at least a category tag (food, transport, hotel, misc) and an amount field. Keep it to a single scrollable screen with a floating "Add Expense" button.</v>
+        <v>[DRY-RUN] UV index and sun protection timing reminder — medium</v>
       </c>
       <c r="J152" t="str">
-        <v>帮旅行规划应用做一个行程预算追踪页面——用户在新建行程时设置总预算和每日消费上限，行程中可以随时记录单笔支出。主界面顶部显示累计花费与总预算的对比，下方有一个每日进度条，随着支出增加不断填充，超出当日限额后变为红色。每条支出记录至少包含分类标签（餐饮、交通、住宿、其他）和金额输入框。整个页面做成单屏可滚动的布局，右下角放一个悬浮的"添加支出"按钮。</v>
-      </c>
-      <c r="K152" t="str">
         <v/>
       </c>
     </row>
@@ -5739,33 +5282,30 @@
         <v>152</v>
       </c>
       <c r="B153" t="str">
-        <v>q_scene_040_001</v>
+        <v>q_scene_042_003</v>
       </c>
       <c r="C153" t="str">
         <v>出行助手</v>
       </c>
       <c r="D153" t="str">
-        <v>打包清单/旅行准备</v>
+        <v>天气/实时信息查询</v>
       </c>
       <c r="E153" t="str">
-        <v>Smart packing list by destination and forecast weather</v>
+        <v>Pollen count and allergy forecast</v>
       </c>
       <c r="F153" t="str">
         <v>medium</v>
       </c>
       <c r="G153">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="H153">
-        <v>9385</v>
+        <v>0</v>
       </c>
       <c r="I153" t="str">
-        <v>Build a smart packing list screen that auto-generates suggested items based on the user's selected destination and the 7-day weather forecast pulled for that location. The list should be grouped by category (clothing, toiletries, electronics, etc.) and each item should show a small weather-reason tag explaining why it's recommended — like "rain expected Day 3" next to a raincoat. Users should be able to tap to check off items, add custom ones, and remove suggestions they don't need. Keep the UI clean and card-based, with a collapsible section per category and a progress bar at the top showing how much of the list is packed.</v>
+        <v>[DRY-RUN] Pollen count and allergy forecast — medium</v>
       </c>
       <c r="J153" t="str">
-        <v>做一个智能打包清单页面，根据用户选择的目的地和该地7天天气预报自动生成建议携带物品。清单按类别分组（衣物、洗漱用品、电子设备等），每个物品旁边显示一个小标签说明推荐原因，比如雨衣旁边标注"第3天有雨"。用户可以点击勾选物品、手动添加自定义物品，也可以删除不需要的建议项。界面保持简洁的卡片风格，每个类别做成可折叠的分区，顶部用一个进度条显示当前整体打包完成度。</v>
-      </c>
-      <c r="K153" t="str">
         <v/>
       </c>
     </row>
@@ -5774,33 +5314,30 @@
         <v>153</v>
       </c>
       <c r="B154" t="str">
-        <v>q_scene_040_002</v>
+        <v>q_scene_043_001</v>
       </c>
       <c r="C154" t="str">
         <v>出行助手</v>
       </c>
       <c r="D154" t="str">
-        <v>打包清单/旅行准备</v>
+        <v>交通时刻/票价查询</v>
       </c>
       <c r="E154" t="str">
-        <v>Categorized template (clothes, toiletries, docs, tech)</v>
+        <v>Ferry and boat crossing schedule</v>
       </c>
       <c r="F154" t="str">
         <v>medium</v>
       </c>
       <c r="G154">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="H154">
-        <v>11246</v>
+        <v>0</v>
       </c>
       <c r="I154" t="str">
-        <v>Build a packing list template screen with four fixed categories — Clothes, Toiletries, Documents, and Tech — each collapsed into an expandable section with a category icon and item count badge. Each category should have a default set of pre-filled items (e.g., Clothes gets shirt, pants, underwear, socks; Tech gets charger, adapter, earphones) that users can check off or delete, plus an inline "Add item" input at the bottom of each section. Keep the layout scrollable and make sure checked items get a strikethrough style so it's visually clear what's already packed.</v>
+        <v>[DRY-RUN] Ferry and boat crossing schedule — medium</v>
       </c>
       <c r="J154" t="str">
-        <v>做一个行李打包清单的模板页面，固定包含四个分类——衣物、洗漱用品、证件和数码设备——每个分类默认折叠，点击可展开，折叠头部显示对应的分类图标和物品数量角标。每个分类下预置一批默认物品（比如衣物类有衬衫、裤子、内衣、袜子，数码类有充电器、转接头、耳机），用户可以逐项勾选或删除，每个分类底部还要有一个行内"添加物品"的输入框。整体布局要可以滚动，已勾选的物品需要加删除线样式，让用户一眼就能看出哪些东西已经收拾好了。</v>
-      </c>
-      <c r="K154" t="str">
         <v/>
       </c>
     </row>
@@ -5809,33 +5346,30 @@
         <v>154</v>
       </c>
       <c r="B155" t="str">
-        <v>q_scene_040_003</v>
+        <v>q_scene_043_002</v>
       </c>
       <c r="C155" t="str">
         <v>出行助手</v>
       </c>
       <c r="D155" t="str">
-        <v>打包清单/旅行准备</v>
+        <v>交通时刻/票价查询</v>
       </c>
       <c r="E155" t="str">
-        <v>Collaborative list for family or group trip</v>
+        <v>Metro and subway line map with fares</v>
       </c>
       <c r="F155" t="str">
         <v>medium</v>
       </c>
       <c r="G155">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="H155">
-        <v>8501</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
-        <v>Build a collaborative packing list feature for group or family trips — users should be able to create a shared list and invite others via a link or code. Each member gets their own color-coded name tag on items they add, and anyone can check off items as packed. Include a simple role distinction so the trip organizer can lock the list or remove items, while regular members can only add or check off their own.</v>
+        <v>[DRY-RUN] Metro and subway line map with fares — medium</v>
       </c>
       <c r="J155" t="str">
-        <v>帮我做一个适合多人出行或家庭旅行的协作打包清单功能——用户可以创建一个共享清单，通过链接或邀请码把其他人拉进来。每个成员添加的物品上都会显示带颜色标记的名字标签，任何人都可以把物品标记为已打包。权限方面要有简单的角色区分：行程负责人可以锁定清单或删除物品，普通成员只能添加自己的物品或勾选状态。</v>
-      </c>
-      <c r="K155" t="str">
         <v/>
       </c>
     </row>
@@ -5844,33 +5378,30 @@
         <v>155</v>
       </c>
       <c r="B156" t="str">
-        <v>q_scene_041_001</v>
+        <v>q_scene_043_003</v>
       </c>
       <c r="C156" t="str">
         <v>出行助手</v>
       </c>
       <c r="D156" t="str">
-        <v>地图/路线导航</v>
+        <v>交通时刻/票价查询</v>
       </c>
       <c r="E156" t="str">
-        <v>Walking route with accessibility and step-free paths</v>
+        <v>Intercity coach booking and schedule</v>
       </c>
       <c r="F156" t="str">
         <v>medium</v>
       </c>
       <c r="G156">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="H156">
-        <v>9948</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
-        <v>Build a walking route screen that highlights step-free paths and accessibility-friendly options — the map should visually distinguish accessible routes (no stairs, no steep inclines) from regular ones using a different color or icon overlay. Add a toggle at the top of the screen to filter for "wheelchair/step-free only" routes, and when a route is selected, show a details panel at the bottom with info like elevator availability and surface type (paved, gravel, etc.).</v>
+        <v>[DRY-RUN] Intercity coach booking and schedule — medium</v>
       </c>
       <c r="J156" t="str">
-        <v>做一个步行路线页面，重点展示无障碍路径和适合行动不便人士的出行选项——地图上需要用不同颜色或图标叠加层，将无障碍路线（无台阶、无陡坡）与普通路线区分开来。在页面顶部加一个切换开关，用于筛选"仅显示轮椅/无台阶路线"，当用户选中某条路线时，底部弹出详情面板，展示电梯是否可用、路面类型（铺装路面、碎石路等）等信息。</v>
-      </c>
-      <c r="K156" t="str">
         <v/>
       </c>
     </row>
@@ -5879,33 +5410,27 @@
         <v>156</v>
       </c>
       <c r="B157" t="str">
-        <v>q_scene_041_002</v>
+        <v>q_scene_044_001</v>
       </c>
       <c r="C157" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D157" t="str">
-        <v>地图/路线导航</v>
-      </c>
-      <c r="E157" t="str">
-        <v>Cycling route with elevation profile and surface</v>
+        <v>"今天吃什么"随机选择器 ★</v>
       </c>
       <c r="F157" t="str">
         <v>medium</v>
       </c>
       <c r="G157">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="H157">
-        <v>8278</v>
+        <v>0</v>
       </c>
       <c r="I157" t="str">
-        <v>Build a cycling route screen that shows the planned path on a map along with an elevation profile chart at the bottom — the chart should display distance on the x-axis and altitude on the y-axis, and each segment should be color-coded by surface type (asphalt, gravel, dirt, etc.) with a small legend. Tapping a point on the elevation chart should highlight the corresponding location on the map. Keep the chart collapsible so it doesn't block the map when not needed.</v>
+        <v>[DRY-RUN] null — medium</v>
       </c>
       <c r="J157" t="str">
-        <v>做一个骑行路线页面，地图上显示规划好的路径，底部有一个海拔剖面图——图表横轴显示距离，纵轴显示海拔高度，每段路线按路面类型（沥青、碎石、土路等）用不同颜色区分，并附上小图例。点击海拔图上的某个点时，地图上对应的位置要高亮显示。图表支持折叠收起，避免不需要时遮挡地图。</v>
-      </c>
-      <c r="K157" t="str">
         <v/>
       </c>
     </row>
@@ -5914,33 +5439,27 @@
         <v>157</v>
       </c>
       <c r="B158" t="str">
-        <v>q_scene_041_003</v>
+        <v>q_scene_044_002</v>
       </c>
       <c r="C158" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D158" t="str">
-        <v>地图/路线导航</v>
-      </c>
-      <c r="E158" t="str">
-        <v>Public transit step-by-step directions</v>
+        <v>"今天吃什么"随机选择器 ★</v>
       </c>
       <c r="F158" t="str">
         <v>medium</v>
       </c>
       <c r="G158">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="H158">
-        <v>9391</v>
+        <v>0</v>
       </c>
       <c r="I158" t="str">
-        <v>Build a step-by-step transit directions screen for the mobile app — each step should show the transit line name, departure/arrival stop, and estimated time in a vertical card list. Include a sticky header with total trip duration and number of transfers, and highlight the current active step with a distinct accent color. Tapping a step should expand it to show a mini map snippet of that leg.</v>
+        <v>[DRY-RUN] null — medium</v>
       </c>
       <c r="J158" t="str">
-        <v>做一个移动端公共交通逐步导航页面——每个步骤用竖向卡片列表呈现，包含线路名称、上下车站点以及预计用时。顶部设置一个吸顶 header，显示总行程时长和换乘次数，当前进行中的步骤用醒目的强调色高亮标注。点击某个步骤时，展开该卡片并显示这段路程对应的小地图缩略图。</v>
-      </c>
-      <c r="K158" t="str">
         <v/>
       </c>
     </row>
@@ -5949,33 +5468,27 @@
         <v>158</v>
       </c>
       <c r="B159" t="str">
-        <v>q_scene_042_001</v>
+        <v>q_scene_044_003</v>
       </c>
       <c r="C159" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D159" t="str">
-        <v>天气/实时信息查询</v>
-      </c>
-      <c r="E159" t="str">
-        <v>Hourly forecast with precipitation probability bar</v>
+        <v>"今天吃什么"随机选择器 ★</v>
       </c>
       <c r="F159" t="str">
         <v>medium</v>
       </c>
       <c r="G159">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="H159">
-        <v>9281</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
-        <v>Build a horizontal scrollable hourly forecast strip for the weather screen — each hour slot should show the time, a weather icon, temperature, and a small vertical bar indicating precipitation probability (0–100%). The bars should be color-coded so low chance stays light blue and high chance shifts to a deeper blue or purple. Make sure the currently selected hour is highlighted with a subtle background pill, and tapping a slot updates a detail panel below with more info like humidity and wind speed.</v>
+        <v>[DRY-RUN] null — medium</v>
       </c>
       <c r="J159" t="str">
-        <v>做一个天气页面里可以横向滚动的逐小时预报条——每个时间格里要显示时间、天气图标、温度，以及一个表示降水概率（0–100%）的小竖条。竖条要用颜色区分概率高低，概率低时显示浅蓝色，概率高时渐变成深蓝或紫色。当前选中的时间格用一个淡色胶囊形背景高亮显示，点击某个格子后，下方的详情面板同步更新，展示湿度、风速等更多信息。</v>
-      </c>
-      <c r="K159" t="str">
         <v/>
       </c>
     </row>
@@ -5984,33 +5497,30 @@
         <v>159</v>
       </c>
       <c r="B160" t="str">
-        <v>q_scene_042_002</v>
+        <v>q_scene_045_001</v>
       </c>
       <c r="C160" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D160" t="str">
-        <v>天气/实时信息查询</v>
+        <v>食物热量/升糖查询 ★</v>
       </c>
       <c r="E160" t="str">
-        <v>10-day outlook with activity suitability tag</v>
+        <v>Daily calorie budget tracker with meal log</v>
       </c>
       <c r="F160" t="str">
         <v>medium</v>
       </c>
       <c r="G160">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="H160">
-        <v>8497</v>
+        <v>0</v>
       </c>
       <c r="I160" t="str">
-        <v>Build a 10-day weather outlook screen for the travel assistant app — each day card should show the basic forecast (temp range, weather icon, precipitation chance) plus a small activity suitability tag like "Good for hiking", "Avoid outdoor", or "OK for driving". The tags should be color-coded (green/yellow/red) based on conditions. Tapping a day card should expand it to show a brief reason why that tag was assigned. Keep the list scrollable and make sure it works well on mobile portrait layout.</v>
+        <v>[DRY-RUN] Daily calorie budget tracker with meal log — medium</v>
       </c>
       <c r="J160" t="str">
-        <v>帮我在旅行助手 App 里做一个 10 天天气预报页面——每张日期卡片要展示基本天气信息（温度范围、天气图标、降水概率），同时附带一个小的活动适宜性标签，比如"适合徒步"、"不宜外出"、"可以驾车"这类。标签根据天气状况用颜色区分（绿/黄/红）。点击某一天的卡片后，卡片展开显示一段简短说明，解释为什么给出这个标签。整个列表要可以滚动，并且在手机竖屏下显示效果要好。</v>
-      </c>
-      <c r="K160" t="str">
         <v/>
       </c>
     </row>
@@ -6019,33 +5529,30 @@
         <v>160</v>
       </c>
       <c r="B161" t="str">
-        <v>q_scene_042_003</v>
+        <v>q_scene_045_002</v>
       </c>
       <c r="C161" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D161" t="str">
-        <v>天气/实时信息查询</v>
+        <v>食物热量/升糖查询 ★</v>
       </c>
       <c r="E161" t="str">
-        <v>Severe weather alert with push notification</v>
+        <v>Macro split (protein, carb, fat) per 100g</v>
       </c>
       <c r="F161" t="str">
         <v>medium</v>
       </c>
       <c r="G161">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H161">
-        <v>12942</v>
+        <v>0</v>
       </c>
       <c r="I161" t="str">
-        <v>Build a severe weather alert screen for the travel assistant app — when a push notification comes in (typhoon, heavy rain, extreme heat, etc.), tapping it should open a full-screen alert modal with the warning level badge, affected area, and a brief safety tip. The modal should have a red/orange color scheme based on severity and include a dismiss button plus a "View Details" link that goes to the full forecast page. Also wire up the foreground notification handler so if the user is already in the app, a banner slides down from the top instead of triggering the modal.</v>
+        <v>[DRY-RUN] Macro split (protein, carb, fat) per 100g — medium</v>
       </c>
       <c r="J161" t="str">
-        <v>为旅行助手应用开发一个恶劣天气预警页面——当收到推送通知时（台风、暴雨、极端高温等），点击通知应弹出全屏预警弹窗，包含预警等级标签、受影响区域以及简短的安全提示。弹窗的红色/橙色配色方案需根据预警严重程度动态调整，同时提供一个关闭按钮和一个跳转到完整天气预报页面的"查看详情"链接。另外还需要处理前台通知逻辑：如果用户当前已在应用内，则从顶部滑下一条横幅通知，而不是直接触发全屏弹窗。</v>
-      </c>
-      <c r="K161" t="str">
         <v/>
       </c>
     </row>
@@ -6054,33 +5561,30 @@
         <v>161</v>
       </c>
       <c r="B162" t="str">
-        <v>q_scene_043_001</v>
+        <v>q_scene_045_003</v>
       </c>
       <c r="C162" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D162" t="str">
-        <v>交通时刻/票价查询</v>
+        <v>食物热量/升糖查询 ★</v>
       </c>
       <c r="E162" t="str">
-        <v>Train timetable with seat class availability</v>
+        <v>Micronutrient deficiency identifier</v>
       </c>
       <c r="F162" t="str">
         <v>medium</v>
       </c>
       <c r="G162">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="H162">
-        <v>9804</v>
+        <v>0</v>
       </c>
       <c r="I162" t="str">
-        <v>Build a train timetable screen for a mobile travel app that shows departure/arrival times along with real-time seat class availability — things like business class, first class, and second class with remaining ticket counts. Each train row should expand to show the seat breakdown when tapped, and sold-out classes should be visually grayed out. Keep the layout clean and scrollable, designed for a portrait phone screen.</v>
+        <v>[DRY-RUN] Micronutrient deficiency identifier — medium</v>
       </c>
       <c r="J162" t="str">
-        <v>帮我做一个手机旅行应用里的火车时刻表页面，要能显示出发和到达时间，同时实时展示各座位等级的余票情况，比如商务座、一等座、二等座各自剩多少张票。每一行列车点击后可以展开查看座位详情，已售罄的座位等级要灰显处理。整体布局要简洁、支持上下滑动，适配竖屏手机。</v>
-      </c>
-      <c r="K162" t="str">
         <v/>
       </c>
     </row>
@@ -6089,33 +5593,30 @@
         <v>162</v>
       </c>
       <c r="B163" t="str">
-        <v>q_scene_043_002</v>
+        <v>q_scene_046_001</v>
       </c>
       <c r="C163" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D163" t="str">
-        <v>交通时刻/票价查询</v>
+        <v>菜谱生成/食材搭配</v>
       </c>
       <c r="E163" t="str">
-        <v>Bus route stop schedule and real-time arrival</v>
+        <v>Cultural fusion recipe creator</v>
       </c>
       <c r="F163" t="str">
         <v>medium</v>
       </c>
       <c r="G163">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="H163">
-        <v>9651</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
-        <v>Build a bus route detail screen that shows all stops along a selected route in a scrollable list, with each stop displaying the scheduled arrival time and a live countdown badge (e.g. "2 min away") that refreshes every 30 seconds. Highlight the next upcoming stop differently so users can instantly spot where the bus is heading. Also add a small toggle at the top to switch between inbound and outbound directions.</v>
+        <v>[DRY-RUN] Cultural fusion recipe creator — medium</v>
       </c>
       <c r="J163" t="str">
-        <v>做一个公交路线详情页，用可滚动列表展示所选线路的所有站点，每个站点显示预计到站时间，并带有实时倒计时标签（比如"2分钟后到站"），每30秒自动刷新一次。将下一个即将到达的站点用不同样式高亮显示，让用户一眼就能看出公交车当前的行驶位置。页面顶部还需要加一个小切换按钮，用于在上行和下行方向之间切换。</v>
-      </c>
-      <c r="K163" t="str">
         <v/>
       </c>
     </row>
@@ -6124,33 +5625,30 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>q_scene_043_003</v>
+        <v>q_scene_046_002</v>
       </c>
       <c r="C164" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="D164" t="str">
-        <v>交通时刻/票价查询</v>
+        <v>菜谱生成/食材搭配</v>
       </c>
       <c r="E164" t="str">
-        <v>Flight search with lowest-fare calendar view</v>
+        <v>Dietary restriction recipe filter and suggest</v>
       </c>
       <c r="F164" t="str">
         <v>medium</v>
       </c>
       <c r="G164">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="H164">
-        <v>14222</v>
+        <v>0</v>
       </c>
       <c r="I164" t="str">
-        <v>Build a flight search screen with a lowest-fare calendar view — the calendar should display the cheapest available fare for each date directly on the date cell, color-coded by price range (green for cheap, yellow for mid, red for expensive). Tapping a date selects it and updates the flight list below. The search bar at the top should support one-way and round-trip toggle, with origin/destination swap button. Keep it mobile-first with a sticky search header and smooth scroll into the results list.</v>
+        <v>[DRY-RUN] Dietary restriction recipe filter and suggest — medium</v>
       </c>
       <c r="J164" t="str">
-        <v>做一个机票搜索页面，带最低票价日历视图——日历的每个日期格子上直接显示当天最便宜的票价，并按价格区间用颜色区分（便宜的绿色、中等的黄色、贵的红色）。点击某个日期后选中该日，并联动刷新下方的航班列表。顶部搜索栏支持单程/往返切换，提供出发地与目的地一键互换按钮。整体以移动端优先设计，搜索栏吸顶固定，点击日期后平滑滚动至结果列表区域。</v>
-      </c>
-      <c r="K164" t="str">
         <v/>
       </c>
     </row>
@@ -6159,30 +5657,30 @@
         <v>164</v>
       </c>
       <c r="B165" t="str">
-        <v>q_scene_044_001</v>
+        <v>q_scene_046_003</v>
       </c>
       <c r="C165" t="str">
         <v>美食探店</v>
       </c>
       <c r="D165" t="str">
-        <v>"今天吃什么"随机选择器 ★</v>
+        <v>菜谱生成/食材搭配</v>
+      </c>
+      <c r="E165" t="str">
+        <v>Step-by-step cooking instruction with timer</v>
       </c>
       <c r="F165" t="str">
         <v>medium</v>
       </c>
       <c r="G165">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="H165">
-        <v>17457</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
-        <v>Build a "spin to decide" random food picker screen for a mobile app — the main interaction is a big circular wheel that the user flicks to spin, and it lands on a random cuisine type or dish category (like 火锅, 烧烤, 寿司, 粤菜, etc.). After it stops, show a card below the wheel with a suggested nearby restaurant pulled from a mock data list, including the name, a thumbnail, rating stars, and distance. Add a "spin again" button and a "I'll eat this" confirm button that saves the choice to a local history list.</v>
+        <v>[DRY-RUN] Step-by-step cooking instruction with timer — medium</v>
       </c>
       <c r="J165" t="str">
-        <v>做一个移动端的"转盘随机选餐"页面——核心交互是一个大圆形转盘，用户可以拨动它旋转，转盘停下后随机落在某个菜系或餐饮类别上（比如火锅、烧烤、寿司、粤菜之类的）。转盘停止后，在下方展示一张卡片，从模拟数据里推荐一家附近的餐厅，包含餐厅名称、缩略图、星级评分和距离信息。另外需要一个"再转一次"按钮，以及一个"就吃这个"的确认按钮，点击后将本次选择保存到本地历史记录里。</v>
-      </c>
-      <c r="K165" t="str">
         <v/>
       </c>
     </row>
@@ -6191,30 +5689,30 @@
         <v>165</v>
       </c>
       <c r="B166" t="str">
-        <v>q_scene_044_002</v>
+        <v>q_scene_047_001</v>
       </c>
       <c r="C166" t="str">
         <v>美食探店</v>
       </c>
       <c r="D166" t="str">
-        <v>"今天吃什么"随机选择器 ★</v>
+        <v>餐厅列表/点评浏览</v>
+      </c>
+      <c r="E166" t="str">
+        <v>Queue wait time and booking availability</v>
       </c>
       <c r="F166" t="str">
         <v>medium</v>
       </c>
       <c r="G166">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="H166">
-        <v>12548</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
-        <v>Build a "spin to pick" random food selector screen for a mobile food discovery app. The main element should be a large circular spinning wheel divided into 6–8 segments, each showing a food category (like 火锅, 寿司, 炸鸡, 粥, etc.) with a matching color and small icon. When the user taps a central "spin" button, the wheel should animate with a satisfying deceleration ease-out and land on a random segment. After it stops, show a result card sliding up from the bottom with the chosen category name, a brief description, and a "找附近餐厅" CTA button. Keep the overall style clean and appetizing — warm background tones, rounded UI elements, nothing too heavy.</v>
+        <v>[DRY-RUN] Queue wait time and booking availability — medium</v>
       </c>
       <c r="J166" t="str">
-        <v>帮我做一个手机美食探索 App 里的「转盘随机选餐」页面。核心元素是一个大圆形转盘，分成 6 到 8 个扇形区域，每个区域显示一种美食分类（比如火锅、寿司、炸鸡、粥之类的），配上对应的颜色和小图标。用户点击转盘中央的「转」按钮后，转盘要有那种越转越慢、最后缓缓停下来的减速动画，随机落在某个扇形上。停止之后，从底部滑出一张结果卡片，展示选中的分类名称、一段简短介绍，以及一个「找附近餐厅」的 CTA 按钮。整体风格要清爽、有食欲感——暖色系背景、圆角 UI 元素，不要太厚重压抑。</v>
-      </c>
-      <c r="K166" t="str">
         <v/>
       </c>
     </row>
@@ -6223,30 +5721,30 @@
         <v>166</v>
       </c>
       <c r="B167" t="str">
-        <v>q_scene_044_003</v>
+        <v>q_scene_047_002</v>
       </c>
       <c r="C167" t="str">
         <v>美食探店</v>
       </c>
       <c r="D167" t="str">
-        <v>"今天吃什么"随机选择器 ★</v>
+        <v>餐厅列表/点评浏览</v>
+      </c>
+      <c r="E167" t="str">
+        <v>Hidden gem low-traffic recommender</v>
       </c>
       <c r="F167" t="str">
         <v>medium</v>
       </c>
       <c r="G167">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="H167">
-        <v>11552</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
-        <v>Add a "spin the wheel" style random restaurant picker screen — it should animate like a slot machine or roulette wheel cycling through food category icons (ramen, hotpot, BBQ, etc.) before landing on one. After it lands, show a card below with the selected category name, a short description, and a "Find nearby" button. The spin should be triggered by a big centered button and take about 2–3 seconds with an easing slow-down effect at the end.</v>
+        <v>[DRY-RUN] Hidden gem low-traffic recommender — medium</v>
       </c>
       <c r="J167" t="str">
-        <v>做一个"转盘抽奖"风格的随机餐厅选择页面——动画要像老虎机或轮盘赌那样，先快速循环滚动各种美食分类图标（拉面、火锅、烧烤等），最后停在某一个上面。停下来之后，在下方展示一张卡片，包含选中分类的名称、简短描述，以及一个"查找附近"按钮。滚动动画由页面中央一个大按钮触发，整个过程持续约2到3秒，结尾要有缓动减速效果。</v>
-      </c>
-      <c r="K167" t="str">
         <v/>
       </c>
     </row>
@@ -6255,33 +5753,30 @@
         <v>167</v>
       </c>
       <c r="B168" t="str">
-        <v>q_scene_045_001</v>
+        <v>q_scene_047_003</v>
       </c>
       <c r="C168" t="str">
         <v>美食探店</v>
       </c>
       <c r="D168" t="str">
-        <v>食物热量/升糖查询 ★</v>
+        <v>餐厅列表/点评浏览</v>
       </c>
       <c r="E168" t="str">
-        <v>Barcode scan calorie and nutrition lookup</v>
+        <v>Top 10 local specialty dish showcase</v>
       </c>
       <c r="F168" t="str">
         <v>medium</v>
       </c>
       <c r="G168">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="H168">
-        <v>9182</v>
+        <v>0</v>
       </c>
       <c r="I168" t="str">
-        <v>Build a barcode scanner screen for the food calorie lookup app — when the user points the camera at a product barcode, it should auto-detect and scan without needing a button tap, then immediately show a bottom sheet with the food name, calories per serving, and key nutrition stats (carbs, protein, fat, GI index if available). If the barcode isn't found in the database, show a "not found" state with an option to manually search by name instead.</v>
+        <v>[DRY-RUN] Top 10 local specialty dish showcase — medium</v>
       </c>
       <c r="J168" t="str">
-        <v>帮我做一个食物热量查询应用里的条形码扫描页面——用户把摄像头对准商品条形码后，应该能自动识别并完成扫描，不需要手动点按钮，扫描成功后立刻从底部弹出一个bottom sheet，显示食品名称、每份热量以及主要营养数据（碳水、蛋白质、脂肪，如果有的话还要显示GI指数）。如果数据库里查不到这个条形码，就展示一个"未找到"的状态页，并提供一个入口让用户改为按名称手动搜索。</v>
-      </c>
-      <c r="K168" t="str">
         <v/>
       </c>
     </row>
@@ -6290,33 +5785,30 @@
         <v>168</v>
       </c>
       <c r="B169" t="str">
-        <v>q_scene_045_002</v>
+        <v>q_scene_048_001</v>
       </c>
       <c r="C169" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="D169" t="str">
-        <v>食物热量/升糖查询 ★</v>
+        <v>文字猜谜/知识竞赛 ★</v>
       </c>
       <c r="E169" t="str">
-        <v>Restaurant menu nutritional info viewer</v>
+        <v>Anagram unscrambler word challenge</v>
       </c>
       <c r="F169" t="str">
         <v>medium</v>
       </c>
       <c r="G169">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="H169">
-        <v>10251</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
-        <v>Build a restaurant menu nutritional info viewer screen for a food discovery app. Each menu item should show calories, carbs, protein, fat, and a glycemic index indicator (low/medium/high with color coding). Add a collapsible detail panel per item so users can tap to expand full nutrition breakdown without cluttering the list. The top of the screen should have a daily intake summary bar that updates as users log items they plan to eat.</v>
+        <v>[DRY-RUN] Anagram unscrambler word challenge — medium</v>
       </c>
       <c r="J169" t="str">
-        <v>为一款美食探索应用开发餐厅菜单营养信息查看页面。每个菜品需显示热量、碳水化合物、蛋白质、脂肪，以及一个血糖指数标签（低/中/高，用不同颜色区分）。每个菜品下方设置可折叠的详情面板，用户点击后可展开查看完整营养成分明细，避免列表过于拥挤。页面顶部放置一个每日摄入汇总进度条，当用户将菜品加入饮食计划时自动更新数据。</v>
-      </c>
-      <c r="K169" t="str">
         <v/>
       </c>
     </row>
@@ -6325,33 +5817,30 @@
         <v>169</v>
       </c>
       <c r="B170" t="str">
-        <v>q_scene_045_003</v>
+        <v>q_scene_048_002</v>
       </c>
       <c r="C170" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="D170" t="str">
-        <v>食物热量/升糖查询 ★</v>
+        <v>文字猜谜/知识竞赛 ★</v>
       </c>
       <c r="E170" t="str">
-        <v>Glycemic index and glycemic load database</v>
+        <v>Hangman with topic and language selector</v>
       </c>
       <c r="F170" t="str">
         <v>medium</v>
       </c>
       <c r="G170">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="H170">
-        <v>9953</v>
+        <v>0</v>
       </c>
       <c r="I170" t="str">
-        <v>Build a glycemic index and glycemic load database screen for the food lookup section — users should be able to search or browse foods and see both GI and GL values displayed clearly, along with a quick visual indicator (like a color-coded badge: low/medium/high) so it's easy to scan at a glance. The list should support filtering by food category (grains, fruits, dairy, etc.) and tapping a food item should expand a detail card showing serving size, GI score, GL calculation, and a short note on how it affects blood sugar.</v>
+        <v>[DRY-RUN] Hangman with topic and language selector — medium</v>
       </c>
       <c r="J170" t="str">
-        <v>在食物查询模块做一个血糖生成指数（GI）和血糖负荷（GL）的数据库页面——用户可以搜索或浏览食物，清晰地看到每项食物对应的 GI 值和 GL 值，同时配上直观的颜色标签（低/中/高）方便快速扫览。列表需要支持按食物类别筛选（谷物、水果、乳制品等），点击某个食物条目后展开详情卡片，显示建议份量、GI 评分、GL 计算结果，以及一段关于该食物如何影响血糖的简短说明。</v>
-      </c>
-      <c r="K170" t="str">
         <v/>
       </c>
     </row>
@@ -6360,33 +5849,30 @@
         <v>170</v>
       </c>
       <c r="B171" t="str">
-        <v>q_scene_046_001</v>
+        <v>q_scene_048_003</v>
       </c>
       <c r="C171" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="D171" t="str">
-        <v>菜谱生成/食材搭配</v>
+        <v>文字猜谜/知识竞赛 ★</v>
       </c>
       <c r="E171" t="str">
-        <v>Pantry ingredient to recipe generator</v>
+        <v>Daily riddle with timed reveal</v>
       </c>
       <c r="F171" t="str">
         <v>medium</v>
       </c>
       <c r="G171">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H171">
-        <v>11115</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
-        <v>Build a pantry ingredient input screen where users can tap to add ingredients they have on hand — use a tag-style chip UI so ingredients can be added and removed easily. Once they've added at least 3 ingredients, a "Find Recipes" button activates and triggers a recipe results list below, each card showing the recipe name, a thumbnail, how many of the user's ingredients it uses (e.g. "uses 4/5 ingredients"), and a match percentage. Cards with higher match should sort to the top by default.</v>
+        <v>[DRY-RUN] Daily riddle with timed reveal — medium</v>
       </c>
       <c r="J171" t="str">
-        <v>做一个食材库存输入页面，用户可以点击来添加手边现有的食材，用标签式 chip UI 展示，支持随时添加和删除。当已添加至少 3 种食材时，"查找食谱"按钮变为可用状态，点击后在页面下方展示食谱结果列表，每张卡片需显示食谱名称、缩略图、匹配到的食材数量（例如"已匹配 4/5 种食材"）以及匹配度百分比，默认按匹配度从高到低排序。</v>
-      </c>
-      <c r="K171" t="str">
         <v/>
       </c>
     </row>
@@ -6395,33 +5881,30 @@
         <v>171</v>
       </c>
       <c r="B172" t="str">
-        <v>q_scene_046_002</v>
+        <v>q_scene_049_001</v>
       </c>
       <c r="C172" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="D172" t="str">
-        <v>菜谱生成/食材搭配</v>
+        <v>抽签/转盘/随机决策 ★</v>
       </c>
       <c r="E172" t="str">
-        <v>AI week meal plan builder</v>
+        <v>Prize giveaway wheel with custom entries</v>
       </c>
       <c r="F172" t="str">
         <v>medium</v>
       </c>
       <c r="G172">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="H172">
-        <v>9280</v>
+        <v>0</v>
       </c>
       <c r="I172" t="str">
-        <v>Build out the AI weekly meal plan screen — user picks dietary preferences (vegetarian, low-carb, etc.) and number of people, then the AI generates a full 7-day plan with breakfast/lunch/dinner slots. Each meal card should show a thumbnail, estimated cook time, and a tap-to-expand for ingredients. Add a "Regenerate Day" button per row so users can swap out just one day without redoing the whole week.</v>
+        <v>[DRY-RUN] Prize giveaway wheel with custom entries — medium</v>
       </c>
       <c r="J172" t="str">
-        <v>做一个AI智能周餐计划页面——用户可以选择饮食偏好（素食、低碳水等）和用餐人数，然后由AI生成完整的七天计划，包含早餐、午餐和晚餐三个时间段。每张餐食卡片需要显示缩略图、预计烹饪时间，并支持点击展开查看食材详情。每一天的行末加一个"重新生成当天"按钮，让用户可以单独替换某一天的方案，而不必重新生成整周计划。</v>
-      </c>
-      <c r="K172" t="str">
         <v/>
       </c>
     </row>
@@ -6430,33 +5913,30 @@
         <v>172</v>
       </c>
       <c r="B173" t="str">
-        <v>q_scene_047_001</v>
+        <v>q_scene_049_002</v>
       </c>
       <c r="C173" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="D173" t="str">
-        <v>餐厅列表/点评浏览</v>
+        <v>抽签/转盘/随机决策 ★</v>
       </c>
       <c r="E173" t="str">
-        <v>Nearby restaurant map with cuisine filter</v>
+        <v>Secret Santa name draw randomizer</v>
       </c>
       <c r="F173" t="str">
         <v>medium</v>
       </c>
       <c r="G173">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="H173">
-        <v>9779</v>
+        <v>0</v>
       </c>
       <c r="I173" t="str">
-        <v>Build a nearby restaurant map screen where users can see pins on a map view and filter results by cuisine type (e.g. Chinese, Japanese, Italian, etc.) using a horizontally scrollable chip row at the top. Tapping a cuisine chip should update the visible pins in real time without a full page reload. Each pin should show a small thumbnail and rating on tap, and there should be a bottom sheet that slides up with the restaurant list synced to whatever filter is active.</v>
+        <v>[DRY-RUN] Secret Santa name draw randomizer — medium</v>
       </c>
       <c r="J173" t="str">
-        <v>做一个附近餐厅地图页面，地图上显示各餐厅的标记点，顶部放一排可横向滑动的菜系筛选标签（如中餐、日料、意大利菜等）。点击某个菜系标签后，地图上的标记点要实时更新，不能整页刷新。点击标记点时弹出该餐厅的小缩略图和评分。页面底部有一个可上滑展开的 bottom sheet，里面的餐厅列表始终与当前选中的筛选条件保持同步。</v>
-      </c>
-      <c r="K173" t="str">
         <v/>
       </c>
     </row>
@@ -6465,33 +5945,30 @@
         <v>173</v>
       </c>
       <c r="B174" t="str">
-        <v>q_scene_047_002</v>
+        <v>q_scene_049_003</v>
       </c>
       <c r="C174" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="D174" t="str">
-        <v>餐厅列表/点评浏览</v>
+        <v>抽签/转盘/随机决策 ★</v>
       </c>
       <c r="E174" t="str">
-        <v>Review browser with photo-first layout</v>
+        <v>Team pairing random generator</v>
       </c>
       <c r="F174" t="str">
         <v>medium</v>
       </c>
       <c r="G174">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="H174">
-        <v>10753</v>
+        <v>0</v>
       </c>
       <c r="I174" t="str">
-        <v>Build a review browser screen for a restaurant discovery app where photos take center stage — each review card should lead with a large full-width photo (or photo strip if multiple), followed by the star rating, reviewer name, and a truncated text snippet that expands on tap. The list should be vertically scrollable and feel like an Instagram-style feed rather than a traditional text list. Make sure tapping a photo opens a full-screen image viewer with swipe-between support, and include a sticky filter bar at the top for sorting by Most Recent, Highest Rated, and Photos Only.</v>
+        <v>[DRY-RUN] Team pairing random generator — medium</v>
       </c>
       <c r="J174" t="str">
-        <v>帮我做一个餐厅发现类App的评价浏览页面，整体风格要以图片为核心——每张评价卡片最上方放一张大尺寸全宽图（如果有多张图就显示成横向图片条），下面依次是星级评分、用户昵称，以及截断展示的评价文字，点击文字后展开完整内容。列表整体要竖向滚动，视觉感受要像Instagram信息流那种感觉，而不是传统的文字列表。点击图片需要进入全屏图片查看器，支持左右滑动切换。页面顶部要有一个吸顶的筛选栏，提供"最新""评分最高""仅看图片"三种排序或筛选选项。</v>
-      </c>
-      <c r="K174" t="str">
         <v/>
       </c>
     </row>
@@ -6500,33 +5977,30 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>q_scene_048_001</v>
+        <v>q_scene_050_001</v>
       </c>
       <c r="C175" t="str">
         <v>休闲游戏</v>
       </c>
       <c r="D175" t="str">
-        <v>文字猜谜/知识竞赛 ★</v>
+        <v>经典小游戏</v>
       </c>
       <c r="E175" t="str">
-        <v>Daily word guess (Wordle-style) challenge</v>
+        <v>Match-3 color gem cascade game</v>
       </c>
       <c r="F175" t="str">
         <v>medium</v>
       </c>
       <c r="G175">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="H175">
-        <v>9665</v>
+        <v>0</v>
       </c>
       <c r="I175" t="str">
-        <v>Build a daily word-guess screen (Wordle-style) for a mobile casual game — 6 rows × 5 letter tiles, with color-flip animations when the player submits a guess (green = correct position, yellow = wrong position, gray = not in word). Include a on-screen QWERTY keyboard that updates key colors to match the best hint each letter has received so far. There should be a "Daily Challenge" header showing a countdown timer to the next puzzle reset at midnight, and a results modal that pops up on win/loss showing the guess distribution bar chart and a share-result button.</v>
+        <v>[DRY-RUN] Match-3 color gem cascade game — medium</v>
       </c>
       <c r="J175" t="str">
-        <v>做一个手机休闲游戏里的每日猜词界面，Wordle风格——6行×5列字母格，玩家提交猜测后每个格子依次触发翻转变色动画（绿色=位置正确，黄色=字母存在但位置不对，灰色=单词中没有该字母）。下方配一个屏幕虚拟QWERTY键盘，每个按键的颜色根据该字母迄今收到的最佳提示状态同步更新。顶部显示"每日挑战"标题，并带一个倒计时器，实时显示距午夜谜题重置还剩多少时间。游戏结束（胜利或失败）时弹出结果弹窗，展示各猜测轮次的次数分布柱状图，以及一个分享结果的按钮。</v>
-      </c>
-      <c r="K175" t="str">
         <v/>
       </c>
     </row>
@@ -6535,33 +6009,30 @@
         <v>175</v>
       </c>
       <c r="B176" t="str">
-        <v>q_scene_048_002</v>
+        <v>q_scene_050_002</v>
       </c>
       <c r="C176" t="str">
         <v>休闲游戏</v>
       </c>
       <c r="D176" t="str">
-        <v>文字猜谜/知识竞赛 ★</v>
+        <v>经典小游戏</v>
       </c>
       <c r="E176" t="str">
-        <v>Category trivia quiz with difficulty picker</v>
+        <v>Snake path and food pursuit</v>
       </c>
       <c r="F176" t="str">
         <v>medium</v>
       </c>
       <c r="G176">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="H176">
-        <v>9488</v>
+        <v>0</v>
       </c>
       <c r="I176" t="str">
-        <v>Build a category trivia quiz screen for a casual mobile game where users first pick a topic category (e.g. Science, History, Pop Culture, Sports) from a horizontal scroll row of icon+label cards, then select a difficulty level (Easy / Medium / Hard) using a segmented picker that visually highlights the selected tier with a color change. Once both are chosen, a "Start Quiz" button becomes active. The quiz itself should show one question at a time with 4 answer options as tappable cards, a progress bar at the top, and a timer countdown per question. Show instant feedback on tap — green for correct, red for wrong — before auto-advancing to the next question.</v>
+        <v>[DRY-RUN] Snake path and food pursuit — medium</v>
       </c>
       <c r="J176" t="str">
-        <v>做一个休闲手游里的分类知识竞答界面。用户首先从一排可横向滑动的图标+标签卡片中选择题目分类（比如科学、历史、流行文化、体育），然后通过一个分段选择器选择难度（简单 / 普通 / 困难），选中的难度档位要用颜色变化高亮显示。两项都选完之后，「开始答题」按钮才变为可点击状态。答题过程中每次只显示一道题，下方有四个可点击的选项卡片，顶部有进度条，每道题还要有倒计时。点击选项后立即给出反馈——答对显示绿色，答错显示红色，然后自动跳转到下一题。</v>
-      </c>
-      <c r="K176" t="str">
         <v/>
       </c>
     </row>
@@ -6570,33 +6041,30 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>q_scene_049_001</v>
+        <v>q_scene_050_003</v>
       </c>
       <c r="C177" t="str">
         <v>休闲游戏</v>
       </c>
       <c r="D177" t="str">
-        <v>抽签/转盘/随机决策 ★</v>
+        <v>经典小游戏</v>
       </c>
       <c r="E177" t="str">
-        <v>Restaurant choice customizable spin wheel</v>
+        <v>Tetris falling block arrangement</v>
       </c>
       <c r="F177" t="str">
         <v>medium</v>
       </c>
       <c r="G177">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="H177">
-        <v>10016</v>
+        <v>0</v>
       </c>
       <c r="I177" t="str">
-        <v>Build a customizable spin wheel for picking restaurants — users should be able to add, edit, and remove restaurant names from the wheel before spinning. The wheel itself needs smooth spinning animation with a satisfying slowdown effect and a clear pointer/arrow indicator at the top. After the spin lands, show a result popup with the chosen restaurant name and a "Spin Again" button. Keep the wheel segments colored differently so each entry is visually distinct, and make sure the add/edit panel is accessible via a small button below the wheel without cluttering the main screen.</v>
+        <v>[DRY-RUN] Tetris falling block arrangement — medium</v>
       </c>
       <c r="J177" t="str">
-        <v>做一个可自定义的转盘，用来随机选餐厅——用户可以在转动之前自由添加、编辑和删除转盘上的餐厅名称。转盘本身要有流畅的旋转动画，带有令人满足的减速效果，顶部需要有一个清晰的指针或箭头标识。转盘停下后，弹出结果提示框，显示被选中的餐厅名称，并提供一个"再转一次"的按钮。每个扇区用不同颜色区分，让各个选项在视觉上一目了然。添加和编辑餐厅的面板通过转盘下方的一个小按钮打开，不要让主界面显得杂乱。</v>
-      </c>
-      <c r="K177" t="str">
         <v/>
       </c>
     </row>
@@ -6605,33 +6073,30 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>q_scene_049_002</v>
+        <v>q_scene_051_001</v>
       </c>
       <c r="C178" t="str">
         <v>休闲游戏</v>
       </c>
       <c r="D178" t="str">
-        <v>抽签/转盘/随机决策 ★</v>
+        <v>情绪减压/解压玩具</v>
       </c>
       <c r="E178" t="str">
-        <v>Group chore assignment lottery draw</v>
+        <v>Sand drawing table with erase gesture</v>
       </c>
       <c r="F178" t="str">
         <v>medium</v>
       </c>
       <c r="G178">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="H178">
-        <v>10699</v>
+        <v>0</v>
       </c>
       <c r="I178" t="str">
-        <v>Build a group chore assignment lottery screen where users can input a list of household members and a list of chores, then tap a "Draw" button to randomly assign one chore per person with a spinning animation before revealing results. Each person's result should pop in one by one after the spin ends, and there should be a "Reassign" option that lets you re-spin just for a specific person without redoing everyone else.</v>
+        <v>[DRY-RUN] Sand drawing table with erase gesture — medium</v>
       </c>
       <c r="J178" t="str">
-        <v>做一个家庭家务抽签分配页面，用户可以输入家庭成员名单和家务清单，点击「抽签」按钮后触发旋转动画，动画结束后逐一弹出每个人被分配到的家务。每人随机分配一项，结果要一个一个地出现，不能一次全部展示。另外需要一个「重新抽取」功能，可以单独针对某一个人重新转动抽签，不影响其他已经分配好的结果。</v>
-      </c>
-      <c r="K178" t="str">
         <v/>
       </c>
     </row>
@@ -6640,33 +6105,30 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>q_scene_050_001</v>
+        <v>q_scene_051_002</v>
       </c>
       <c r="C179" t="str">
         <v>休闲游戏</v>
       </c>
       <c r="D179" t="str">
-        <v>经典小游戏</v>
+        <v>情绪减压/解压玩具</v>
       </c>
       <c r="E179" t="str">
-        <v>2048 tile merge number puzzle</v>
+        <v>Kinetic sand simulation with finger drag</v>
       </c>
       <c r="F179" t="str">
         <v>medium</v>
       </c>
       <c r="G179">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="H179">
-        <v>10086</v>
+        <v>0</v>
       </c>
       <c r="I179" t="str">
-        <v>Build a 2048 tile merge puzzle game for mobile — 4x4 grid with smooth slide animations when tiles merge, showing the score counter at the top. Tiles should have distinct background colors per number value (2, 4, 8, 16, etc.) and support swipe gestures for all four directions. Include a "New Game" button and a best score tracker stored in localStorage.</v>
+        <v>[DRY-RUN] Kinetic sand simulation with finger drag — medium</v>
       </c>
       <c r="J179" t="str">
-        <v>做一个适合移动端的2048滑块合并益智游戏——4×4网格布局，方块合并时要有流畅的滑动动画，顶部显示当前得分。不同数值的方块（2、4、8、16等）需要有各自对应的背景颜色，并支持四个方向的滑动手势操作。页面上要有一个"新游戏"按钮，同时用localStorage记录并展示历史最高分。</v>
-      </c>
-      <c r="K179" t="str">
         <v/>
       </c>
     </row>
@@ -6675,33 +6137,30 @@
         <v>179</v>
       </c>
       <c r="B180" t="str">
-        <v>q_scene_050_002</v>
+        <v>q_scene_051_003</v>
       </c>
       <c r="C180" t="str">
         <v>休闲游戏</v>
       </c>
       <c r="D180" t="str">
-        <v>经典小游戏</v>
+        <v>情绪减压/解压玩具</v>
       </c>
       <c r="E180" t="str">
-        <v>Minesweeper with difficulty selector</v>
+        <v>Slime stretching and poking toy</v>
       </c>
       <c r="F180" t="str">
         <v>medium</v>
       </c>
       <c r="G180">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="H180">
-        <v>11309</v>
+        <v>0</v>
       </c>
       <c r="I180" t="str">
-        <v>Build a mobile Minesweeper game with a difficulty selector screen that lets users pick between Easy (9×9, 10 mines), Medium (16×16, 40 mines), and Hard (16×30, 99 mines) before starting. The game board should render as a scrollable grid of tappable cells — long press to flag a mine, tap to reveal. Include a top bar showing elapsed time, mine count remaining, and a reset button. The difficulty selector should be a clean card-based UI that you return to when the game ends (win or lose), with a brief result message shown before navigating back.</v>
+        <v>[DRY-RUN] Slime stretching and poking toy — medium</v>
       </c>
       <c r="J180" t="str">
-        <v>做一个手机端的扫雷游戏，进入游戏前先显示一个难度选择界面，让用户在简单（9×9，10个雷）、中等（16×16，40个雷）和困难（16×30，99个雷）三个难度之间选择。游戏棋盘要做成可滚动的网格，每个格子都能点击——长按标记地雷，短按翻开格子。顶部要有一个状态栏，显示已用时间、剩余地雷数和重置按钮。难度选择页用卡片式布局，干净简洁，游戏结束（无论胜负）后跳回该页面，并在返回前短暂展示一条结果提示。</v>
-      </c>
-      <c r="K180" t="str">
         <v/>
       </c>
     </row>
@@ -6710,33 +6169,30 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>q_scene_051_001</v>
+        <v>q_scene_052_001</v>
       </c>
       <c r="C181" t="str">
-        <v>休闲游戏</v>
+        <v>多媒体处理</v>
       </c>
       <c r="D181" t="str">
-        <v>情绪减压/解压玩具</v>
+        <v>图片编辑/滤镜/裁剪</v>
       </c>
       <c r="E181" t="str">
-        <v>Virtual bubble wrap popping sensation</v>
+        <v>Square and story crop with safe zone guide</v>
       </c>
       <c r="F181" t="str">
         <v>medium</v>
       </c>
       <c r="G181">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="H181">
-        <v>11549</v>
+        <v>0</v>
       </c>
       <c r="I181" t="str">
-        <v>Build a virtual bubble wrap screen for a stress-relief mobile app — a grid of soft, rounded bubbles that pop individually when tapped. Each bubble should have a satisfying press animation (slight squish down then a quick burst/deflate) paired with a subtle haptic feedback pulse and a soft "pop" sound effect. Once a bubble is popped it stays flat/deflated so users can work through the whole sheet. Include a "refill" button at the bottom that re-inflates all bubbles with a ripple animation. The grid should be at least 8×12 and feel tactile and responsive, not laggy.</v>
+        <v>[DRY-RUN] Square and story crop with safe zone guide — medium</v>
       </c>
       <c r="J181" t="str">
-        <v>为一款解压应用做一个虚拟气泡膜页面——整张页面是一个由圆润、软乎乎的气泡组成的网格，每颗气泡点击后可以单独戳破。每颗气泡要有爽感十足的按压动画（先轻微下压变形，然后快速爆开/瘪掉），同时配合细腻的触觉震动反馈和一声轻柔的"啵"音效。气泡一旦被戳破就保持扁瘪状态，让用户可以把整张一颗颗戳完。底部加一个"重新充气"按钮，点击后以涟漪扩散的动画把所有气泡重新鼓起来。网格至少要 8×12，整体手感要细腻真实、响应要灵敏，不能有任何卡顿感。</v>
-      </c>
-      <c r="K181" t="str">
         <v/>
       </c>
     </row>
@@ -6745,33 +6201,30 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>q_scene_051_002</v>
+        <v>q_scene_052_002</v>
       </c>
       <c r="C182" t="str">
-        <v>休闲游戏</v>
+        <v>多媒体处理</v>
       </c>
       <c r="D182" t="str">
-        <v>情绪减压/解压玩具</v>
+        <v>图片编辑/滤镜/裁剪</v>
       </c>
       <c r="E182" t="str">
-        <v>Fidget spinner and cube interaction toy</v>
+        <v>Collage builder with template grid layout</v>
       </c>
       <c r="F182" t="str">
         <v>medium</v>
       </c>
       <c r="G182">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="H182">
-        <v>11166</v>
+        <v>0</v>
       </c>
       <c r="I182" t="str">
-        <v>Build a stress-relief toy screen that combines a fidget spinner and a fidget cube in one view. The spinner should be in the center — user can swipe/flick it to spin, with momentum and a satisfying slowdown over time. Below or beside it, add a small cube widget with at least 3 interactive surfaces: a clickable button that clicks, a toggle switch that flips, and a scroll wheel that scrolls. Both toys should have haptic feedback tied to their interactions and some ambient particle or glow effect that reacts to how fast the spinner is going. Keep it all on one screen, no navigation needed.</v>
+        <v>[DRY-RUN] Collage builder with template grid layout — medium</v>
       </c>
       <c r="J182" t="str">
-        <v>做一个解压玩具页面，把指尖陀螺和解压魔方整合在同一个界面里。陀螺放在页面中央，用户可以滑动或轻弹让它转起来，要有惯性效果，转速随时间自然减慢，那种慢慢停下来的感觉要够爽。在陀螺下方或旁边放一个小魔方组件，至少要有3个可交互的面：一个按下去有清脆回馈感的按钮、一个可以拨动的开关，还有一个能滚动的滚轮。两个玩具的所有交互都要绑定触感震动反馈，同时加上一些环境粒子或光晕特效，特效的强弱要跟陀螺的转速实时联动。所有内容都放在一个页面里，不需要任何导航跳转。</v>
-      </c>
-      <c r="K182" t="str">
         <v/>
       </c>
     </row>
@@ -6780,7 +6233,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>q_scene_052_001</v>
+        <v>q_scene_052_003</v>
       </c>
       <c r="C183" t="str">
         <v>多媒体处理</v>
@@ -6789,24 +6242,21 @@
         <v>图片编辑/滤镜/裁剪</v>
       </c>
       <c r="E183" t="str">
-        <v>One-click background removal and replacement</v>
+        <v>Brightness, contrast and saturation adjuster</v>
       </c>
       <c r="F183" t="str">
         <v>medium</v>
       </c>
       <c r="G183">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="H183">
-        <v>10480</v>
+        <v>0</v>
       </c>
       <c r="I183" t="str">
-        <v>Need to build a one-click background removal and replacement feature for the photo editor. Tapping a "Remove BG" button should automatically detect and cut out the subject, then show a bottom sheet with replacement options — solid colors, gradient presets, and a "Choose from Gallery" option. The cutout should have a soft edge/feather effect so it doesn't look harsh. After picking a new background, the user should be able to drag and scale the subject layer on top of it before hitting save. Keep it all within a single screen flow without navigating away.</v>
+        <v>[DRY-RUN] Brightness, contrast and saturation adjuster — medium</v>
       </c>
       <c r="J183" t="str">
-        <v>需要在图片编辑器里做一个一键抠图换背景的功能。用户点击「去除背景」按钮后，系统自动识别并抠出主体，然后从底部弹出一个操作面板，里面包含纯色、渐变预设以及「从相册选取」这几个背景替换选项。抠出的主体边缘要有羽化软化处理，不能显得生硬。选好新背景之后，用户可以在背景上对主体图层进行拖动和缩放调整，确认后再点击保存。整个流程要在同一个页面内完成，不能跳转到其他页面。</v>
-      </c>
-      <c r="K183" t="str">
         <v/>
       </c>
     </row>
@@ -6815,33 +6265,30 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>q_scene_052_002</v>
+        <v>q_scene_053_001</v>
       </c>
       <c r="C184" t="str">
         <v>多媒体处理</v>
       </c>
       <c r="D184" t="str">
-        <v>图片编辑/滤镜/裁剪</v>
+        <v>海报/简历/卡片模板 ★</v>
       </c>
       <c r="E184" t="str">
-        <v>Portrait beauty filter and skin tone adjust</v>
+        <v>Business card front-and-back designer</v>
       </c>
       <c r="F184" t="str">
         <v>medium</v>
       </c>
       <c r="G184">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="H184">
-        <v>9882</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
-        <v>Need to build a portrait beauty filter panel for a mobile photo editor — it should include a skin smoothing slider, a skin tone adjustment wheel (warm/cool tones plus a hue picker), and a separate brightness/whitening control for the face area only. The UI should stack these controls in a bottom sheet that slides up when the user taps the "Beauty" button, with real-time preview applied to the image as sliders are dragged. Face detection should trigger automatically to mask the effect to skin regions only.</v>
+        <v>[DRY-RUN] Business card front-and-back designer — medium</v>
       </c>
       <c r="J184" t="str">
-        <v>要给一款手机端修图应用做一个人像美颜滤镜面板——需要包含磨皮滑块、肤色调节色轮（支持冷暖色调切换以及色相自由拾取），以及一个单独针对面部区域的亮度/美白控制项。这几个控件要叠放在一个底部抽屉里，用户点击"美颜"按钮时从底部滑入展开，拖动滑块的同时图片实时预览效果。人脸检测需要自动触发，将滤镜效果精准遮罩到皮肤区域。</v>
-      </c>
-      <c r="K184" t="str">
         <v/>
       </c>
     </row>
@@ -6850,7 +6297,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="str">
-        <v>q_scene_053_001</v>
+        <v>q_scene_053_002</v>
       </c>
       <c r="C185" t="str">
         <v>多媒体处理</v>
@@ -6859,24 +6306,21 @@
         <v>海报/简历/卡片模板 ★</v>
       </c>
       <c r="E185" t="str">
-        <v>ATS-optimized resume template builder</v>
+        <v>Wedding invitation card creator</v>
       </c>
       <c r="F185" t="str">
         <v>medium</v>
       </c>
       <c r="G185">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="H185">
-        <v>74245</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
-        <v>Build out the resume template builder screen for the app — it needs to focus on ATS-friendly layouts, so the templates should use single-column or clean two-column structures with no fancy graphics or text boxes that would confuse parsers. Include a template picker at the top with 4–5 preset styles (labeled things like "Classic", "Modern Clean", "Tech Minimal"), and below that a live preview panel showing how the resume looks as the user fills in sections. Make sure the section order (Summary, Experience, Education, Skills) is drag-reorderable but defaults to the ATS-recommended order. Also add a small "ATS Score" indicator somewhere visible that updates based on keyword density and formatting choices.</v>
+        <v>[DRY-RUN] Wedding invitation card creator — medium</v>
       </c>
       <c r="J185" t="str">
-        <v>帮我做一个简历模板生成器页面——核心是要兼容ATS解析，所以模板只能用单栏或简洁的双栏布局，不能有花哨的图形或文本框，免得被解析器误读。顶部放一个模板选择器，提供4到5种预设风格，名字可以叫"经典"、"现代简洁"、"科技极简"之类的。下方是一个实时预览区，用户填写各个板块内容时可以即时看到简历效果。简历板块的排列顺序（个人简介、工作经历、教育背景、技能特长）要支持拖拽排序，但默认按ATS推荐顺序排列。另外在显眼的位置加一个小的"ATS评分"指示器，根据关键词密度和排版选择实时更新分值。</v>
-      </c>
-      <c r="K185" t="str">
         <v/>
       </c>
     </row>
@@ -6885,7 +6329,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="str">
-        <v>q_scene_053_002</v>
+        <v>q_scene_053_003</v>
       </c>
       <c r="C186" t="str">
         <v>多媒体处理</v>
@@ -6894,24 +6338,21 @@
         <v>海报/简历/卡片模板 ★</v>
       </c>
       <c r="E186" t="str">
-        <v>Event poster with date and venue placeholder</v>
+        <v>Instagram story animated template</v>
       </c>
       <c r="F186" t="str">
         <v>medium</v>
       </c>
       <c r="G186">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="H186">
-        <v>136337</v>
+        <v>0</v>
       </c>
       <c r="I186" t="str">
-        <v>Build a mobile event poster template screen where users can tap to edit a date placeholder (formatted as "MON DD, YYYY") and a venue placeholder ("Venue Name + City") directly on the poster canvas. The poster should have a bold headline area at the top, an eye-catching background that supports both solid color and gradient options, and the date/venue fields should sit near the bottom in a visually distinct block. Include a simple toolbar at the bottom for switching background style and font color, and make sure the editable fields show a subtle highlight border when tapped so it's obvious what's being edited.</v>
+        <v>[DRY-RUN] Instagram story animated template — medium</v>
       </c>
       <c r="J186" t="str">
-        <v>做一个移动端活动海报模板页面，用户可以直接在海报画布上点击编辑日期占位符（格式为"MON DD, YYYY"）和场地占位符（"场馆名称 + 城市"），不需要跳转到别的编辑页面。海报顶部要有一块视觉突出的大标题区域，背景支持纯色和渐变两种风格，日期和场地信息放在海报靠近底部的位置，用一个样式明显的信息块来承载。页面底部放一个简单的工具栏，用于切换背景样式和文字颜色。用户点击可编辑字段时，该字段要出现一个淡淡的高亮描边，让人一眼就能看出当前正在编辑哪个内容。</v>
-      </c>
-      <c r="K186" t="str">
         <v/>
       </c>
     </row>
@@ -6929,24 +6370,21 @@
         <v>音视频播放界面</v>
       </c>
       <c r="E187" t="str">
-        <v>Music player with waveform visualizer</v>
+        <v>Audiobook chapter navigation player</v>
       </c>
       <c r="F187" t="str">
         <v>medium</v>
       </c>
       <c r="G187">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="H187">
-        <v>71113</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
-        <v>Build a mobile music player screen that includes a real-time waveform visualizer — the waveform should animate in sync with playback and be displayed as a horizontal bar graph style (not circular). Include the standard controls: play/pause, skip forward/back, and a scrubber bar that overlaps or sits just below the waveform. The track title and artist name should sit at the top, and the overall color scheme should be dark with accent colors pulled dynamically from the album art.</v>
+        <v>[DRY-RUN] Audiobook chapter navigation player — medium</v>
       </c>
       <c r="J187" t="str">
-        <v>做一个移动端音乐播放器界面，要有实时波形可视化效果——波形需要跟随播放进度同步动起来，样式是横向柱状图那种（不要圆形的）。标准控制栏要齐全：播放/暂停、快进快退，还有一个进度条，叠在波形上面或者紧贴波形下方都行。曲目名称和歌手名放在顶部，整体配色走深色风格，强调色从专辑封面里动态提取。</v>
-      </c>
-      <c r="K187" t="str">
         <v/>
       </c>
     </row>
@@ -6964,24 +6402,21 @@
         <v>音视频播放界面</v>
       </c>
       <c r="E188" t="str">
-        <v>Podcast episode browser and queue manager</v>
+        <v>Lyrics sync karaoke mode display</v>
       </c>
       <c r="F188" t="str">
         <v>medium</v>
       </c>
       <c r="G188">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H188">
-        <v>70462</v>
+        <v>0</v>
       </c>
       <c r="I188" t="str">
-        <v>Build a podcast episode browser screen with a queue manager panel for a mobile app. The browser should show episodes in a scrollable list with thumbnail, title, duration, and publish date — tapping an episode opens a bottom sheet with description and an "Add to Queue" button. The queue panel slides up from the bottom and lets users reorder episodes via drag handles and remove them with a swipe-left gesture. Keep the now-playing mini-bar visible at the bottom even when the queue panel is open.</v>
+        <v>[DRY-RUN] Lyrics sync karaoke mode display — medium</v>
       </c>
       <c r="J188" t="str">
-        <v>做一个移动端播客单集浏览页面，带有播放队列管理面板。浏览列表需要支持滚动，每条单集显示封面缩略图、标题、时长和发布日期，点击某集后从底部弹出底部抽屉，展示简介并提供"加入队列"按钮。队列面板从底部上滑展开，支持通过拖拽手柄调整单集顺序，向左滑动可删除。队列面板打开时，底部正在播放的迷你播放条需始终保持可见。</v>
-      </c>
-      <c r="K188" t="str">
         <v/>
       </c>
     </row>
@@ -6999,24 +6434,21 @@
         <v>内容创作工具</v>
       </c>
       <c r="E189" t="str">
-        <v>Blog post draft with SEO keyword hint</v>
+        <v>Script and screenplay format writer</v>
       </c>
       <c r="F189" t="str">
         <v>medium</v>
       </c>
       <c r="G189">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="H189">
-        <v>70434</v>
+        <v>0</v>
       </c>
       <c r="I189" t="str">
-        <v>Build a blog post draft screen for the mobile content creation app — it should have a text editor area where users can type their draft, and a collapsible panel at the bottom that shows suggested SEO keywords based on the current content. The keyword hints should update as the user types (debounced, not on every keystroke), and each keyword chip should show an estimated search volume badge. Tapping a keyword inserts it into the draft at the cursor position.</v>
+        <v>[DRY-RUN] Script and screenplay format writer — medium</v>
       </c>
       <c r="J189" t="str">
-        <v>为移动端内容创作应用做一个博客文章草稿编辑页面——需要有一个文本编辑区供用户输入草稿内容，底部有一个可折叠面板，根据当前内容给出 SEO 关键词建议。关键词提示要随用户输入实时更新（做防抖处理，不要每次击键都触发），每个关键词标签上显示预估搜索量的角标。点击某个关键词后，将其插入到草稿中光标所在的位置。</v>
-      </c>
-      <c r="K189" t="str">
         <v/>
       </c>
     </row>
@@ -7034,24 +6466,21 @@
         <v>内容创作工具</v>
       </c>
       <c r="E190" t="str">
-        <v>Social media caption AI generator</v>
+        <v>Podcast episode outline builder</v>
       </c>
       <c r="F190" t="str">
         <v>medium</v>
       </c>
       <c r="G190">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="H190">
-        <v>71483</v>
+        <v>0</v>
       </c>
       <c r="I190" t="str">
-        <v>Build a screen for the AI caption generator feature — user picks a platform (Instagram, TikTok, Twitter/X, LinkedIn) from a horizontal chip selector at the top, then pastes or types a brief content description in a text area, hits "Generate," and gets 3 caption variations displayed as swipeable cards below. Each card should show the caption text, a character count badge, and a copy button. Keep the layout single-column and thumb-friendly since this is mobile.</v>
+        <v>[DRY-RUN] Podcast episode outline builder — medium</v>
       </c>
       <c r="J190" t="str">
-        <v>做一个AI文案生成功能的页面——顶部用横向的标签选择器让用户选平台（Instagram、TikTok、Twitter/X、LinkedIn），然后在下方的文本框里粘贴或输入简短的内容描述，点击"生成"后，底部以可左右滑动的卡片形式展示3条文案备选。每张卡片上要显示文案正文、字数角标和一个复制按钮。整体保持单列布局，考虑到是移动端，操作区域要适合拇指点击。</v>
-      </c>
-      <c r="K190" t="str">
         <v/>
       </c>
     </row>
@@ -7072,18 +6501,15 @@
         <v>medium</v>
       </c>
       <c r="G191">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="H191">
-        <v>9971</v>
+        <v>0</v>
       </c>
       <c r="I191" t="str">
-        <v>Build a news feed screen for a mobile app — cards should show a headline, source name, timestamp, and thumbnail on the right side. Add a horizontal category tab bar at the top (like "Top", "Tech", "Sports", "Finance") that filters the feed. Cards need a subtle swipe-left action to dismiss a story and a bookmark icon to save it. Keep the layout clean, no clutter, and make sure the tab bar stays sticky when scrolling.</v>
+        <v>[DRY-RUN] null — medium</v>
       </c>
       <c r="J191" t="str">
-        <v>帮我做一个移动端的新闻流页面——每张卡片要显示标题、来源名称、时间戳，以及右侧的缩略图。顶部加一个横向的分类标签栏，类似"推荐"、"科技"、"体育"、"财经"这种，用来筛选内容。卡片要支持向左轻扫来屏蔽这条新闻，还要有一个书签图标可以收藏。整体布局要简洁干净，不要太杂乱，滚动时标签栏要保持吸顶固定。</v>
-      </c>
-      <c r="K191" t="str">
         <v/>
       </c>
     </row>
@@ -7104,18 +6530,15 @@
         <v>medium</v>
       </c>
       <c r="G192">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="H192">
-        <v>10562</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
-        <v>Build a mobile news feed screen with an infinite-scroll card list — each card needs a thumbnail on the left, a headline (2-line max with ellipsis), source name, and a relative timestamp like "3h ago". Add a top tab bar for category filtering (e.g. Top, Tech, Sports, Finance) that highlights the active tab with an underline indicator and smoothly scrolls to reposition content on switch. Cards should have a subtle tap highlight state and a bookmark icon in the top-right corner that toggles filled/outline on press.</v>
+        <v>[DRY-RUN] null — medium</v>
       </c>
       <c r="J192" t="str">
-        <v>做一个移动端新闻资讯页面，主体是支持无限滚动的卡片列表——每张卡片左侧放缩略图，右侧显示标题（最多两行，超出部分用省略号截断）、来源名称以及相对时间戳，比如"3小时前"。顶部加一排分类 Tab 栏（例如推荐、科技、体育、财经），当前激活的 Tab 用下划线指示器高亮，切换分类时内容区要平滑滚动重新定位。卡片点击时需要有轻微的高亮反馈，右上角放一个书签图标，每次点击在填充和描边两种状态之间切换。</v>
-      </c>
-      <c r="K192" t="str">
         <v/>
       </c>
     </row>
@@ -7133,24 +6556,21 @@
         <v>文章详情/阅读模式</v>
       </c>
       <c r="E193" t="str">
-        <v>Distraction-free reading mode with font control</v>
+        <v>Sentence-level highlight and share quote</v>
       </c>
       <c r="F193" t="str">
         <v>medium</v>
       </c>
       <c r="G193">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="H193">
-        <v>8579</v>
+        <v>0</v>
       </c>
       <c r="I193" t="str">
-        <v>Build a distraction-free reading mode for the article detail screen — when the user taps the screen, the top nav bar and bottom toolbar should fade out, leaving only the article content. Add a persistent floating button (bottom-right corner) that opens a small panel with font size controls (smaller/larger with a live preview) and a font style toggle between serif and sans-serif. The panel should dismiss when tapping outside it, and the reading mode state should persist if the user navigates back and reopens the same article.</v>
+        <v>[DRY-RUN] Sentence-level highlight and share quote — medium</v>
       </c>
       <c r="J193" t="str">
-        <v>帮我在文章详情页做一个沉浸式阅读模式——用户点击屏幕时，顶部导航栏和底部工具栏淡出隐藏，只保留正文内容。右下角需要有一个常驻的悬浮按钮，点击后弹出一个小面板，里面有字号调节功能（缩小/放大，实时预览效果）以及衬线体和无衬线体之间的切换。点击面板外部区域时自动关闭面板。另外，阅读模式的状态要能持久化，用户返回后再次打开同一篇文章时应该恢复之前的设置。</v>
-      </c>
-      <c r="K193" t="str">
         <v/>
       </c>
     </row>
@@ -7168,24 +6588,21 @@
         <v>文章详情/阅读模式</v>
       </c>
       <c r="E194" t="str">
-        <v>Article estimated read time display</v>
+        <v>In-article glossary term popup</v>
       </c>
       <c r="F194" t="str">
         <v>medium</v>
       </c>
       <c r="G194">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="H194">
-        <v>8958</v>
+        <v>0</v>
       </c>
       <c r="I194" t="str">
-        <v>Add an estimated read time indicator to the article detail page — it should appear near the article title or subtitle area, showing something like "5 min read" based on word count. Keep it subtle, maybe a small clock icon + text in a muted color so it doesn't compete with the headline. Also make sure it updates dynamically if the article content changes length, and on the reading progress bar at the bottom show remaining read time like "2 min left" as the user scrolls.</v>
+        <v>[DRY-RUN] In-article glossary term popup — medium</v>
       </c>
       <c r="J194" t="str">
-        <v>在文章详情页加一个预计阅读时长的提示，放在标题或副标题附近，根据字数显示类似"5分钟阅读"这样的内容。风格要低调一点，用个小时钟图标配上灰色文字，别抢了标题的风头。另外如果文章内容长度有变化，这个时长要能动态更新。底部的阅读进度条那里也要加上剩余阅读时间，用户往下滚动时实时显示"还剩2分钟"这样的信息。</v>
-      </c>
-      <c r="K194" t="str">
         <v/>
       </c>
     </row>
@@ -7203,24 +6620,21 @@
         <v>订阅/频道管理</v>
       </c>
       <c r="E195" t="str">
-        <v>News source subscription browser</v>
+        <v>Email newsletter import and read in-app</v>
       </c>
       <c r="F195" t="str">
         <v>medium</v>
       </c>
       <c r="G195">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="H195">
-        <v>9790</v>
+        <v>0</v>
       </c>
       <c r="I195" t="str">
-        <v>Build a news source subscription browser screen for the app — users should be able to scroll through a categorized list of available sources (grouped by topic like Tech, Politics, Sports, etc.), see a brief description and follower count for each, and tap a subscribe/unsubscribe toggle that updates instantly without a full page reload. Also needs a search bar at the top to filter sources by name, and already-subscribed sources should be visually distinguished (like a checkmark or filled button state) so users can tell at a glance what they're already following.</v>
+        <v>[DRY-RUN] Email newsletter import and read in-app — medium</v>
       </c>
       <c r="J195" t="str">
-        <v>做一个新闻来源订阅浏览页面——用户可以滚动浏览按话题分类的来源列表（比如科技、政治、体育等），每个来源显示简短描述和关注人数，点击订阅/取消订阅的开关后立即生效，不需要整页刷新。顶部还要有一个搜索栏，方便按名称筛选来源。已订阅的来源需要有明显的视觉区分（比如打勾或按钮填充状态），让用户一眼就能看出自己已经关注了哪些。</v>
-      </c>
-      <c r="K195" t="str">
         <v/>
       </c>
     </row>
@@ -7238,24 +6652,21 @@
         <v>订阅/频道管理</v>
       </c>
       <c r="E196" t="str">
-        <v>Interest category selector for personalization</v>
+        <v>RSS feed add by URL</v>
       </c>
       <c r="F196" t="str">
         <v>medium</v>
       </c>
       <c r="G196">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="H196">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="I196" t="str">
-        <v>Build an interest category selector screen for the onboarding flow of a news subscription app. Users should be able to pick multiple topic categories (like Politics, Tech, Sports, Finance, etc.) displayed as a grid of tappable chips or cards with icons. Selected ones should visually highlight, and there should be a minimum selection requirement (at least 3) before the "Continue" button activates. Keep it mobile-first with smooth tap feedback animations.</v>
+        <v>[DRY-RUN] RSS feed add by URL — medium</v>
       </c>
       <c r="J196" t="str">
-        <v>为新闻订阅应用的引导流程搭建一个兴趣分类选择页面。用户可以从网格布局的可点击标签或卡片中多选感兴趣的话题类别（比如政治、科技、体育、财经等），每个选项都带有图标。选中后要有明显的高亮视觉反馈，并且至少需要选满3个类别，"继续"按钮才会变为可点击状态。整体以移动端优先，点击时要有流畅的动效反馈。</v>
-      </c>
-      <c r="K196" t="str">
         <v/>
       </c>
     </row>
@@ -7273,24 +6684,21 @@
         <v>搜索与筛选</v>
       </c>
       <c r="E197" t="str">
-        <v>News keyword search with date range filter</v>
+        <v>Author and journalist name search</v>
       </c>
       <c r="F197" t="str">
         <v>medium</v>
       </c>
       <c r="G197">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H197">
-        <v>10417</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
-        <v>Build a news search screen with a keyword input bar at the top and a date range filter below it — users should be able to pick a start and end date using a calendar picker. When they hit search, results show as a scrollable list of news cards with title, source, and publish date. The date filter should default to the last 7 days but be collapsible to save space. Also make sure the search triggers both on button tap and on keyboard submit.</v>
+        <v>[DRY-RUN] Author and journalist name search — medium</v>
       </c>
       <c r="J197" t="str">
-        <v>做一个新闻搜索页面，顶部放关键词输入框，下方是日期范围筛选器——用户可以通过日历选择器分别设置开始和结束日期。点击搜索后，结果以可滚动的新闻卡片列表展示，每张卡片显示标题、来源和发布时间。日期筛选器默认选中最近7天，同时支持折叠收起以节省空间。另外，搜索要同时支持点击按钮和键盘回车两种触发方式。</v>
-      </c>
-      <c r="K197" t="str">
         <v/>
       </c>
     </row>
@@ -7308,24 +6716,21 @@
         <v>搜索与筛选</v>
       </c>
       <c r="E198" t="str">
-        <v>Trending topic search suggestion</v>
+        <v>Source and outlet name filter</v>
       </c>
       <c r="F198" t="str">
         <v>medium</v>
       </c>
       <c r="G198">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="H198">
-        <v>8579</v>
+        <v>0</v>
       </c>
       <c r="I198" t="str">
-        <v>Build a trending topic search suggestion dropdown for the news app's search bar — when a user taps the search field, show a list of real-time trending topics pulled from the feed (like "Top 10 Today" style), each with a small fire/trending icon and a view count badge. Tapping any suggestion should auto-fill the search bar and trigger a search. Keep it scrollable horizontally if there are more than 5 items, and make sure it dismisses cleanly when the user starts typing their own query.</v>
+        <v>[DRY-RUN] Source and outlet name filter — medium</v>
       </c>
       <c r="J198" t="str">
-        <v>给新闻App的搜索栏做一个热门话题搜索建议下拉组件——用户点击搜索框时，自动展示从信息流中拉取的实时热榜话题（类似"今日热榜前10"的风格），每个条目带一个小火焰/热门图标和浏览量角标。点击任意建议词条后，自动填充搜索框并触发搜索。超过5条时支持横向滑动浏览，用户开始自己输入内容时，下拉列表要能干净地自动收起。</v>
-      </c>
-      <c r="K198" t="str">
         <v/>
       </c>
     </row>
@@ -7343,24 +6748,21 @@
         <v>商品详情/规格选择</v>
       </c>
       <c r="E199" t="str">
-        <v>Product photo zoom and 360-degree rotation view</v>
+        <v>Size guide with body measurement input</v>
       </c>
       <c r="F199" t="str">
         <v>medium</v>
       </c>
       <c r="G199">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="H199">
-        <v>10619</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
-        <v>Need to build a product image viewer for the detail page that supports both pinch-to-zoom on individual photos and a 360-degree rotation mode when the product has a spin sequence loaded. The 360 view should let users drag left/right to rotate through the frames smoothly, and there should be a toggle button to switch between normal gallery mode and 360 mode. Zoom should cap at like 3x and snap back when released. Make sure it works well on mobile touch events.</v>
+        <v>[DRY-RUN] Size guide with body measurement input — medium</v>
       </c>
       <c r="J199" t="str">
-        <v>详情页需要做一个商品图片查看器，支持对单张图片进行双指捏合缩放，同时在商品有360度旋转序列图的情况下提供全景旋转模式。360度视图要能让用户左右拖动来流畅地切换帧画面，并且需要一个切换按钮在普通相册模式和360度模式之间来回切换。缩放最大倍数限制在3倍左右，松手后自动回弹复位。要确保在移动端触摸事件上的体验良好。</v>
-      </c>
-      <c r="K199" t="str">
         <v/>
       </c>
     </row>
@@ -7378,24 +6780,21 @@
         <v>购物车/结算</v>
       </c>
       <c r="E200" t="str">
-        <v>Multi-item cart with quantity adjuster</v>
+        <v>Save-for-later from cart action</v>
       </c>
       <c r="F200" t="str">
         <v>medium</v>
       </c>
       <c r="G200">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="H200">
-        <v>8333</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
-        <v>Build a multi-item shopping cart screen for mobile where each cart item has a quantity adjuster with + and - buttons, and the total price updates in real time as quantities change. Items should show a thumbnail, product name, unit price, and subtotal. If quantity hits 0, prompt to remove the item instead of going negative. Include a sticky bottom bar showing the total item count and grand total with a checkout button.</v>
+        <v>[DRY-RUN] Save-for-later from cart action — medium</v>
       </c>
       <c r="J200" t="str">
-        <v>做一个移动端的多商品购物车页面，每个商品行都有加减数量的「+」和「-」按钮，数量变化时总价实时更新。每条商品需要展示缩略图、商品名称、单价和小计。当数量减到 0 时，弹出提示询问是否删除该商品，而不是让数量继续变为负数。页面底部有一个吸底栏，显示已选商品总件数和合计金额，并带有结算按钮。</v>
-      </c>
-      <c r="K200" t="str">
         <v/>
       </c>
     </row>
@@ -7413,30 +6812,27 @@
         <v>订单/物流追踪</v>
       </c>
       <c r="E201" t="str">
-        <v>Real-time shipment GPS map tracking</v>
+        <v>Delivery status step timeline</v>
       </c>
       <c r="F201" t="str">
         <v>medium</v>
       </c>
       <c r="G201">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="H201">
-        <v>10305</v>
+        <v>0</v>
       </c>
       <c r="I201" t="str">
-        <v>Build a real-time GPS map tracking screen for a shipment tracking mobile app. The map should show the delivery driver's live location as a moving marker that updates every 10–15 seconds, with the route drawn from origin to destination and the user's delivery address pinned. Include a bottom sheet that shows estimated arrival time, current status (e.g. "Out for delivery"), and driver info — it should partially overlap the map and be swipeable up for more details.</v>
+        <v>[DRY-RUN] Delivery status step timeline — medium</v>
       </c>
       <c r="J201" t="str">
-        <v>为一款货物追踪移动应用开发实时 GPS 地图追踪页面。地图上需要显示配送员的实时位置，用一个每隔 10 到 15 秒自动更新的动态标记来表示，同时在地图上绘制从起点到终点的配送路线，并标注用户的收货地址。页面底部需要有一个 bottom sheet，展示预计到达时间、当前配送状态（如"正在配送中"）以及快递员信息——它应该部分遮盖地图，并且支持向上滑动以查看更多详情。</v>
-      </c>
-      <c r="K201" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J201"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7444,6 +6840,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B13"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7458,7 +6858,7 @@
         <v>generated_at</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-12T13:50:16.644Z</v>
+        <v>2026-05-14T03:26:47.230Z</v>
       </c>
     </row>
     <row r="3">
@@ -7522,7 +6922,7 @@
         <v>avg_word_count</v>
       </c>
       <c r="B10">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -7546,7 +6946,7 @@
         <v>elapsed_sec</v>
       </c>
       <c r="B13">
-        <v>667.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7558,7 +6958,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7570,10 +6974,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>深度研究展示</v>
+        <v>交互方式</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -7581,20 +6985,20 @@
         <v>实用工具</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>交互方式</v>
+        <v>教育学习</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>教育学习</v>
+        <v>办公效率</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -7602,15 +7006,15 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>办公效率</v>
+        <v>健康管理</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>健康管理</v>
+        <v>出行助手</v>
       </c>
       <c r="B7">
         <v>15</v>
@@ -7618,31 +7022,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>出行助手</v>
+        <v>美食探店</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>美食探店</v>
+        <v>休闲游戏</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>休闲游戏</v>
+        <v>多媒体处理</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>多媒体处理</v>
+        <v>新闻资讯</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -7650,23 +7054,15 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>新闻资讯</v>
+        <v>购物消费</v>
       </c>
       <c r="B12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>购物消费</v>
-      </c>
-      <c r="B13">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
   </ignoredErrors>
 </worksheet>
 </file>